--- a/outputs/VIC_historical_prices.xlsx
+++ b/outputs/VIC_historical_prices.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly Data" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Heatmap" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Monthly Data" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Heatmap" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/outputs/VIC_historical_prices.xlsx
+++ b/outputs/VIC_historical_prices.xlsx
@@ -528,16 +528,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>73.63</v>
+        <v>70.13</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>92.45</v>
+        <v>89.88</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>74.58</v>
+        <v>70.93000000000001</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>93.78</v>
+        <v>91.06999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -547,16 +547,16 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>78.79000000000001</v>
+        <v>76.62</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>93.17</v>
+        <v>91.48</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>80.89</v>
+        <v>78.55</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>95.66</v>
+        <v>93.81999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>70.47</v>
+        <v>69.05</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>83.56</v>
+        <v>82.26000000000001</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>73.15000000000001</v>
+        <v>71.54000000000001</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>86.76000000000001</v>
+        <v>85.25</v>
       </c>
     </row>
     <row r="8">
@@ -585,16 +585,16 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>79.51000000000001</v>
+        <v>79.23</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>93.23</v>
+        <v>92.84999999999999</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>86.83</v>
+        <v>86.37</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>101.89</v>
+        <v>101.28</v>
       </c>
     </row>
     <row r="9">
@@ -604,22 +604,22 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>78.42</v>
+        <v>78.31</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>94.55</v>
+        <v>94.37</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>92.8</v>
+        <v>92.56999999999999</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>112.17</v>
+        <v>111.82</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Data through: Mar 2026</t>
+          <t>Data through: Apr 2026</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F274"/>
+  <dimension ref="A1:F275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6233,6 +6233,26 @@
       </c>
       <c r="F274" s="7" t="inlineStr"/>
     </row>
+    <row r="275">
+      <c r="A275" s="4" t="inlineStr">
+        <is>
+          <t>Apr 2026</t>
+        </is>
+      </c>
+      <c r="B275" s="5" t="n">
+        <v>32.76</v>
+      </c>
+      <c r="C275" s="5" t="n">
+        <v>39.73</v>
+      </c>
+      <c r="D275" s="5" t="n">
+        <v>32.76</v>
+      </c>
+      <c r="E275" s="5" t="n">
+        <v>39.73</v>
+      </c>
+      <c r="F275" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6244,7 +6264,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E274"/>
+  <dimension ref="A1:E275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -11468,8 +11488,27 @@
         <v>44.39</v>
       </c>
     </row>
+    <row r="275">
+      <c r="A275" s="4" t="inlineStr">
+        <is>
+          <t>Apr 2026</t>
+        </is>
+      </c>
+      <c r="B275" s="5" t="n">
+        <v>32.76</v>
+      </c>
+      <c r="C275" s="5" t="n">
+        <v>39.73</v>
+      </c>
+      <c r="D275" s="5" t="n">
+        <v>32.76</v>
+      </c>
+      <c r="E275" s="5" t="n">
+        <v>39.73</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B274">
+  <conditionalFormatting sqref="B2:B275">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -11481,7 +11520,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C274">
+  <conditionalFormatting sqref="C2:C275">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -11493,7 +11532,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D274">
+  <conditionalFormatting sqref="D2:D275">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -11505,7 +11544,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E274">
+  <conditionalFormatting sqref="E2:E275">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>

--- a/outputs/VIC_historical_prices.xlsx
+++ b/outputs/VIC_historical_prices.xlsx
@@ -528,16 +528,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>70.13</v>
+        <v>67.18000000000001</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>89.88</v>
+        <v>85.73999999999999</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>70.93000000000001</v>
+        <v>68.58</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>91.06999999999999</v>
+        <v>87.76000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -547,16 +547,16 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>76.62</v>
+        <v>72.84999999999999</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>91.48</v>
+        <v>87.20999999999999</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>78.55</v>
+        <v>75.48</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>93.81999999999999</v>
+        <v>90.41</v>
       </c>
     </row>
     <row r="7">
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>69.05</v>
+        <v>66.70999999999999</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>82.26000000000001</v>
+        <v>79.43000000000001</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>71.54000000000001</v>
+        <v>69.78</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>85.25</v>
+        <v>83.15000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -585,16 +585,16 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>79.23</v>
+        <v>78.73</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>92.84999999999999</v>
+        <v>91.67</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>86.37</v>
+        <v>86.73999999999999</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>101.28</v>
+        <v>101.02</v>
       </c>
     </row>
     <row r="9">
@@ -604,22 +604,22 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>78.31</v>
+        <v>78.20999999999999</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>94.37</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>92.56999999999999</v>
+        <v>93.56999999999999</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>111.82</v>
+        <v>112.85</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Data through: Apr 2026</t>
+          <t>Data through: May 2026</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F275"/>
+  <dimension ref="A1:F276"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -690,10 +690,10 @@
         <v>32.99</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>46.97</v>
+        <v>47.61</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>60.48</v>
+        <v>61.31</v>
       </c>
       <c r="F2" s="7" t="inlineStr"/>
     </row>
@@ -710,10 +710,10 @@
         <v>23.45</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>36.87</v>
+        <v>37.38</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>42.91</v>
+        <v>43.5</v>
       </c>
       <c r="F3" s="7" t="inlineStr"/>
     </row>
@@ -730,10 +730,10 @@
         <v>25.19</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>37.86</v>
+        <v>38.38</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>46.01</v>
+        <v>46.64</v>
       </c>
       <c r="F4" s="7" t="inlineStr"/>
     </row>
@@ -750,10 +750,10 @@
         <v>25.19</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>37.81</v>
+        <v>38.33</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>45.92</v>
+        <v>46.56</v>
       </c>
       <c r="F5" s="7" t="inlineStr"/>
     </row>
@@ -770,10 +770,10 @@
         <v>26.23</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>38.55</v>
+        <v>39.08</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>47.74</v>
+        <v>48.39</v>
       </c>
       <c r="F6" s="7" t="inlineStr"/>
     </row>
@@ -790,10 +790,10 @@
         <v>34.01</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>45.36</v>
+        <v>45.99</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>61.79</v>
+        <v>62.64</v>
       </c>
       <c r="F7" s="7" t="inlineStr"/>
     </row>
@@ -810,10 +810,10 @@
         <v>30.37</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>40.79</v>
+        <v>41.35</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>55.01</v>
+        <v>55.77</v>
       </c>
       <c r="F8" s="7" t="inlineStr"/>
     </row>
@@ -830,10 +830,10 @@
         <v>48.76</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>69.75</v>
+        <v>70.70999999999999</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>88.06</v>
+        <v>89.27</v>
       </c>
       <c r="F9" s="7" t="inlineStr"/>
     </row>
@@ -850,10 +850,10 @@
         <v>28.54</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>38.68</v>
+        <v>39.21</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>51.39</v>
+        <v>52.1</v>
       </c>
       <c r="F10" s="7" t="inlineStr"/>
     </row>
@@ -870,10 +870,10 @@
         <v>36.99</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>52.97</v>
+        <v>53.7</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>66.51000000000001</v>
+        <v>67.42</v>
       </c>
       <c r="F11" s="7" t="inlineStr"/>
     </row>
@@ -890,10 +890,10 @@
         <v>39.67</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>56.17</v>
+        <v>56.94</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>71.20999999999999</v>
+        <v>72.19</v>
       </c>
       <c r="F12" s="7" t="inlineStr"/>
     </row>
@@ -910,10 +910,10 @@
         <v>34.73</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>51.32</v>
+        <v>52.02</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>62.25</v>
+        <v>63.11</v>
       </c>
       <c r="F13" s="7" t="inlineStr"/>
     </row>
@@ -930,10 +930,10 @@
         <v>43.7</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>56.15</v>
+        <v>56.92</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>78.22</v>
+        <v>79.3</v>
       </c>
       <c r="F14" s="7" t="inlineStr"/>
     </row>
@@ -950,10 +950,10 @@
         <v>27.37</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>40.31</v>
+        <v>40.86</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>48.92</v>
+        <v>49.6</v>
       </c>
       <c r="F15" s="7" t="inlineStr"/>
     </row>
@@ -970,10 +970,10 @@
         <v>31.48</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>48.55</v>
+        <v>49.22</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>56.19</v>
+        <v>56.97</v>
       </c>
       <c r="F16" s="7" t="inlineStr"/>
     </row>
@@ -990,10 +990,10 @@
         <v>70.45</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>79.91</v>
+        <v>81.01000000000001</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>125.44</v>
+        <v>127.16</v>
       </c>
       <c r="F17" s="7" t="inlineStr"/>
     </row>
@@ -1010,10 +1010,10 @@
         <v>44.55</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>63.33</v>
+        <v>64.2</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>79.12</v>
+        <v>80.20999999999999</v>
       </c>
       <c r="F18" s="7" t="inlineStr"/>
     </row>
@@ -1030,10 +1030,10 @@
         <v>33</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>48.47</v>
+        <v>49.13</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>58.46</v>
+        <v>59.26</v>
       </c>
       <c r="F19" s="7" t="inlineStr"/>
     </row>
@@ -1050,10 +1050,10 @@
         <v>29.72</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>40.37</v>
+        <v>40.93</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>52.53</v>
+        <v>53.25</v>
       </c>
       <c r="F20" s="7" t="inlineStr"/>
     </row>
@@ -1070,10 +1070,10 @@
         <v>27.43</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>38.5</v>
+        <v>39.03</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>48.38</v>
+        <v>49.04</v>
       </c>
       <c r="F21" s="7" t="inlineStr"/>
     </row>
@@ -1090,10 +1090,10 @@
         <v>21.15</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>32.91</v>
+        <v>33.36</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>37.22</v>
+        <v>37.73</v>
       </c>
       <c r="F22" s="7" t="inlineStr"/>
     </row>
@@ -1110,10 +1110,10 @@
         <v>37.8</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>53.79</v>
+        <v>54.53</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>66.38</v>
+        <v>67.3</v>
       </c>
       <c r="F23" s="7" t="inlineStr"/>
     </row>
@@ -1130,10 +1130,10 @@
         <v>29.2</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>43.05</v>
+        <v>43.64</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>51.18</v>
+        <v>51.88</v>
       </c>
       <c r="F24" s="7" t="inlineStr"/>
     </row>
@@ -1150,10 +1150,10 @@
         <v>27.29</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>41.18</v>
+        <v>41.74</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>47.74</v>
+        <v>48.39</v>
       </c>
       <c r="F25" s="7" t="inlineStr"/>
     </row>
@@ -1170,10 +1170,10 @@
         <v>32.37</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>46.22</v>
+        <v>46.86</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>56.44</v>
+        <v>57.21</v>
       </c>
       <c r="F26" s="7" t="inlineStr"/>
     </row>
@@ -1190,10 +1190,10 @@
         <v>40.25</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>52.13</v>
+        <v>52.85</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>69.94</v>
+        <v>70.91</v>
       </c>
       <c r="F27" s="7" t="inlineStr"/>
     </row>
@@ -1210,10 +1210,10 @@
         <v>37.44</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>50.47</v>
+        <v>51.17</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>64.84999999999999</v>
+        <v>65.73999999999999</v>
       </c>
       <c r="F28" s="7" t="inlineStr"/>
     </row>
@@ -1230,10 +1230,10 @@
         <v>28.49</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>39.15</v>
+        <v>39.68</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>49.26</v>
+        <v>49.94</v>
       </c>
       <c r="F29" s="7" t="inlineStr"/>
     </row>
@@ -1250,10 +1250,10 @@
         <v>46.39</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>52.99</v>
+        <v>53.72</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>80.06999999999999</v>
+        <v>81.17</v>
       </c>
       <c r="F30" s="7" t="inlineStr"/>
     </row>
@@ -1270,10 +1270,10 @@
         <v>49.23</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>59</v>
+        <v>59.81</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>84.83</v>
+        <v>86</v>
       </c>
       <c r="F31" s="7" t="inlineStr"/>
     </row>
@@ -1290,10 +1290,10 @@
         <v>88.63</v>
       </c>
       <c r="D32" s="5" t="n">
-        <v>91.81999999999999</v>
+        <v>93.08</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>152.28</v>
+        <v>154.38</v>
       </c>
       <c r="F32" s="7" t="inlineStr"/>
     </row>
@@ -1310,10 +1310,10 @@
         <v>105.51</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>95.95</v>
+        <v>97.27</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>180.77</v>
+        <v>183.26</v>
       </c>
       <c r="F33" s="7" t="inlineStr"/>
     </row>
@@ -1330,10 +1330,10 @@
         <v>29.33</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>39.91</v>
+        <v>40.46</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>50.11</v>
+        <v>50.8</v>
       </c>
       <c r="F34" s="7" t="inlineStr"/>
     </row>
@@ -1350,10 +1350,10 @@
         <v>27.86</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>38.39</v>
+        <v>38.92</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>47.35</v>
+        <v>48</v>
       </c>
       <c r="F35" s="7" t="inlineStr"/>
     </row>
@@ -1370,10 +1370,10 @@
         <v>37.94</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>47.76</v>
+        <v>48.42</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>64.14</v>
+        <v>65.02</v>
       </c>
       <c r="F36" s="7" t="inlineStr"/>
     </row>
@@ -1390,10 +1390,10 @@
         <v>42.49</v>
       </c>
       <c r="D37" s="5" t="n">
-        <v>58.21</v>
+        <v>59.01</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>71.45999999999999</v>
+        <v>72.44</v>
       </c>
       <c r="F37" s="7" t="inlineStr"/>
     </row>
@@ -1410,10 +1410,10 @@
         <v>71.86</v>
       </c>
       <c r="D38" s="5" t="n">
-        <v>79.15000000000001</v>
+        <v>80.23999999999999</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>120.5</v>
+        <v>122.16</v>
       </c>
       <c r="F38" s="7" t="inlineStr"/>
     </row>
@@ -1430,10 +1430,10 @@
         <v>39.11</v>
       </c>
       <c r="D39" s="5" t="n">
-        <v>53.85</v>
+        <v>54.59</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>65.39</v>
+        <v>66.29000000000001</v>
       </c>
       <c r="F39" s="7" t="inlineStr"/>
     </row>
@@ -1450,10 +1450,10 @@
         <v>38.91</v>
       </c>
       <c r="D40" s="5" t="n">
-        <v>51.34</v>
+        <v>52.05</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>64.86</v>
+        <v>65.76000000000001</v>
       </c>
       <c r="F40" s="7" t="inlineStr"/>
     </row>
@@ -1470,10 +1470,10 @@
         <v>34.69</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>46.13</v>
+        <v>46.76</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>57.85</v>
+        <v>58.65</v>
       </c>
       <c r="F41" s="7" t="inlineStr"/>
     </row>
@@ -1490,10 +1490,10 @@
         <v>42.78</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>54.57</v>
+        <v>55.32</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>71.37</v>
+        <v>72.34999999999999</v>
       </c>
       <c r="F42" s="7" t="inlineStr"/>
     </row>
@@ -1510,10 +1510,10 @@
         <v>28.32</v>
       </c>
       <c r="D43" s="5" t="n">
-        <v>37.18</v>
+        <v>37.7</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>47.26</v>
+        <v>47.91</v>
       </c>
       <c r="F43" s="7" t="inlineStr"/>
     </row>
@@ -1530,10 +1530,10 @@
         <v>165.37</v>
       </c>
       <c r="D44" s="5" t="n">
-        <v>152.6</v>
+        <v>154.7</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>275.92</v>
+        <v>279.71</v>
       </c>
       <c r="F44" s="7" t="inlineStr"/>
     </row>
@@ -1550,10 +1550,10 @@
         <v>69.13</v>
       </c>
       <c r="D45" s="5" t="n">
-        <v>79.13</v>
+        <v>80.22</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>115.31</v>
+        <v>116.9</v>
       </c>
       <c r="F45" s="7" t="inlineStr"/>
     </row>
@@ -1570,10 +1570,10 @@
         <v>74.84999999999999</v>
       </c>
       <c r="D46" s="5" t="n">
-        <v>88.84999999999999</v>
+        <v>90.06999999999999</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>124.82</v>
+        <v>126.53</v>
       </c>
       <c r="F46" s="7" t="inlineStr"/>
     </row>
@@ -1590,10 +1590,10 @@
         <v>81.62</v>
       </c>
       <c r="D47" s="5" t="n">
-        <v>112.53</v>
+        <v>114.08</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>135.55</v>
+        <v>137.41</v>
       </c>
       <c r="F47" s="7" t="inlineStr"/>
     </row>
@@ -1610,10 +1610,10 @@
         <v>75.48999999999999</v>
       </c>
       <c r="D48" s="5" t="n">
-        <v>103.61</v>
+        <v>105.03</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>124.86</v>
+        <v>126.58</v>
       </c>
       <c r="F48" s="7" t="inlineStr"/>
     </row>
@@ -1630,10 +1630,10 @@
         <v>218.05</v>
       </c>
       <c r="D49" s="5" t="n">
-        <v>236.02</v>
+        <v>239.27</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>359.19</v>
+        <v>364.13</v>
       </c>
       <c r="F49" s="7" t="inlineStr"/>
     </row>
@@ -1650,10 +1650,10 @@
         <v>115.22</v>
       </c>
       <c r="D50" s="5" t="n">
-        <v>140.6</v>
+        <v>142.54</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>189.37</v>
+        <v>191.97</v>
       </c>
       <c r="F50" s="7" t="inlineStr"/>
     </row>
@@ -1670,10 +1670,10 @@
         <v>50.83</v>
       </c>
       <c r="D51" s="5" t="n">
-        <v>68.43000000000001</v>
+        <v>69.37</v>
       </c>
       <c r="E51" s="5" t="n">
-        <v>83.34999999999999</v>
+        <v>84.5</v>
       </c>
       <c r="F51" s="7" t="inlineStr"/>
     </row>
@@ -1690,10 +1690,10 @@
         <v>55.04</v>
       </c>
       <c r="D52" s="5" t="n">
-        <v>72.93000000000001</v>
+        <v>73.94</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>90.05</v>
+        <v>91.28</v>
       </c>
       <c r="F52" s="7" t="inlineStr"/>
     </row>
@@ -1710,10 +1710,10 @@
         <v>45.32</v>
       </c>
       <c r="D53" s="5" t="n">
-        <v>57.92</v>
+        <v>58.71</v>
       </c>
       <c r="E53" s="5" t="n">
-        <v>73.91</v>
+        <v>74.93000000000001</v>
       </c>
       <c r="F53" s="7" t="inlineStr"/>
     </row>
@@ -1730,10 +1730,10 @@
         <v>54.55</v>
       </c>
       <c r="D54" s="5" t="n">
-        <v>69.48</v>
+        <v>70.43000000000001</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>88.69</v>
+        <v>89.91</v>
       </c>
       <c r="F54" s="7" t="inlineStr"/>
     </row>
@@ -1750,10 +1750,10 @@
         <v>62.08</v>
       </c>
       <c r="D55" s="5" t="n">
-        <v>72.59999999999999</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="E55" s="5" t="n">
-        <v>100.63</v>
+        <v>102.01</v>
       </c>
       <c r="F55" s="7" t="inlineStr"/>
     </row>
@@ -1770,10 +1770,10 @@
         <v>55.11</v>
       </c>
       <c r="D56" s="5" t="n">
-        <v>65.15000000000001</v>
+        <v>66.04000000000001</v>
       </c>
       <c r="E56" s="5" t="n">
-        <v>88.93000000000001</v>
+        <v>90.16</v>
       </c>
       <c r="F56" s="7" t="inlineStr"/>
     </row>
@@ -1790,10 +1790,10 @@
         <v>52.11</v>
       </c>
       <c r="D57" s="5" t="n">
-        <v>59.25</v>
+        <v>60.07</v>
       </c>
       <c r="E57" s="5" t="n">
-        <v>83.72</v>
+        <v>84.87</v>
       </c>
       <c r="F57" s="7" t="inlineStr"/>
     </row>
@@ -1810,10 +1810,10 @@
         <v>84.56999999999999</v>
       </c>
       <c r="D58" s="5" t="n">
-        <v>83.40000000000001</v>
+        <v>84.54000000000001</v>
       </c>
       <c r="E58" s="5" t="n">
-        <v>135.27</v>
+        <v>137.13</v>
       </c>
       <c r="F58" s="7" t="inlineStr"/>
     </row>
@@ -1830,10 +1830,10 @@
         <v>50.14</v>
       </c>
       <c r="D59" s="5" t="n">
-        <v>63.45</v>
+        <v>64.31999999999999</v>
       </c>
       <c r="E59" s="5" t="n">
-        <v>79.81</v>
+        <v>80.91</v>
       </c>
       <c r="F59" s="7" t="inlineStr"/>
     </row>
@@ -1850,10 +1850,10 @@
         <v>64.59</v>
       </c>
       <c r="D60" s="5" t="n">
-        <v>85.59</v>
+        <v>86.77</v>
       </c>
       <c r="E60" s="5" t="n">
-        <v>102.32</v>
+        <v>103.73</v>
       </c>
       <c r="F60" s="7" t="inlineStr"/>
     </row>
@@ -1870,10 +1870,10 @@
         <v>52.09</v>
       </c>
       <c r="D61" s="5" t="n">
-        <v>66.28</v>
+        <v>67.19</v>
       </c>
       <c r="E61" s="5" t="n">
-        <v>82.13</v>
+        <v>83.26000000000001</v>
       </c>
       <c r="F61" s="7" t="inlineStr"/>
     </row>
@@ -1890,10 +1890,10 @@
         <v>60.12</v>
       </c>
       <c r="D62" s="5" t="n">
-        <v>67.59999999999999</v>
+        <v>68.53</v>
       </c>
       <c r="E62" s="5" t="n">
-        <v>94.42</v>
+        <v>95.72</v>
       </c>
       <c r="F62" s="7" t="inlineStr"/>
     </row>
@@ -1910,10 +1910,10 @@
         <v>50.92</v>
       </c>
       <c r="D63" s="5" t="n">
-        <v>64</v>
+        <v>64.88</v>
       </c>
       <c r="E63" s="5" t="n">
-        <v>79.66</v>
+        <v>80.76000000000001</v>
       </c>
       <c r="F63" s="7" t="inlineStr"/>
     </row>
@@ -1930,10 +1930,10 @@
         <v>47.77</v>
       </c>
       <c r="D64" s="5" t="n">
-        <v>57.07</v>
+        <v>57.86</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>74.45</v>
+        <v>75.47</v>
       </c>
       <c r="F64" s="7" t="inlineStr"/>
     </row>
@@ -1950,10 +1950,10 @@
         <v>51.76</v>
       </c>
       <c r="D65" s="5" t="n">
-        <v>61.42</v>
+        <v>62.27</v>
       </c>
       <c r="E65" s="5" t="n">
-        <v>80.76000000000001</v>
+        <v>81.87</v>
       </c>
       <c r="F65" s="7" t="inlineStr"/>
     </row>
@@ -1970,10 +1970,10 @@
         <v>45.33</v>
       </c>
       <c r="D66" s="5" t="n">
-        <v>53.98</v>
+        <v>54.72</v>
       </c>
       <c r="E66" s="5" t="n">
-        <v>70.8</v>
+        <v>71.77</v>
       </c>
       <c r="F66" s="7" t="inlineStr"/>
     </row>
@@ -1990,10 +1990,10 @@
         <v>27.82</v>
       </c>
       <c r="D67" s="5" t="n">
-        <v>35.17</v>
+        <v>35.65</v>
       </c>
       <c r="E67" s="5" t="n">
-        <v>43.5</v>
+        <v>44.1</v>
       </c>
       <c r="F67" s="7" t="inlineStr"/>
     </row>
@@ -2010,10 +2010,10 @@
         <v>248.2</v>
       </c>
       <c r="D68" s="5" t="n">
-        <v>196.22</v>
+        <v>198.92</v>
       </c>
       <c r="E68" s="5" t="n">
-        <v>387.94</v>
+        <v>393.28</v>
       </c>
       <c r="F68" s="7" t="inlineStr"/>
     </row>
@@ -2030,10 +2030,10 @@
         <v>44.74</v>
       </c>
       <c r="D69" s="5" t="n">
-        <v>52.19</v>
+        <v>52.9</v>
       </c>
       <c r="E69" s="5" t="n">
-        <v>69.90000000000001</v>
+        <v>70.87</v>
       </c>
       <c r="F69" s="7" t="inlineStr"/>
     </row>
@@ -2050,10 +2050,10 @@
         <v>32.56</v>
       </c>
       <c r="D70" s="5" t="n">
-        <v>39.47</v>
+        <v>40.01</v>
       </c>
       <c r="E70" s="5" t="n">
-        <v>50.86</v>
+        <v>51.55</v>
       </c>
       <c r="F70" s="7" t="inlineStr"/>
     </row>
@@ -2070,10 +2070,10 @@
         <v>49.27</v>
       </c>
       <c r="D71" s="5" t="n">
-        <v>58.16</v>
+        <v>58.96</v>
       </c>
       <c r="E71" s="5" t="n">
-        <v>76.83</v>
+        <v>77.88</v>
       </c>
       <c r="F71" s="7" t="inlineStr"/>
     </row>
@@ -2090,10 +2090,10 @@
         <v>37.87</v>
       </c>
       <c r="D72" s="5" t="n">
-        <v>48.96</v>
+        <v>49.63</v>
       </c>
       <c r="E72" s="5" t="n">
-        <v>58.95</v>
+        <v>59.76</v>
       </c>
       <c r="F72" s="7" t="inlineStr"/>
     </row>
@@ -2110,10 +2110,10 @@
         <v>37.13</v>
       </c>
       <c r="D73" s="5" t="n">
-        <v>46.73</v>
+        <v>47.38</v>
       </c>
       <c r="E73" s="5" t="n">
-        <v>57.71</v>
+        <v>58.5</v>
       </c>
       <c r="F73" s="7" t="inlineStr"/>
     </row>
@@ -2130,10 +2130,10 @@
         <v>32.55</v>
       </c>
       <c r="D74" s="5" t="n">
-        <v>41.58</v>
+        <v>42.15</v>
       </c>
       <c r="E74" s="5" t="n">
-        <v>50.43</v>
+        <v>51.12</v>
       </c>
       <c r="F74" s="7" t="inlineStr"/>
     </row>
@@ -2150,10 +2150,10 @@
         <v>28.02</v>
       </c>
       <c r="D75" s="5" t="n">
-        <v>34.66</v>
+        <v>35.13</v>
       </c>
       <c r="E75" s="5" t="n">
-        <v>43.27</v>
+        <v>43.87</v>
       </c>
       <c r="F75" s="7" t="inlineStr"/>
     </row>
@@ -2170,10 +2170,10 @@
         <v>27.43</v>
       </c>
       <c r="D76" s="5" t="n">
-        <v>35.32</v>
+        <v>35.8</v>
       </c>
       <c r="E76" s="5" t="n">
-        <v>42.23</v>
+        <v>42.81</v>
       </c>
       <c r="F76" s="7" t="inlineStr"/>
     </row>
@@ -2190,10 +2190,10 @@
         <v>31.55</v>
       </c>
       <c r="D77" s="5" t="n">
-        <v>39.28</v>
+        <v>39.82</v>
       </c>
       <c r="E77" s="5" t="n">
-        <v>48.49</v>
+        <v>49.15</v>
       </c>
       <c r="F77" s="7" t="inlineStr"/>
     </row>
@@ -2210,10 +2210,10 @@
         <v>44.98</v>
       </c>
       <c r="D78" s="5" t="n">
-        <v>49.75</v>
+        <v>50.44</v>
       </c>
       <c r="E78" s="5" t="n">
-        <v>69</v>
+        <v>69.95</v>
       </c>
       <c r="F78" s="7" t="inlineStr"/>
     </row>
@@ -2230,10 +2230,10 @@
         <v>29.49</v>
       </c>
       <c r="D79" s="5" t="n">
-        <v>36</v>
+        <v>36.5</v>
       </c>
       <c r="E79" s="5" t="n">
-        <v>45.16</v>
+        <v>45.78</v>
       </c>
       <c r="F79" s="7" t="inlineStr"/>
     </row>
@@ -2250,10 +2250,10 @@
         <v>114.74</v>
       </c>
       <c r="D80" s="5" t="n">
-        <v>93.05</v>
+        <v>94.33</v>
       </c>
       <c r="E80" s="5" t="n">
-        <v>175.17</v>
+        <v>177.58</v>
       </c>
       <c r="F80" s="7" t="inlineStr"/>
     </row>
@@ -2270,10 +2270,10 @@
         <v>124.09</v>
       </c>
       <c r="D81" s="5" t="n">
-        <v>103.35</v>
+        <v>104.78</v>
       </c>
       <c r="E81" s="5" t="n">
-        <v>188.86</v>
+        <v>191.45</v>
       </c>
       <c r="F81" s="7" t="inlineStr"/>
     </row>
@@ -2290,10 +2290,10 @@
         <v>27.11</v>
       </c>
       <c r="D82" s="5" t="n">
-        <v>34.68</v>
+        <v>35.16</v>
       </c>
       <c r="E82" s="5" t="n">
-        <v>41.13</v>
+        <v>41.7</v>
       </c>
       <c r="F82" s="7" t="inlineStr"/>
     </row>
@@ -2310,10 +2310,10 @@
         <v>131.25</v>
       </c>
       <c r="D83" s="5" t="n">
-        <v>108.36</v>
+        <v>109.85</v>
       </c>
       <c r="E83" s="5" t="n">
-        <v>198.74</v>
+        <v>201.47</v>
       </c>
       <c r="F83" s="7" t="inlineStr"/>
     </row>
@@ -2330,10 +2330,10 @@
         <v>34.97</v>
       </c>
       <c r="D84" s="5" t="n">
-        <v>46.07</v>
+        <v>46.71</v>
       </c>
       <c r="E84" s="5" t="n">
-        <v>52.84</v>
+        <v>53.57</v>
       </c>
       <c r="F84" s="7" t="inlineStr"/>
     </row>
@@ -2350,10 +2350,10 @@
         <v>36.19</v>
       </c>
       <c r="D85" s="5" t="n">
-        <v>47.35</v>
+        <v>48.01</v>
       </c>
       <c r="E85" s="5" t="n">
-        <v>54.58</v>
+        <v>55.33</v>
       </c>
       <c r="F85" s="7" t="inlineStr"/>
     </row>
@@ -2370,10 +2370,10 @@
         <v>30.36</v>
       </c>
       <c r="D86" s="5" t="n">
-        <v>40.09</v>
+        <v>40.65</v>
       </c>
       <c r="E86" s="5" t="n">
-        <v>45.68</v>
+        <v>46.3</v>
       </c>
       <c r="F86" s="7" t="inlineStr"/>
     </row>
@@ -2390,10 +2390,10 @@
         <v>30.73</v>
       </c>
       <c r="D87" s="5" t="n">
-        <v>40.6</v>
+        <v>41.16</v>
       </c>
       <c r="E87" s="5" t="n">
-        <v>46.12</v>
+        <v>46.76</v>
       </c>
       <c r="F87" s="7" t="inlineStr"/>
     </row>
@@ -2410,10 +2410,10 @@
         <v>24.89</v>
       </c>
       <c r="D88" s="5" t="n">
-        <v>33.12</v>
+        <v>33.58</v>
       </c>
       <c r="E88" s="5" t="n">
-        <v>37.27</v>
+        <v>37.78</v>
       </c>
       <c r="F88" s="7" t="inlineStr"/>
     </row>
@@ -2430,10 +2430,10 @@
         <v>24.65</v>
       </c>
       <c r="D89" s="5" t="n">
-        <v>31.13</v>
+        <v>31.56</v>
       </c>
       <c r="E89" s="5" t="n">
-        <v>36.86</v>
+        <v>37.37</v>
       </c>
       <c r="F89" s="7" t="inlineStr"/>
     </row>
@@ -2450,10 +2450,10 @@
         <v>21.04</v>
       </c>
       <c r="D90" s="5" t="n">
-        <v>27.51</v>
+        <v>27.89</v>
       </c>
       <c r="E90" s="5" t="n">
-        <v>31.42</v>
+        <v>31.85</v>
       </c>
       <c r="F90" s="7" t="inlineStr"/>
     </row>
@@ -2470,10 +2470,10 @@
         <v>18.96</v>
       </c>
       <c r="D91" s="5" t="n">
-        <v>24.64</v>
+        <v>24.98</v>
       </c>
       <c r="E91" s="5" t="n">
-        <v>28.28</v>
+        <v>28.67</v>
       </c>
       <c r="F91" s="7" t="inlineStr"/>
     </row>
@@ -2490,10 +2490,10 @@
         <v>66.16</v>
       </c>
       <c r="D92" s="5" t="n">
-        <v>60.94</v>
+        <v>61.78</v>
       </c>
       <c r="E92" s="5" t="n">
-        <v>98.17</v>
+        <v>99.52</v>
       </c>
       <c r="F92" s="7" t="inlineStr"/>
     </row>
@@ -2510,10 +2510,10 @@
         <v>59.69</v>
       </c>
       <c r="D93" s="5" t="n">
-        <v>59.73</v>
+        <v>60.55</v>
       </c>
       <c r="E93" s="5" t="n">
-        <v>88.12</v>
+        <v>89.33</v>
       </c>
       <c r="F93" s="7" t="inlineStr"/>
     </row>
@@ -2530,10 +2530,10 @@
         <v>28.62</v>
       </c>
       <c r="D94" s="5" t="n">
-        <v>36.66</v>
+        <v>37.17</v>
       </c>
       <c r="E94" s="5" t="n">
-        <v>42.04</v>
+        <v>42.62</v>
       </c>
       <c r="F94" s="7" t="inlineStr"/>
     </row>
@@ -2550,10 +2550,10 @@
         <v>28.26</v>
       </c>
       <c r="D95" s="5" t="n">
-        <v>37.49</v>
+        <v>38</v>
       </c>
       <c r="E95" s="5" t="n">
-        <v>41.38</v>
+        <v>41.95</v>
       </c>
       <c r="F95" s="7" t="inlineStr"/>
     </row>
@@ -2570,10 +2570,10 @@
         <v>40.58</v>
       </c>
       <c r="D96" s="5" t="n">
-        <v>50.15</v>
+        <v>50.84</v>
       </c>
       <c r="E96" s="5" t="n">
-        <v>59.24</v>
+        <v>60.06</v>
       </c>
       <c r="F96" s="7" t="inlineStr"/>
     </row>
@@ -2590,10 +2590,10 @@
         <v>33.89</v>
       </c>
       <c r="D97" s="5" t="n">
-        <v>40.63</v>
+        <v>41.19</v>
       </c>
       <c r="E97" s="5" t="n">
-        <v>49.32</v>
+        <v>50</v>
       </c>
       <c r="F97" s="7" t="inlineStr"/>
     </row>
@@ -2610,10 +2610,10 @@
         <v>37.84</v>
       </c>
       <c r="D98" s="5" t="n">
-        <v>42.83</v>
+        <v>43.42</v>
       </c>
       <c r="E98" s="5" t="n">
-        <v>54.96</v>
+        <v>55.72</v>
       </c>
       <c r="F98" s="7" t="inlineStr"/>
     </row>
@@ -2630,10 +2630,10 @@
         <v>35.44</v>
       </c>
       <c r="D99" s="5" t="n">
-        <v>43.42</v>
+        <v>44.01</v>
       </c>
       <c r="E99" s="5" t="n">
-        <v>51.38</v>
+        <v>52.08</v>
       </c>
       <c r="F99" s="7" t="inlineStr"/>
     </row>
@@ -2650,10 +2650,10 @@
         <v>31.61</v>
       </c>
       <c r="D100" s="5" t="n">
-        <v>39.03</v>
+        <v>39.57</v>
       </c>
       <c r="E100" s="5" t="n">
-        <v>45.73</v>
+        <v>46.36</v>
       </c>
       <c r="F100" s="7" t="inlineStr"/>
     </row>
@@ -2670,10 +2670,10 @@
         <v>29</v>
       </c>
       <c r="D101" s="5" t="n">
-        <v>34.16</v>
+        <v>34.63</v>
       </c>
       <c r="E101" s="5" t="n">
-        <v>41.96</v>
+        <v>42.53</v>
       </c>
       <c r="F101" s="7" t="inlineStr"/>
     </row>
@@ -2690,10 +2690,10 @@
         <v>30.77</v>
       </c>
       <c r="D102" s="5" t="n">
-        <v>38.46</v>
+        <v>38.98</v>
       </c>
       <c r="E102" s="5" t="n">
-        <v>44.52</v>
+        <v>45.13</v>
       </c>
       <c r="F102" s="7" t="inlineStr"/>
     </row>
@@ -2710,10 +2710,10 @@
         <v>25.62</v>
       </c>
       <c r="D103" s="5" t="n">
-        <v>32.09</v>
+        <v>32.53</v>
       </c>
       <c r="E103" s="5" t="n">
-        <v>37.07</v>
+        <v>37.58</v>
       </c>
       <c r="F103" s="7" t="inlineStr"/>
     </row>
@@ -2730,10 +2730,10 @@
         <v>29.13</v>
       </c>
       <c r="D104" s="5" t="n">
-        <v>34.76</v>
+        <v>35.24</v>
       </c>
       <c r="E104" s="5" t="n">
-        <v>42.14</v>
+        <v>42.72</v>
       </c>
       <c r="F104" s="7" t="inlineStr"/>
     </row>
@@ -2750,10 +2750,10 @@
         <v>30.01</v>
       </c>
       <c r="D105" s="5" t="n">
-        <v>37.38</v>
+        <v>37.9</v>
       </c>
       <c r="E105" s="5" t="n">
-        <v>43.4</v>
+        <v>44</v>
       </c>
       <c r="F105" s="7" t="inlineStr"/>
     </row>
@@ -2770,10 +2770,10 @@
         <v>27.89</v>
       </c>
       <c r="D106" s="5" t="n">
-        <v>34.27</v>
+        <v>34.74</v>
       </c>
       <c r="E106" s="5" t="n">
-        <v>40.33</v>
+        <v>40.88</v>
       </c>
       <c r="F106" s="7" t="inlineStr"/>
     </row>
@@ -2790,10 +2790,10 @@
         <v>36.3</v>
       </c>
       <c r="D107" s="5" t="n">
-        <v>46.2</v>
+        <v>46.84</v>
       </c>
       <c r="E107" s="5" t="n">
-        <v>52.4</v>
+        <v>53.12</v>
       </c>
       <c r="F107" s="7" t="inlineStr"/>
     </row>
@@ -2810,10 +2810,10 @@
         <v>30.09</v>
       </c>
       <c r="D108" s="5" t="n">
-        <v>38.3</v>
+        <v>38.83</v>
       </c>
       <c r="E108" s="5" t="n">
-        <v>43.36</v>
+        <v>43.96</v>
       </c>
       <c r="F108" s="7" t="inlineStr"/>
     </row>
@@ -2830,10 +2830,10 @@
         <v>42.66</v>
       </c>
       <c r="D109" s="5" t="n">
-        <v>52.86</v>
+        <v>53.59</v>
       </c>
       <c r="E109" s="5" t="n">
-        <v>61.37</v>
+        <v>62.21</v>
       </c>
       <c r="F109" s="7" t="inlineStr"/>
     </row>
@@ -2850,10 +2850,10 @@
         <v>90.05</v>
       </c>
       <c r="D110" s="9" t="n">
-        <v>105.19</v>
+        <v>106.64</v>
       </c>
       <c r="E110" s="9" t="n">
-        <v>128.95</v>
+        <v>130.72</v>
       </c>
       <c r="F110" s="10" t="inlineStr">
         <is>
@@ -2874,10 +2874,10 @@
         <v>58.79</v>
       </c>
       <c r="D111" s="9" t="n">
-        <v>79.48999999999999</v>
+        <v>80.58</v>
       </c>
       <c r="E111" s="9" t="n">
-        <v>83.81</v>
+        <v>84.95999999999999</v>
       </c>
       <c r="F111" s="10" t="inlineStr">
         <is>
@@ -2898,10 +2898,10 @@
         <v>60.96</v>
       </c>
       <c r="D112" s="9" t="n">
-        <v>75.90000000000001</v>
+        <v>76.94</v>
       </c>
       <c r="E112" s="9" t="n">
-        <v>86.51000000000001</v>
+        <v>87.7</v>
       </c>
       <c r="F112" s="10" t="inlineStr">
         <is>
@@ -2922,10 +2922,10 @@
         <v>55</v>
       </c>
       <c r="D113" s="9" t="n">
-        <v>72.7</v>
+        <v>73.7</v>
       </c>
       <c r="E113" s="9" t="n">
-        <v>77.98999999999999</v>
+        <v>79.06</v>
       </c>
       <c r="F113" s="10" t="inlineStr">
         <is>
@@ -2946,10 +2946,10 @@
         <v>108.73</v>
       </c>
       <c r="D114" s="9" t="n">
-        <v>109.34</v>
+        <v>110.85</v>
       </c>
       <c r="E114" s="9" t="n">
-        <v>154.04</v>
+        <v>156.16</v>
       </c>
       <c r="F114" s="10" t="inlineStr">
         <is>
@@ -2970,10 +2970,10 @@
         <v>58.92</v>
       </c>
       <c r="D115" s="9" t="n">
-        <v>73.86</v>
+        <v>74.88</v>
       </c>
       <c r="E115" s="9" t="n">
-        <v>83.40000000000001</v>
+        <v>84.55</v>
       </c>
       <c r="F115" s="10" t="inlineStr">
         <is>
@@ -2994,10 +2994,10 @@
         <v>65.31</v>
       </c>
       <c r="D116" s="9" t="n">
-        <v>76.73999999999999</v>
+        <v>77.79000000000001</v>
       </c>
       <c r="E116" s="9" t="n">
-        <v>92.34999999999999</v>
+        <v>93.62</v>
       </c>
       <c r="F116" s="10" t="inlineStr">
         <is>
@@ -3018,10 +3018,10 @@
         <v>59.78</v>
       </c>
       <c r="D117" s="9" t="n">
-        <v>75.69</v>
+        <v>76.73</v>
       </c>
       <c r="E117" s="9" t="n">
-        <v>84.43000000000001</v>
+        <v>85.59</v>
       </c>
       <c r="F117" s="10" t="inlineStr">
         <is>
@@ -3042,10 +3042,10 @@
         <v>60.03</v>
       </c>
       <c r="D118" s="9" t="n">
-        <v>73.8</v>
+        <v>74.81</v>
       </c>
       <c r="E118" s="9" t="n">
-        <v>84.69</v>
+        <v>85.84999999999999</v>
       </c>
       <c r="F118" s="10" t="inlineStr">
         <is>
@@ -3066,10 +3066,10 @@
         <v>53.46</v>
       </c>
       <c r="D119" s="9" t="n">
-        <v>70.48</v>
+        <v>71.45</v>
       </c>
       <c r="E119" s="9" t="n">
-        <v>75.31999999999999</v>
+        <v>76.36</v>
       </c>
       <c r="F119" s="10" t="inlineStr">
         <is>
@@ -3090,10 +3090,10 @@
         <v>61.01</v>
       </c>
       <c r="D120" s="9" t="n">
-        <v>77.19</v>
+        <v>78.25</v>
       </c>
       <c r="E120" s="9" t="n">
-        <v>85.84999999999999</v>
+        <v>87.03</v>
       </c>
       <c r="F120" s="10" t="inlineStr">
         <is>
@@ -3114,10 +3114,10 @@
         <v>70.51000000000001</v>
       </c>
       <c r="D121" s="9" t="n">
-        <v>85.59</v>
+        <v>86.77</v>
       </c>
       <c r="E121" s="9" t="n">
-        <v>99.09999999999999</v>
+        <v>100.46</v>
       </c>
       <c r="F121" s="10" t="inlineStr">
         <is>
@@ -3138,10 +3138,10 @@
         <v>62.4</v>
       </c>
       <c r="D122" s="9" t="n">
-        <v>81.68000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="E122" s="9" t="n">
-        <v>87.34</v>
+        <v>88.55</v>
       </c>
       <c r="F122" s="10" t="inlineStr">
         <is>
@@ -3162,10 +3162,10 @@
         <v>57.79</v>
       </c>
       <c r="D123" s="9" t="n">
-        <v>75.45</v>
+        <v>76.48999999999999</v>
       </c>
       <c r="E123" s="9" t="n">
-        <v>80.56999999999999</v>
+        <v>81.67</v>
       </c>
       <c r="F123" s="10" t="inlineStr">
         <is>
@@ -3186,10 +3186,10 @@
         <v>52.11</v>
       </c>
       <c r="D124" s="9" t="n">
-        <v>68.38</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="E124" s="9" t="n">
-        <v>72.36</v>
+        <v>73.34999999999999</v>
       </c>
       <c r="F124" s="10" t="inlineStr">
         <is>
@@ -3210,10 +3210,10 @@
         <v>51.91</v>
       </c>
       <c r="D125" s="9" t="n">
-        <v>68.53</v>
+        <v>69.47</v>
       </c>
       <c r="E125" s="9" t="n">
-        <v>71.91</v>
+        <v>72.89</v>
       </c>
       <c r="F125" s="10" t="inlineStr">
         <is>
@@ -3234,10 +3234,10 @@
         <v>49.47</v>
       </c>
       <c r="D126" s="9" t="n">
-        <v>64.62</v>
+        <v>65.51000000000001</v>
       </c>
       <c r="E126" s="9" t="n">
-        <v>68.36</v>
+        <v>69.3</v>
       </c>
       <c r="F126" s="10" t="inlineStr">
         <is>
@@ -3258,10 +3258,10 @@
         <v>57.51</v>
       </c>
       <c r="D127" s="9" t="n">
-        <v>69.38</v>
+        <v>70.34</v>
       </c>
       <c r="E127" s="9" t="n">
-        <v>79.28</v>
+        <v>80.37</v>
       </c>
       <c r="F127" s="10" t="inlineStr">
         <is>
@@ -3282,10 +3282,10 @@
         <v>105.62</v>
       </c>
       <c r="D128" s="9" t="n">
-        <v>99.65000000000001</v>
+        <v>101.03</v>
       </c>
       <c r="E128" s="9" t="n">
-        <v>145.32</v>
+        <v>147.32</v>
       </c>
       <c r="F128" s="10" t="inlineStr">
         <is>
@@ -3306,10 +3306,10 @@
         <v>51.64</v>
       </c>
       <c r="D129" s="9" t="n">
-        <v>67.63</v>
+        <v>68.56</v>
       </c>
       <c r="E129" s="9" t="n">
-        <v>70.91</v>
+        <v>71.89</v>
       </c>
       <c r="F129" s="10" t="inlineStr">
         <is>
@@ -3330,10 +3330,10 @@
         <v>50.99</v>
       </c>
       <c r="D130" s="9" t="n">
-        <v>62.99</v>
+        <v>63.85</v>
       </c>
       <c r="E130" s="9" t="n">
-        <v>69.88</v>
+        <v>70.84</v>
       </c>
       <c r="F130" s="10" t="inlineStr">
         <is>
@@ -3354,10 +3354,10 @@
         <v>46.48</v>
       </c>
       <c r="D131" s="9" t="n">
-        <v>59.91</v>
+        <v>60.74</v>
       </c>
       <c r="E131" s="9" t="n">
-        <v>63.59</v>
+        <v>64.47</v>
       </c>
       <c r="F131" s="10" t="inlineStr">
         <is>
@@ -3378,10 +3378,10 @@
         <v>53.42</v>
       </c>
       <c r="D132" s="9" t="n">
-        <v>65.84</v>
+        <v>66.73999999999999</v>
       </c>
       <c r="E132" s="9" t="n">
-        <v>72.97</v>
+        <v>73.97</v>
       </c>
       <c r="F132" s="10" t="inlineStr">
         <is>
@@ -3402,10 +3402,10 @@
         <v>53.9</v>
       </c>
       <c r="D133" s="9" t="n">
-        <v>67.05</v>
+        <v>67.97</v>
       </c>
       <c r="E133" s="9" t="n">
-        <v>73.5</v>
+        <v>74.51000000000001</v>
       </c>
       <c r="F133" s="10" t="inlineStr">
         <is>
@@ -3426,10 +3426,10 @@
         <v>43.69</v>
       </c>
       <c r="D134" s="5" t="n">
-        <v>52.55</v>
+        <v>53.27</v>
       </c>
       <c r="E134" s="5" t="n">
-        <v>59.49</v>
+        <v>60.31</v>
       </c>
       <c r="F134" s="7" t="inlineStr"/>
     </row>
@@ -3446,10 +3446,10 @@
         <v>40.67</v>
       </c>
       <c r="D135" s="5" t="n">
-        <v>46.93</v>
+        <v>47.57</v>
       </c>
       <c r="E135" s="5" t="n">
-        <v>55.3</v>
+        <v>56.06</v>
       </c>
       <c r="F135" s="7" t="inlineStr"/>
     </row>
@@ -3466,10 +3466,10 @@
         <v>42.07</v>
       </c>
       <c r="D136" s="5" t="n">
-        <v>49.24</v>
+        <v>49.91</v>
       </c>
       <c r="E136" s="5" t="n">
-        <v>57.13</v>
+        <v>57.91</v>
       </c>
       <c r="F136" s="7" t="inlineStr"/>
     </row>
@@ -3486,10 +3486,10 @@
         <v>30.63</v>
       </c>
       <c r="D137" s="5" t="n">
-        <v>36.08</v>
+        <v>36.58</v>
       </c>
       <c r="E137" s="5" t="n">
-        <v>41.57</v>
+        <v>42.14</v>
       </c>
       <c r="F137" s="7" t="inlineStr"/>
     </row>
@@ -3506,10 +3506,10 @@
         <v>34.46</v>
       </c>
       <c r="D138" s="5" t="n">
-        <v>38.73</v>
+        <v>39.26</v>
       </c>
       <c r="E138" s="5" t="n">
-        <v>46.73</v>
+        <v>47.38</v>
       </c>
       <c r="F138" s="7" t="inlineStr"/>
     </row>
@@ -3526,10 +3526,10 @@
         <v>31.31</v>
       </c>
       <c r="D139" s="5" t="n">
-        <v>35.97</v>
+        <v>36.46</v>
       </c>
       <c r="E139" s="5" t="n">
-        <v>42.43</v>
+        <v>43.02</v>
       </c>
       <c r="F139" s="7" t="inlineStr"/>
     </row>
@@ -3546,10 +3546,10 @@
         <v>33.61</v>
       </c>
       <c r="D140" s="5" t="n">
-        <v>35.35</v>
+        <v>35.84</v>
       </c>
       <c r="E140" s="5" t="n">
-        <v>45.52</v>
+        <v>46.15</v>
       </c>
       <c r="F140" s="7" t="inlineStr"/>
     </row>
@@ -3566,10 +3566,10 @@
         <v>35.21</v>
       </c>
       <c r="D141" s="5" t="n">
-        <v>37.94</v>
+        <v>38.46</v>
       </c>
       <c r="E141" s="5" t="n">
-        <v>47.66</v>
+        <v>48.32</v>
       </c>
       <c r="F141" s="7" t="inlineStr"/>
     </row>
@@ -3586,10 +3586,10 @@
         <v>31.79</v>
       </c>
       <c r="D142" s="5" t="n">
-        <v>34.91</v>
+        <v>35.39</v>
       </c>
       <c r="E142" s="5" t="n">
-        <v>43</v>
+        <v>43.6</v>
       </c>
       <c r="F142" s="7" t="inlineStr"/>
     </row>
@@ -3606,10 +3606,10 @@
         <v>35.26</v>
       </c>
       <c r="D143" s="5" t="n">
-        <v>39.02</v>
+        <v>39.55</v>
       </c>
       <c r="E143" s="5" t="n">
-        <v>47.58</v>
+        <v>48.24</v>
       </c>
       <c r="F143" s="7" t="inlineStr"/>
     </row>
@@ -3626,10 +3626,10 @@
         <v>38.41</v>
       </c>
       <c r="D144" s="5" t="n">
-        <v>40.19</v>
+        <v>40.74</v>
       </c>
       <c r="E144" s="5" t="n">
-        <v>51.71</v>
+        <v>52.42</v>
       </c>
       <c r="F144" s="7" t="inlineStr"/>
     </row>
@@ -3646,10 +3646,10 @@
         <v>41.52</v>
       </c>
       <c r="D145" s="5" t="n">
-        <v>46.22</v>
+        <v>46.85</v>
       </c>
       <c r="E145" s="5" t="n">
-        <v>55.77</v>
+        <v>56.53</v>
       </c>
       <c r="F145" s="7" t="inlineStr"/>
     </row>
@@ -3666,10 +3666,10 @@
         <v>42.82</v>
       </c>
       <c r="D146" s="5" t="n">
-        <v>46.61</v>
+        <v>47.26</v>
       </c>
       <c r="E146" s="5" t="n">
-        <v>57.44</v>
+        <v>58.23</v>
       </c>
       <c r="F146" s="7" t="inlineStr"/>
     </row>
@@ -3686,10 +3686,10 @@
         <v>42.1</v>
       </c>
       <c r="D147" s="5" t="n">
-        <v>46.94</v>
+        <v>47.59</v>
       </c>
       <c r="E147" s="5" t="n">
-        <v>56.4</v>
+        <v>57.18</v>
       </c>
       <c r="F147" s="7" t="inlineStr"/>
     </row>
@@ -3706,10 +3706,10 @@
         <v>50.84</v>
       </c>
       <c r="D148" s="5" t="n">
-        <v>59.61</v>
+        <v>60.43</v>
       </c>
       <c r="E148" s="5" t="n">
-        <v>68.02</v>
+        <v>68.95999999999999</v>
       </c>
       <c r="F148" s="7" t="inlineStr"/>
     </row>
@@ -3726,10 +3726,10 @@
         <v>45.47</v>
       </c>
       <c r="D149" s="5" t="n">
-        <v>47.61</v>
+        <v>48.26</v>
       </c>
       <c r="E149" s="5" t="n">
-        <v>60.76</v>
+        <v>61.59</v>
       </c>
       <c r="F149" s="7" t="inlineStr"/>
     </row>
@@ -3746,10 +3746,10 @@
         <v>45.23</v>
       </c>
       <c r="D150" s="5" t="n">
-        <v>46.6</v>
+        <v>47.24</v>
       </c>
       <c r="E150" s="5" t="n">
-        <v>60.36</v>
+        <v>61.19</v>
       </c>
       <c r="F150" s="7" t="inlineStr"/>
     </row>
@@ -3766,10 +3766,10 @@
         <v>62.67</v>
       </c>
       <c r="D151" s="5" t="n">
-        <v>63.99</v>
+        <v>64.87</v>
       </c>
       <c r="E151" s="5" t="n">
-        <v>83.53</v>
+        <v>84.68000000000001</v>
       </c>
       <c r="F151" s="7" t="inlineStr"/>
     </row>
@@ -3786,10 +3786,10 @@
         <v>72.90000000000001</v>
       </c>
       <c r="D152" s="5" t="n">
-        <v>62.62</v>
+        <v>63.48</v>
       </c>
       <c r="E152" s="5" t="n">
-        <v>97.23</v>
+        <v>98.56</v>
       </c>
       <c r="F152" s="7" t="inlineStr"/>
     </row>
@@ -3806,10 +3806,10 @@
         <v>44.52</v>
       </c>
       <c r="D153" s="5" t="n">
-        <v>47.27</v>
+        <v>47.92</v>
       </c>
       <c r="E153" s="5" t="n">
-        <v>59.42</v>
+        <v>60.23</v>
       </c>
       <c r="F153" s="7" t="inlineStr"/>
     </row>
@@ -3826,10 +3826,10 @@
         <v>59.65</v>
       </c>
       <c r="D154" s="5" t="n">
-        <v>61.28</v>
+        <v>62.13</v>
       </c>
       <c r="E154" s="5" t="n">
-        <v>79.66</v>
+        <v>80.76000000000001</v>
       </c>
       <c r="F154" s="7" t="inlineStr"/>
     </row>
@@ -3846,10 +3846,10 @@
         <v>61.49</v>
       </c>
       <c r="D155" s="5" t="n">
-        <v>61.18</v>
+        <v>62.02</v>
       </c>
       <c r="E155" s="5" t="n">
-        <v>82</v>
+        <v>83.13</v>
       </c>
       <c r="F155" s="7" t="inlineStr"/>
     </row>
@@ -3866,10 +3866,10 @@
         <v>76.45999999999999</v>
       </c>
       <c r="D156" s="5" t="n">
-        <v>72.22</v>
+        <v>73.22</v>
       </c>
       <c r="E156" s="5" t="n">
-        <v>101.81</v>
+        <v>103.21</v>
       </c>
       <c r="F156" s="7" t="inlineStr"/>
     </row>
@@ -3886,10 +3886,10 @@
         <v>118.54</v>
       </c>
       <c r="D157" s="5" t="n">
-        <v>123.35</v>
+        <v>125.05</v>
       </c>
       <c r="E157" s="5" t="n">
-        <v>157.61</v>
+        <v>159.78</v>
       </c>
       <c r="F157" s="7" t="inlineStr"/>
     </row>
@@ -3906,10 +3906,10 @@
         <v>86.77</v>
       </c>
       <c r="D158" s="5" t="n">
-        <v>85.75</v>
+        <v>86.93000000000001</v>
       </c>
       <c r="E158" s="5" t="n">
-        <v>115.1</v>
+        <v>116.69</v>
       </c>
       <c r="F158" s="7" t="inlineStr"/>
     </row>
@@ -3926,10 +3926,10 @@
         <v>55.76</v>
       </c>
       <c r="D159" s="5" t="n">
-        <v>57.22</v>
+        <v>58.01</v>
       </c>
       <c r="E159" s="5" t="n">
-        <v>73.79000000000001</v>
+        <v>74.81</v>
       </c>
       <c r="F159" s="7" t="inlineStr"/>
     </row>
@@ -3946,10 +3946,10 @@
         <v>48.5</v>
       </c>
       <c r="D160" s="5" t="n">
-        <v>54.16</v>
+        <v>54.91</v>
       </c>
       <c r="E160" s="5" t="n">
-        <v>64.04000000000001</v>
+        <v>64.92</v>
       </c>
       <c r="F160" s="7" t="inlineStr"/>
     </row>
@@ -3966,10 +3966,10 @@
         <v>41.02</v>
       </c>
       <c r="D161" s="5" t="n">
-        <v>43.73</v>
+        <v>44.33</v>
       </c>
       <c r="E161" s="5" t="n">
-        <v>54.07</v>
+        <v>54.81</v>
       </c>
       <c r="F161" s="7" t="inlineStr"/>
     </row>
@@ -3986,10 +3986,10 @@
         <v>46.93</v>
       </c>
       <c r="D162" s="5" t="n">
-        <v>47.46</v>
+        <v>48.11</v>
       </c>
       <c r="E162" s="5" t="n">
-        <v>61.75</v>
+        <v>62.6</v>
       </c>
       <c r="F162" s="7" t="inlineStr"/>
     </row>
@@ -4006,10 +4006,10 @@
         <v>37.59</v>
       </c>
       <c r="D163" s="5" t="n">
-        <v>39.27</v>
+        <v>39.81</v>
       </c>
       <c r="E163" s="5" t="n">
-        <v>49.37</v>
+        <v>50.05</v>
       </c>
       <c r="F163" s="7" t="inlineStr"/>
     </row>
@@ -4026,10 +4026,10 @@
         <v>81.03</v>
       </c>
       <c r="D164" s="5" t="n">
-        <v>81.36</v>
+        <v>82.48</v>
       </c>
       <c r="E164" s="5" t="n">
-        <v>106.27</v>
+        <v>107.73</v>
       </c>
       <c r="F164" s="7" t="inlineStr"/>
     </row>
@@ -4046,10 +4046,10 @@
         <v>114.18</v>
       </c>
       <c r="D165" s="5" t="n">
-        <v>112.68</v>
+        <v>114.23</v>
       </c>
       <c r="E165" s="5" t="n">
-        <v>149.51</v>
+        <v>151.57</v>
       </c>
       <c r="F165" s="7" t="inlineStr"/>
     </row>
@@ -4066,10 +4066,10 @@
         <v>112.64</v>
       </c>
       <c r="D166" s="5" t="n">
-        <v>118.49</v>
+        <v>120.12</v>
       </c>
       <c r="E166" s="5" t="n">
-        <v>147.27</v>
+        <v>149.3</v>
       </c>
       <c r="F166" s="7" t="inlineStr"/>
     </row>
@@ -4086,10 +4086,10 @@
         <v>123.35</v>
       </c>
       <c r="D167" s="5" t="n">
-        <v>141.37</v>
+        <v>143.32</v>
       </c>
       <c r="E167" s="5" t="n">
-        <v>161.17</v>
+        <v>163.38</v>
       </c>
       <c r="F167" s="7" t="inlineStr"/>
     </row>
@@ -4106,10 +4106,10 @@
         <v>123.09</v>
       </c>
       <c r="D168" s="5" t="n">
-        <v>140.95</v>
+        <v>142.89</v>
       </c>
       <c r="E168" s="5" t="n">
-        <v>160.72</v>
+        <v>162.93</v>
       </c>
       <c r="F168" s="7" t="inlineStr"/>
     </row>
@@ -4126,10 +4126,10 @@
         <v>105</v>
       </c>
       <c r="D169" s="5" t="n">
-        <v>128.53</v>
+        <v>130.3</v>
       </c>
       <c r="E169" s="5" t="n">
-        <v>137.01</v>
+        <v>138.9</v>
       </c>
       <c r="F169" s="7" t="inlineStr"/>
     </row>
@@ -4146,10 +4146,10 @@
         <v>131.48</v>
       </c>
       <c r="D170" s="5" t="n">
-        <v>152.86</v>
+        <v>154.96</v>
       </c>
       <c r="E170" s="5" t="n">
-        <v>171.22</v>
+        <v>173.57</v>
       </c>
       <c r="F170" s="7" t="inlineStr"/>
     </row>
@@ -4166,10 +4166,10 @@
         <v>119.74</v>
       </c>
       <c r="D171" s="5" t="n">
-        <v>133.3</v>
+        <v>135.13</v>
       </c>
       <c r="E171" s="5" t="n">
-        <v>155.61</v>
+        <v>157.75</v>
       </c>
       <c r="F171" s="7" t="inlineStr"/>
     </row>
@@ -4186,10 +4186,10 @@
         <v>89.62</v>
       </c>
       <c r="D172" s="5" t="n">
-        <v>103.02</v>
+        <v>104.43</v>
       </c>
       <c r="E172" s="5" t="n">
-        <v>116.23</v>
+        <v>117.83</v>
       </c>
       <c r="F172" s="7" t="inlineStr"/>
     </row>
@@ -4206,10 +4206,10 @@
         <v>82.48</v>
       </c>
       <c r="D173" s="5" t="n">
-        <v>94.87</v>
+        <v>96.17</v>
       </c>
       <c r="E173" s="5" t="n">
-        <v>106.73</v>
+        <v>108.2</v>
       </c>
       <c r="F173" s="7" t="inlineStr"/>
     </row>
@@ -4226,10 +4226,10 @@
         <v>112.43</v>
       </c>
       <c r="D174" s="5" t="n">
-        <v>123.36</v>
+        <v>125.06</v>
       </c>
       <c r="E174" s="5" t="n">
-        <v>145.17</v>
+        <v>147.16</v>
       </c>
       <c r="F174" s="7" t="inlineStr"/>
     </row>
@@ -4246,10 +4246,10 @@
         <v>97.75</v>
       </c>
       <c r="D175" s="5" t="n">
-        <v>109.31</v>
+        <v>110.82</v>
       </c>
       <c r="E175" s="5" t="n">
-        <v>125.93</v>
+        <v>127.66</v>
       </c>
       <c r="F175" s="7" t="inlineStr"/>
     </row>
@@ -4266,10 +4266,10 @@
         <v>183</v>
       </c>
       <c r="D176" s="5" t="n">
-        <v>171.71</v>
+        <v>174.07</v>
       </c>
       <c r="E176" s="5" t="n">
-        <v>235.42</v>
+        <v>238.65</v>
       </c>
       <c r="F176" s="7" t="inlineStr"/>
     </row>
@@ -4286,10 +4286,10 @@
         <v>124.33</v>
       </c>
       <c r="D177" s="5" t="n">
-        <v>125.15</v>
+        <v>126.88</v>
       </c>
       <c r="E177" s="5" t="n">
-        <v>159.71</v>
+        <v>161.91</v>
       </c>
       <c r="F177" s="7" t="inlineStr"/>
     </row>
@@ -4306,10 +4306,10 @@
         <v>82.25</v>
       </c>
       <c r="D178" s="5" t="n">
-        <v>97.5</v>
+        <v>98.84</v>
       </c>
       <c r="E178" s="5" t="n">
-        <v>105.5</v>
+        <v>106.95</v>
       </c>
       <c r="F178" s="7" t="inlineStr"/>
     </row>
@@ -4326,10 +4326,10 @@
         <v>87.09</v>
       </c>
       <c r="D179" s="5" t="n">
-        <v>94.86</v>
+        <v>96.16</v>
       </c>
       <c r="E179" s="5" t="n">
-        <v>111.58</v>
+        <v>113.11</v>
       </c>
       <c r="F179" s="7" t="inlineStr"/>
     </row>
@@ -4346,10 +4346,10 @@
         <v>95.98</v>
       </c>
       <c r="D180" s="5" t="n">
-        <v>102.1</v>
+        <v>103.51</v>
       </c>
       <c r="E180" s="5" t="n">
-        <v>122.82</v>
+        <v>124.51</v>
       </c>
       <c r="F180" s="7" t="inlineStr"/>
     </row>
@@ -4366,10 +4366,10 @@
         <v>112.11</v>
       </c>
       <c r="D181" s="5" t="n">
-        <v>119.79</v>
+        <v>121.43</v>
       </c>
       <c r="E181" s="5" t="n">
-        <v>143.29</v>
+        <v>145.26</v>
       </c>
       <c r="F181" s="7" t="inlineStr"/>
     </row>
@@ -4386,10 +4386,10 @@
         <v>88.33</v>
       </c>
       <c r="D182" s="5" t="n">
-        <v>89.47</v>
+        <v>90.7</v>
       </c>
       <c r="E182" s="5" t="n">
-        <v>112.73</v>
+        <v>114.28</v>
       </c>
       <c r="F182" s="7" t="inlineStr"/>
     </row>
@@ -4406,10 +4406,10 @@
         <v>102.2</v>
       </c>
       <c r="D183" s="5" t="n">
-        <v>100.9</v>
+        <v>102.29</v>
       </c>
       <c r="E183" s="5" t="n">
-        <v>130.25</v>
+        <v>132.04</v>
       </c>
       <c r="F183" s="7" t="inlineStr"/>
     </row>
@@ -4426,10 +4426,10 @@
         <v>108.02</v>
       </c>
       <c r="D184" s="5" t="n">
-        <v>118.16</v>
+        <v>119.79</v>
       </c>
       <c r="E184" s="5" t="n">
-        <v>137.47</v>
+        <v>139.36</v>
       </c>
       <c r="F184" s="7" t="inlineStr"/>
     </row>
@@ -4446,10 +4446,10 @@
         <v>109.7</v>
       </c>
       <c r="D185" s="5" t="n">
-        <v>126.82</v>
+        <v>128.57</v>
       </c>
       <c r="E185" s="5" t="n">
-        <v>139.36</v>
+        <v>141.28</v>
       </c>
       <c r="F185" s="7" t="inlineStr"/>
     </row>
@@ -4466,10 +4466,10 @@
         <v>105.48</v>
       </c>
       <c r="D186" s="5" t="n">
-        <v>124.08</v>
+        <v>125.79</v>
       </c>
       <c r="E186" s="5" t="n">
-        <v>133.77</v>
+        <v>135.61</v>
       </c>
       <c r="F186" s="7" t="inlineStr"/>
     </row>
@@ -4486,10 +4486,10 @@
         <v>113.92</v>
       </c>
       <c r="D187" s="5" t="n">
-        <v>116.21</v>
+        <v>117.81</v>
       </c>
       <c r="E187" s="5" t="n">
-        <v>144.23</v>
+        <v>146.21</v>
       </c>
       <c r="F187" s="7" t="inlineStr"/>
     </row>
@@ -4506,10 +4506,10 @@
         <v>423.33</v>
       </c>
       <c r="D188" s="5" t="n">
-        <v>316.94</v>
+        <v>321.3</v>
       </c>
       <c r="E188" s="5" t="n">
-        <v>535.97</v>
+        <v>543.34</v>
       </c>
       <c r="F188" s="7" t="inlineStr"/>
     </row>
@@ -4526,10 +4526,10 @@
         <v>120.86</v>
       </c>
       <c r="D189" s="5" t="n">
-        <v>140.74</v>
+        <v>142.68</v>
       </c>
       <c r="E189" s="5" t="n">
-        <v>153.02</v>
+        <v>155.13</v>
       </c>
       <c r="F189" s="7" t="inlineStr"/>
     </row>
@@ -4546,10 +4546,10 @@
         <v>177.81</v>
       </c>
       <c r="D190" s="5" t="n">
-        <v>166.01</v>
+        <v>168.29</v>
       </c>
       <c r="E190" s="5" t="n">
-        <v>225.14</v>
+        <v>228.24</v>
       </c>
       <c r="F190" s="7" t="inlineStr"/>
     </row>
@@ -4566,10 +4566,10 @@
         <v>106.79</v>
       </c>
       <c r="D191" s="5" t="n">
-        <v>124.4</v>
+        <v>126.11</v>
       </c>
       <c r="E191" s="5" t="n">
-        <v>134.95</v>
+        <v>136.81</v>
       </c>
       <c r="F191" s="7" t="inlineStr"/>
     </row>
@@ -4586,10 +4586,10 @@
         <v>104.25</v>
       </c>
       <c r="D192" s="5" t="n">
-        <v>115.9</v>
+        <v>117.5</v>
       </c>
       <c r="E192" s="5" t="n">
-        <v>131.48</v>
+        <v>133.29</v>
       </c>
       <c r="F192" s="7" t="inlineStr"/>
     </row>
@@ -4606,10 +4606,10 @@
         <v>122.01</v>
       </c>
       <c r="D193" s="5" t="n">
-        <v>128.15</v>
+        <v>129.91</v>
       </c>
       <c r="E193" s="5" t="n">
-        <v>153.58</v>
+        <v>155.69</v>
       </c>
       <c r="F193" s="7" t="inlineStr"/>
     </row>
@@ -4626,10 +4626,10 @@
         <v>105.02</v>
       </c>
       <c r="D194" s="5" t="n">
-        <v>107.95</v>
+        <v>109.43</v>
       </c>
       <c r="E194" s="5" t="n">
-        <v>131.94</v>
+        <v>133.76</v>
       </c>
       <c r="F194" s="7" t="inlineStr"/>
     </row>
@@ -4646,10 +4646,10 @@
         <v>130.29</v>
       </c>
       <c r="D195" s="5" t="n">
-        <v>131.61</v>
+        <v>133.42</v>
       </c>
       <c r="E195" s="5" t="n">
-        <v>163.38</v>
+        <v>165.63</v>
       </c>
       <c r="F195" s="7" t="inlineStr"/>
     </row>
@@ -4666,10 +4666,10 @@
         <v>121.93</v>
       </c>
       <c r="D196" s="5" t="n">
-        <v>131.12</v>
+        <v>132.93</v>
       </c>
       <c r="E196" s="5" t="n">
-        <v>152.61</v>
+        <v>154.71</v>
       </c>
       <c r="F196" s="7" t="inlineStr"/>
     </row>
@@ -4686,10 +4686,10 @@
         <v>113.03</v>
       </c>
       <c r="D197" s="5" t="n">
-        <v>125.75</v>
+        <v>127.48</v>
       </c>
       <c r="E197" s="5" t="n">
-        <v>141.15</v>
+        <v>143.09</v>
       </c>
       <c r="F197" s="7" t="inlineStr"/>
     </row>
@@ -4706,10 +4706,10 @@
         <v>69.79000000000001</v>
       </c>
       <c r="D198" s="5" t="n">
-        <v>84.7</v>
+        <v>85.87</v>
       </c>
       <c r="E198" s="5" t="n">
-        <v>86.95999999999999</v>
+        <v>88.15000000000001</v>
       </c>
       <c r="F198" s="7" t="inlineStr"/>
     </row>
@@ -4726,10 +4726,10 @@
         <v>77.45999999999999</v>
       </c>
       <c r="D199" s="5" t="n">
-        <v>76.31999999999999</v>
+        <v>77.37</v>
       </c>
       <c r="E199" s="5" t="n">
-        <v>96.29000000000001</v>
+        <v>97.62</v>
       </c>
       <c r="F199" s="7" t="inlineStr"/>
     </row>
@@ -4746,10 +4746,10 @@
         <v>255.88</v>
       </c>
       <c r="D200" s="5" t="n">
-        <v>177.48</v>
+        <v>179.93</v>
       </c>
       <c r="E200" s="5" t="n">
-        <v>317.7</v>
+        <v>322.07</v>
       </c>
       <c r="F200" s="7" t="inlineStr"/>
     </row>
@@ -4766,10 +4766,10 @@
         <v>55.83</v>
       </c>
       <c r="D201" s="5" t="n">
-        <v>59.91</v>
+        <v>60.73</v>
       </c>
       <c r="E201" s="5" t="n">
-        <v>69.23</v>
+        <v>70.18000000000001</v>
       </c>
       <c r="F201" s="7" t="inlineStr"/>
     </row>
@@ -4786,10 +4786,10 @@
         <v>50.47</v>
       </c>
       <c r="D202" s="5" t="n">
-        <v>53.63</v>
+        <v>54.37</v>
       </c>
       <c r="E202" s="5" t="n">
-        <v>62.51</v>
+        <v>63.37</v>
       </c>
       <c r="F202" s="7" t="inlineStr"/>
     </row>
@@ -4806,10 +4806,10 @@
         <v>41.9</v>
       </c>
       <c r="D203" s="5" t="n">
-        <v>43.42</v>
+        <v>44.01</v>
       </c>
       <c r="E203" s="5" t="n">
-        <v>52.23</v>
+        <v>52.95</v>
       </c>
       <c r="F203" s="7" t="inlineStr"/>
     </row>
@@ -4826,10 +4826,10 @@
         <v>47.04</v>
       </c>
       <c r="D204" s="5" t="n">
-        <v>48.04</v>
+        <v>48.7</v>
       </c>
       <c r="E204" s="5" t="n">
-        <v>59.02</v>
+        <v>59.83</v>
       </c>
       <c r="F204" s="7" t="inlineStr"/>
     </row>
@@ -4846,10 +4846,10 @@
         <v>62.91</v>
       </c>
       <c r="D205" s="5" t="n">
-        <v>61.45</v>
+        <v>62.3</v>
       </c>
       <c r="E205" s="5" t="n">
-        <v>79.45</v>
+        <v>80.54000000000001</v>
       </c>
       <c r="F205" s="7" t="inlineStr"/>
     </row>
@@ -4866,10 +4866,10 @@
         <v>75.01000000000001</v>
       </c>
       <c r="D206" s="5" t="n">
-        <v>79.90000000000001</v>
+        <v>81</v>
       </c>
       <c r="E206" s="5" t="n">
-        <v>94.23999999999999</v>
+        <v>95.54000000000001</v>
       </c>
       <c r="F206" s="7" t="inlineStr"/>
     </row>
@@ -4886,10 +4886,10 @@
         <v>66.40000000000001</v>
       </c>
       <c r="D207" s="5" t="n">
-        <v>67.12</v>
+        <v>68.04000000000001</v>
       </c>
       <c r="E207" s="5" t="n">
-        <v>83</v>
+        <v>84.14</v>
       </c>
       <c r="F207" s="7" t="inlineStr"/>
     </row>
@@ -4906,10 +4906,10 @@
         <v>39.08</v>
       </c>
       <c r="D208" s="5" t="n">
-        <v>43.09</v>
+        <v>43.68</v>
       </c>
       <c r="E208" s="5" t="n">
-        <v>48.6</v>
+        <v>49.27</v>
       </c>
       <c r="F208" s="7" t="inlineStr"/>
     </row>
@@ -4926,10 +4926,10 @@
         <v>55.4</v>
       </c>
       <c r="D209" s="5" t="n">
-        <v>55.53</v>
+        <v>56.3</v>
       </c>
       <c r="E209" s="5" t="n">
-        <v>68.69</v>
+        <v>69.63</v>
       </c>
       <c r="F209" s="7" t="inlineStr"/>
     </row>
@@ -4946,10 +4946,10 @@
         <v>49.88</v>
       </c>
       <c r="D210" s="5" t="n">
-        <v>54.48</v>
+        <v>55.23</v>
       </c>
       <c r="E210" s="5" t="n">
-        <v>61.66</v>
+        <v>62.51</v>
       </c>
       <c r="F210" s="7" t="inlineStr"/>
     </row>
@@ -4966,10 +4966,10 @@
         <v>23.5</v>
       </c>
       <c r="D211" s="5" t="n">
-        <v>29.32</v>
+        <v>29.72</v>
       </c>
       <c r="E211" s="5" t="n">
-        <v>28.96</v>
+        <v>29.36</v>
       </c>
       <c r="F211" s="7" t="inlineStr"/>
     </row>
@@ -4986,10 +4986,10 @@
         <v>20.68</v>
       </c>
       <c r="D212" s="5" t="n">
-        <v>28.07</v>
+        <v>28.46</v>
       </c>
       <c r="E212" s="5" t="n">
-        <v>25.44</v>
+        <v>25.79</v>
       </c>
       <c r="F212" s="7" t="inlineStr"/>
     </row>
@@ -5006,10 +5006,10 @@
         <v>24.89</v>
       </c>
       <c r="D213" s="5" t="n">
-        <v>26.83</v>
+        <v>27.19</v>
       </c>
       <c r="E213" s="5" t="n">
-        <v>30.56</v>
+        <v>30.98</v>
       </c>
       <c r="F213" s="7" t="inlineStr"/>
     </row>
@@ -5026,10 +5026,10 @@
         <v>32.84</v>
       </c>
       <c r="D214" s="5" t="n">
-        <v>37.2</v>
+        <v>37.71</v>
       </c>
       <c r="E214" s="5" t="n">
-        <v>40.24</v>
+        <v>40.79</v>
       </c>
       <c r="F214" s="7" t="inlineStr"/>
     </row>
@@ -5046,10 +5046,10 @@
         <v>62.46</v>
       </c>
       <c r="D215" s="5" t="n">
-        <v>60.47</v>
+        <v>61.3</v>
       </c>
       <c r="E215" s="5" t="n">
-        <v>76.34999999999999</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="F215" s="7" t="inlineStr"/>
     </row>
@@ -5066,10 +5066,10 @@
         <v>114.98</v>
       </c>
       <c r="D216" s="5" t="n">
-        <v>88.81999999999999</v>
+        <v>90.04000000000001</v>
       </c>
       <c r="E216" s="5" t="n">
-        <v>140.21</v>
+        <v>142.14</v>
       </c>
       <c r="F216" s="7" t="inlineStr"/>
     </row>
@@ -5086,10 +5086,10 @@
         <v>107.95</v>
       </c>
       <c r="D217" s="5" t="n">
-        <v>106.95</v>
+        <v>108.42</v>
       </c>
       <c r="E217" s="5" t="n">
-        <v>131.31</v>
+        <v>133.12</v>
       </c>
       <c r="F217" s="7" t="inlineStr"/>
     </row>
@@ -5106,10 +5106,10 @@
         <v>126.87</v>
       </c>
       <c r="D218" s="5" t="n">
-        <v>111.26</v>
+        <v>112.79</v>
       </c>
       <c r="E218" s="5" t="n">
-        <v>153.89</v>
+        <v>156.01</v>
       </c>
       <c r="F218" s="7" t="inlineStr"/>
     </row>
@@ -5126,10 +5126,10 @@
         <v>55.18</v>
       </c>
       <c r="D219" s="5" t="n">
-        <v>56.85</v>
+        <v>57.63</v>
       </c>
       <c r="E219" s="5" t="n">
-        <v>66.75</v>
+        <v>67.66</v>
       </c>
       <c r="F219" s="7" t="inlineStr"/>
     </row>
@@ -5146,10 +5146,10 @@
         <v>33.73</v>
       </c>
       <c r="D220" s="5" t="n">
-        <v>33.44</v>
+        <v>33.9</v>
       </c>
       <c r="E220" s="5" t="n">
-        <v>40.69</v>
+        <v>41.24</v>
       </c>
       <c r="F220" s="7" t="inlineStr"/>
     </row>
@@ -5166,10 +5166,10 @@
         <v>15.09</v>
       </c>
       <c r="D221" s="5" t="n">
-        <v>22.17</v>
+        <v>22.48</v>
       </c>
       <c r="E221" s="5" t="n">
-        <v>18.12</v>
+        <v>18.37</v>
       </c>
       <c r="F221" s="7" t="inlineStr"/>
     </row>
@@ -5186,10 +5186,10 @@
         <v>40.78</v>
       </c>
       <c r="D222" s="5" t="n">
-        <v>41.89</v>
+        <v>42.46</v>
       </c>
       <c r="E222" s="5" t="n">
-        <v>48.77</v>
+        <v>49.45</v>
       </c>
       <c r="F222" s="7" t="inlineStr"/>
     </row>
@@ -5206,10 +5206,10 @@
         <v>30.8</v>
       </c>
       <c r="D223" s="5" t="n">
-        <v>38.39</v>
+        <v>38.91</v>
       </c>
       <c r="E223" s="5" t="n">
-        <v>36.68</v>
+        <v>37.19</v>
       </c>
       <c r="F223" s="7" t="inlineStr"/>
     </row>
@@ -5226,10 +5226,10 @@
         <v>75.01000000000001</v>
       </c>
       <c r="D224" s="5" t="n">
-        <v>71.92</v>
+        <v>72.91</v>
       </c>
       <c r="E224" s="5" t="n">
-        <v>88.7</v>
+        <v>89.92</v>
       </c>
       <c r="F224" s="7" t="inlineStr"/>
     </row>
@@ -5246,10 +5246,10 @@
         <v>48.54</v>
       </c>
       <c r="D225" s="5" t="n">
-        <v>63.6</v>
+        <v>64.48</v>
       </c>
       <c r="E225" s="5" t="n">
-        <v>56.99</v>
+        <v>57.78</v>
       </c>
       <c r="F225" s="7" t="inlineStr"/>
     </row>
@@ -5266,10 +5266,10 @@
         <v>56.47</v>
       </c>
       <c r="D226" s="5" t="n">
-        <v>63.86</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="E226" s="5" t="n">
-        <v>65.83</v>
+        <v>66.73999999999999</v>
       </c>
       <c r="F226" s="7" t="inlineStr"/>
     </row>
@@ -5286,10 +5286,10 @@
         <v>168.15</v>
       </c>
       <c r="D227" s="5" t="n">
-        <v>164</v>
+        <v>166.25</v>
       </c>
       <c r="E227" s="5" t="n">
-        <v>194.87</v>
+        <v>197.55</v>
       </c>
       <c r="F227" s="7" t="inlineStr"/>
     </row>
@@ -5306,10 +5306,10 @@
         <v>264.24</v>
       </c>
       <c r="D228" s="5" t="n">
-        <v>269.17</v>
+        <v>272.88</v>
       </c>
       <c r="E228" s="5" t="n">
-        <v>304.43</v>
+        <v>308.62</v>
       </c>
       <c r="F228" s="7" t="inlineStr"/>
     </row>
@@ -5326,10 +5326,10 @@
         <v>375.96</v>
       </c>
       <c r="D229" s="5" t="n">
-        <v>339.58</v>
+        <v>344.25</v>
       </c>
       <c r="E229" s="5" t="n">
-        <v>430.6</v>
+        <v>436.52</v>
       </c>
       <c r="F229" s="7" t="inlineStr"/>
     </row>
@@ -5346,10 +5346,10 @@
         <v>432</v>
       </c>
       <c r="D230" s="5" t="n">
-        <v>387.43</v>
+        <v>392.76</v>
       </c>
       <c r="E230" s="5" t="n">
-        <v>491.77</v>
+        <v>498.54</v>
       </c>
       <c r="F230" s="7" t="inlineStr"/>
     </row>
@@ -5366,10 +5366,10 @@
         <v>137.33</v>
       </c>
       <c r="D231" s="5" t="n">
-        <v>136.92</v>
+        <v>138.8</v>
       </c>
       <c r="E231" s="5" t="n">
-        <v>155.38</v>
+        <v>157.52</v>
       </c>
       <c r="F231" s="7" t="inlineStr"/>
     </row>
@@ -5386,10 +5386,10 @@
         <v>130.9</v>
       </c>
       <c r="D232" s="5" t="n">
-        <v>125.7</v>
+        <v>127.43</v>
       </c>
       <c r="E232" s="5" t="n">
-        <v>147.22</v>
+        <v>149.24</v>
       </c>
       <c r="F232" s="7" t="inlineStr"/>
     </row>
@@ -5406,10 +5406,10 @@
         <v>97.36</v>
       </c>
       <c r="D233" s="5" t="n">
-        <v>110.55</v>
+        <v>112.07</v>
       </c>
       <c r="E233" s="5" t="n">
-        <v>108.83</v>
+        <v>110.32</v>
       </c>
       <c r="F233" s="7" t="inlineStr"/>
     </row>
@@ -5426,10 +5426,10 @@
         <v>58.3</v>
       </c>
       <c r="D234" s="5" t="n">
-        <v>65.14</v>
+        <v>66.03</v>
       </c>
       <c r="E234" s="5" t="n">
-        <v>64.77</v>
+        <v>65.66</v>
       </c>
       <c r="F234" s="7" t="inlineStr"/>
     </row>
@@ -5446,10 +5446,10 @@
         <v>11.57</v>
       </c>
       <c r="D235" s="5" t="n">
-        <v>34.54</v>
+        <v>35.02</v>
       </c>
       <c r="E235" s="5" t="n">
-        <v>12.78</v>
+        <v>12.95</v>
       </c>
       <c r="F235" s="7" t="inlineStr"/>
     </row>
@@ -5466,10 +5466,10 @@
         <v>32.05</v>
       </c>
       <c r="D236" s="5" t="n">
-        <v>52.86</v>
+        <v>53.59</v>
       </c>
       <c r="E236" s="5" t="n">
-        <v>35.23</v>
+        <v>35.72</v>
       </c>
       <c r="F236" s="7" t="inlineStr"/>
     </row>
@@ -5486,10 +5486,10 @@
         <v>55.29</v>
       </c>
       <c r="D237" s="5" t="n">
-        <v>63.48</v>
+        <v>64.36</v>
       </c>
       <c r="E237" s="5" t="n">
-        <v>60.51</v>
+        <v>61.34</v>
       </c>
       <c r="F237" s="7" t="inlineStr"/>
     </row>
@@ -5506,10 +5506,10 @@
         <v>54.59</v>
       </c>
       <c r="D238" s="5" t="n">
-        <v>67.56999999999999</v>
+        <v>68.5</v>
       </c>
       <c r="E238" s="5" t="n">
-        <v>59.48</v>
+        <v>60.29</v>
       </c>
       <c r="F238" s="7" t="inlineStr"/>
     </row>
@@ -5526,10 +5526,10 @@
         <v>86.78</v>
       </c>
       <c r="D239" s="5" t="n">
-        <v>90.84</v>
+        <v>92.09</v>
       </c>
       <c r="E239" s="5" t="n">
-        <v>94.28</v>
+        <v>95.56999999999999</v>
       </c>
       <c r="F239" s="7" t="inlineStr"/>
     </row>
@@ -5546,10 +5546,10 @@
         <v>145.97</v>
       </c>
       <c r="D240" s="5" t="n">
-        <v>137.74</v>
+        <v>139.64</v>
       </c>
       <c r="E240" s="5" t="n">
-        <v>158.13</v>
+        <v>160.3</v>
       </c>
       <c r="F240" s="7" t="inlineStr"/>
     </row>
@@ -5566,10 +5566,10 @@
         <v>85.79000000000001</v>
       </c>
       <c r="D241" s="5" t="n">
-        <v>58.9</v>
+        <v>59.71</v>
       </c>
       <c r="E241" s="5" t="n">
-        <v>92.67</v>
+        <v>93.95</v>
       </c>
       <c r="F241" s="7" t="inlineStr"/>
     </row>
@@ -5586,10 +5586,10 @@
         <v>76.38</v>
       </c>
       <c r="D242" s="5" t="n">
-        <v>59.41</v>
+        <v>60.23</v>
       </c>
       <c r="E242" s="5" t="n">
-        <v>82.19</v>
+        <v>83.31999999999999</v>
       </c>
       <c r="F242" s="7" t="inlineStr"/>
     </row>
@@ -5606,10 +5606,10 @@
         <v>80.04000000000001</v>
       </c>
       <c r="D243" s="5" t="n">
-        <v>69.31</v>
+        <v>70.27</v>
       </c>
       <c r="E243" s="5" t="n">
-        <v>85.8</v>
+        <v>86.98</v>
       </c>
       <c r="F243" s="7" t="inlineStr"/>
     </row>
@@ -5626,10 +5626,10 @@
         <v>28.16</v>
       </c>
       <c r="D244" s="5" t="n">
-        <v>28.1</v>
+        <v>28.48</v>
       </c>
       <c r="E244" s="5" t="n">
-        <v>30.07</v>
+        <v>30.49</v>
       </c>
       <c r="F244" s="7" t="inlineStr"/>
     </row>
@@ -5646,10 +5646,10 @@
         <v>15.14</v>
       </c>
       <c r="D245" s="5" t="n">
-        <v>18.32</v>
+        <v>18.57</v>
       </c>
       <c r="E245" s="5" t="n">
-        <v>16.13</v>
+        <v>16.36</v>
       </c>
       <c r="F245" s="7" t="inlineStr"/>
     </row>
@@ -5666,10 +5666,10 @@
         <v>31.79</v>
       </c>
       <c r="D246" s="5" t="n">
-        <v>37.16</v>
+        <v>37.67</v>
       </c>
       <c r="E246" s="5" t="n">
-        <v>33.81</v>
+        <v>34.27</v>
       </c>
       <c r="F246" s="7" t="inlineStr"/>
     </row>
@@ -5686,10 +5686,10 @@
         <v>25.23</v>
       </c>
       <c r="D247" s="5" t="n">
-        <v>26.84</v>
+        <v>27.21</v>
       </c>
       <c r="E247" s="5" t="n">
-        <v>26.78</v>
+        <v>27.14</v>
       </c>
       <c r="F247" s="7" t="inlineStr"/>
     </row>
@@ -5706,10 +5706,10 @@
         <v>17.65</v>
       </c>
       <c r="D248" s="5" t="n">
-        <v>23.38</v>
+        <v>23.7</v>
       </c>
       <c r="E248" s="5" t="n">
-        <v>18.67</v>
+        <v>18.93</v>
       </c>
       <c r="F248" s="7" t="inlineStr"/>
     </row>
@@ -5726,10 +5726,10 @@
         <v>133.13</v>
       </c>
       <c r="D249" s="5" t="n">
-        <v>87.48</v>
+        <v>88.68000000000001</v>
       </c>
       <c r="E249" s="5" t="n">
-        <v>140.41</v>
+        <v>142.34</v>
       </c>
       <c r="F249" s="7" t="inlineStr"/>
     </row>
@@ -5746,10 +5746,10 @@
         <v>46.25</v>
       </c>
       <c r="D250" s="5" t="n">
-        <v>54.67</v>
+        <v>55.42</v>
       </c>
       <c r="E250" s="5" t="n">
-        <v>48.63</v>
+        <v>49.3</v>
       </c>
       <c r="F250" s="7" t="inlineStr"/>
     </row>
@@ -5766,10 +5766,10 @@
         <v>80.23</v>
       </c>
       <c r="D251" s="5" t="n">
-        <v>88.84999999999999</v>
+        <v>90.08</v>
       </c>
       <c r="E251" s="5" t="n">
-        <v>84.06999999999999</v>
+        <v>85.22</v>
       </c>
       <c r="F251" s="7" t="inlineStr"/>
     </row>
@@ -5786,10 +5786,10 @@
         <v>146.58</v>
       </c>
       <c r="D252" s="5" t="n">
-        <v>138.84</v>
+        <v>140.75</v>
       </c>
       <c r="E252" s="5" t="n">
-        <v>153.05</v>
+        <v>155.16</v>
       </c>
       <c r="F252" s="7" t="inlineStr"/>
     </row>
@@ -5806,10 +5806,10 @@
         <v>198.82</v>
       </c>
       <c r="D253" s="5" t="n">
-        <v>170.89</v>
+        <v>173.24</v>
       </c>
       <c r="E253" s="5" t="n">
-        <v>206.88</v>
+        <v>209.73</v>
       </c>
       <c r="F253" s="7" t="inlineStr"/>
     </row>
@@ -5826,10 +5826,10 @@
         <v>191.83</v>
       </c>
       <c r="D254" s="5" t="n">
-        <v>155.08</v>
+        <v>157.21</v>
       </c>
       <c r="E254" s="5" t="n">
-        <v>199.47</v>
+        <v>202.21</v>
       </c>
       <c r="F254" s="7" t="inlineStr"/>
     </row>
@@ -5846,10 +5846,10 @@
         <v>216.14</v>
       </c>
       <c r="D255" s="5" t="n">
-        <v>149</v>
+        <v>151.05</v>
       </c>
       <c r="E255" s="5" t="n">
-        <v>224.58</v>
+        <v>227.67</v>
       </c>
       <c r="F255" s="7" t="inlineStr"/>
     </row>
@@ -5866,10 +5866,10 @@
         <v>26.5</v>
       </c>
       <c r="D256" s="5" t="n">
-        <v>18.06</v>
+        <v>18.3</v>
       </c>
       <c r="E256" s="5" t="n">
-        <v>27.51</v>
+        <v>27.89</v>
       </c>
       <c r="F256" s="7" t="inlineStr"/>
     </row>
@@ -5886,10 +5886,10 @@
         <v>10.18</v>
       </c>
       <c r="D257" s="5" t="n">
-        <v>21.13</v>
+        <v>21.42</v>
       </c>
       <c r="E257" s="5" t="n">
-        <v>10.56</v>
+        <v>10.71</v>
       </c>
       <c r="F257" s="7" t="inlineStr"/>
     </row>
@@ -5906,10 +5906,10 @@
         <v>52.94</v>
       </c>
       <c r="D258" s="5" t="n">
-        <v>66.45</v>
+        <v>67.36</v>
       </c>
       <c r="E258" s="5" t="n">
-        <v>54.9</v>
+        <v>55.65</v>
       </c>
       <c r="F258" s="7" t="inlineStr"/>
     </row>
@@ -5926,10 +5926,10 @@
         <v>39.93</v>
       </c>
       <c r="D259" s="5" t="n">
-        <v>54.14</v>
+        <v>54.89</v>
       </c>
       <c r="E259" s="5" t="n">
-        <v>41.38</v>
+        <v>41.95</v>
       </c>
       <c r="F259" s="7" t="inlineStr"/>
     </row>
@@ -5946,10 +5946,10 @@
         <v>23.72</v>
       </c>
       <c r="D260" s="5" t="n">
-        <v>49.95</v>
+        <v>50.64</v>
       </c>
       <c r="E260" s="5" t="n">
-        <v>24.5</v>
+        <v>24.84</v>
       </c>
       <c r="F260" s="7" t="inlineStr"/>
     </row>
@@ -5966,10 +5966,10 @@
         <v>76.73</v>
       </c>
       <c r="D261" s="5" t="n">
-        <v>70.59999999999999</v>
+        <v>71.56999999999999</v>
       </c>
       <c r="E261" s="5" t="n">
-        <v>79.03</v>
+        <v>80.11</v>
       </c>
       <c r="F261" s="7" t="inlineStr"/>
     </row>
@@ -5986,10 +5986,10 @@
         <v>62.93</v>
       </c>
       <c r="D262" s="5" t="n">
-        <v>63.41</v>
+        <v>64.28</v>
       </c>
       <c r="E262" s="5" t="n">
-        <v>64.62</v>
+        <v>65.51000000000001</v>
       </c>
       <c r="F262" s="7" t="inlineStr"/>
     </row>
@@ -6006,10 +6006,10 @@
         <v>70.56</v>
       </c>
       <c r="D263" s="5" t="n">
-        <v>76.56999999999999</v>
+        <v>77.63</v>
       </c>
       <c r="E263" s="5" t="n">
-        <v>72.27</v>
+        <v>73.27</v>
       </c>
       <c r="F263" s="7" t="inlineStr"/>
     </row>
@@ -6026,10 +6026,10 @@
         <v>93.92</v>
       </c>
       <c r="D264" s="5" t="n">
-        <v>79.75</v>
+        <v>80.84</v>
       </c>
       <c r="E264" s="5" t="n">
-        <v>95.95999999999999</v>
+        <v>97.28</v>
       </c>
       <c r="F264" s="7" t="inlineStr"/>
     </row>
@@ -6046,10 +6046,10 @@
         <v>463.18</v>
       </c>
       <c r="D265" s="5" t="n">
-        <v>269.68</v>
+        <v>273.39</v>
       </c>
       <c r="E265" s="5" t="n">
-        <v>472.07</v>
+        <v>478.57</v>
       </c>
       <c r="F265" s="7" t="inlineStr"/>
     </row>
@@ -6066,10 +6066,10 @@
         <v>107.96</v>
       </c>
       <c r="D266" s="5" t="n">
-        <v>83.34</v>
+        <v>84.48999999999999</v>
       </c>
       <c r="E266" s="5" t="n">
-        <v>109.55</v>
+        <v>111.06</v>
       </c>
       <c r="F266" s="7" t="inlineStr"/>
     </row>
@@ -6086,10 +6086,10 @@
         <v>107.79</v>
       </c>
       <c r="D267" s="5" t="n">
-        <v>94.15000000000001</v>
+        <v>95.45</v>
       </c>
       <c r="E267" s="5" t="n">
-        <v>108.9</v>
+        <v>110.4</v>
       </c>
       <c r="F267" s="7" t="inlineStr"/>
     </row>
@@ -6106,10 +6106,10 @@
         <v>61.8</v>
       </c>
       <c r="D268" s="5" t="n">
-        <v>55.6</v>
+        <v>56.36</v>
       </c>
       <c r="E268" s="5" t="n">
-        <v>62.17</v>
+        <v>63.02</v>
       </c>
       <c r="F268" s="7" t="inlineStr"/>
     </row>
@@ -6126,10 +6126,10 @@
         <v>45.13</v>
       </c>
       <c r="D269" s="5" t="n">
-        <v>51.57</v>
+        <v>52.28</v>
       </c>
       <c r="E269" s="5" t="n">
-        <v>45.31</v>
+        <v>45.93</v>
       </c>
       <c r="F269" s="7" t="inlineStr"/>
     </row>
@@ -6146,10 +6146,10 @@
         <v>13.79</v>
       </c>
       <c r="D270" s="5" t="n">
-        <v>31.98</v>
+        <v>32.42</v>
       </c>
       <c r="E270" s="5" t="n">
-        <v>13.82</v>
+        <v>14.01</v>
       </c>
       <c r="F270" s="7" t="inlineStr"/>
     </row>
@@ -6166,10 +6166,10 @@
         <v>16.99</v>
       </c>
       <c r="D271" s="5" t="n">
-        <v>27.51</v>
+        <v>27.89</v>
       </c>
       <c r="E271" s="5" t="n">
-        <v>16.99</v>
+        <v>17.22</v>
       </c>
       <c r="F271" s="7" t="inlineStr"/>
     </row>
@@ -6186,10 +6186,10 @@
         <v>43.74</v>
       </c>
       <c r="D272" s="5" t="n">
-        <v>38.55</v>
+        <v>38.9</v>
       </c>
       <c r="E272" s="5" t="n">
-        <v>43.74</v>
+        <v>44.14</v>
       </c>
       <c r="F272" s="7" t="inlineStr"/>
     </row>
@@ -6206,10 +6206,10 @@
         <v>40.2</v>
       </c>
       <c r="D273" s="5" t="n">
-        <v>45.06</v>
+        <v>45.26</v>
       </c>
       <c r="E273" s="5" t="n">
-        <v>40.2</v>
+        <v>40.38</v>
       </c>
       <c r="F273" s="7" t="inlineStr"/>
     </row>
@@ -6252,6 +6252,26 @@
         <v>39.73</v>
       </c>
       <c r="F275" s="7" t="inlineStr"/>
+    </row>
+    <row r="276">
+      <c r="A276" s="4" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="B276" s="5" t="n">
+        <v>42.63</v>
+      </c>
+      <c r="C276" s="5" t="n">
+        <v>44.24</v>
+      </c>
+      <c r="D276" s="5" t="n">
+        <v>42.63</v>
+      </c>
+      <c r="E276" s="5" t="n">
+        <v>44.24</v>
+      </c>
+      <c r="F276" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6264,7 +6284,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E275"/>
+  <dimension ref="A1:E276"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6314,10 +6334,10 @@
         <v>32.99</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>46.97</v>
+        <v>47.61</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>60.48</v>
+        <v>61.31</v>
       </c>
     </row>
     <row r="3">
@@ -6333,10 +6353,10 @@
         <v>23.45</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>36.87</v>
+        <v>37.38</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>42.91</v>
+        <v>43.5</v>
       </c>
     </row>
     <row r="4">
@@ -6352,10 +6372,10 @@
         <v>25.19</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>37.86</v>
+        <v>38.38</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>46.01</v>
+        <v>46.64</v>
       </c>
     </row>
     <row r="5">
@@ -6371,10 +6391,10 @@
         <v>25.19</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>37.81</v>
+        <v>38.33</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>45.92</v>
+        <v>46.56</v>
       </c>
     </row>
     <row r="6">
@@ -6390,10 +6410,10 @@
         <v>26.23</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>38.55</v>
+        <v>39.08</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>47.74</v>
+        <v>48.39</v>
       </c>
     </row>
     <row r="7">
@@ -6409,10 +6429,10 @@
         <v>34.01</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>45.36</v>
+        <v>45.99</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>61.79</v>
+        <v>62.64</v>
       </c>
     </row>
     <row r="8">
@@ -6428,10 +6448,10 @@
         <v>30.37</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>40.79</v>
+        <v>41.35</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>55.01</v>
+        <v>55.77</v>
       </c>
     </row>
     <row r="9">
@@ -6447,10 +6467,10 @@
         <v>48.76</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>69.75</v>
+        <v>70.70999999999999</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>88.06</v>
+        <v>89.27</v>
       </c>
     </row>
     <row r="10">
@@ -6466,10 +6486,10 @@
         <v>28.54</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>38.68</v>
+        <v>39.21</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>51.39</v>
+        <v>52.1</v>
       </c>
     </row>
     <row r="11">
@@ -6485,10 +6505,10 @@
         <v>36.99</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>52.97</v>
+        <v>53.7</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>66.51000000000001</v>
+        <v>67.42</v>
       </c>
     </row>
     <row r="12">
@@ -6504,10 +6524,10 @@
         <v>39.67</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>56.17</v>
+        <v>56.94</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>71.20999999999999</v>
+        <v>72.19</v>
       </c>
     </row>
     <row r="13">
@@ -6523,10 +6543,10 @@
         <v>34.73</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>51.32</v>
+        <v>52.02</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>62.25</v>
+        <v>63.11</v>
       </c>
     </row>
     <row r="14">
@@ -6542,10 +6562,10 @@
         <v>43.7</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>56.15</v>
+        <v>56.92</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>78.22</v>
+        <v>79.3</v>
       </c>
     </row>
     <row r="15">
@@ -6561,10 +6581,10 @@
         <v>27.37</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>40.31</v>
+        <v>40.86</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>48.92</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="16">
@@ -6580,10 +6600,10 @@
         <v>31.48</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>48.55</v>
+        <v>49.22</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>56.19</v>
+        <v>56.97</v>
       </c>
     </row>
     <row r="17">
@@ -6599,10 +6619,10 @@
         <v>70.45</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>79.91</v>
+        <v>81.01000000000001</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>125.44</v>
+        <v>127.16</v>
       </c>
     </row>
     <row r="18">
@@ -6618,10 +6638,10 @@
         <v>44.55</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>63.33</v>
+        <v>64.2</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>79.12</v>
+        <v>80.20999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -6637,10 +6657,10 @@
         <v>33</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>48.47</v>
+        <v>49.13</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>58.46</v>
+        <v>59.26</v>
       </c>
     </row>
     <row r="20">
@@ -6656,10 +6676,10 @@
         <v>29.72</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>40.37</v>
+        <v>40.93</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>52.53</v>
+        <v>53.25</v>
       </c>
     </row>
     <row r="21">
@@ -6675,10 +6695,10 @@
         <v>27.43</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>38.5</v>
+        <v>39.03</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>48.38</v>
+        <v>49.04</v>
       </c>
     </row>
     <row r="22">
@@ -6694,10 +6714,10 @@
         <v>21.15</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>32.91</v>
+        <v>33.36</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>37.22</v>
+        <v>37.73</v>
       </c>
     </row>
     <row r="23">
@@ -6713,10 +6733,10 @@
         <v>37.8</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>53.79</v>
+        <v>54.53</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>66.38</v>
+        <v>67.3</v>
       </c>
     </row>
     <row r="24">
@@ -6732,10 +6752,10 @@
         <v>29.2</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>43.05</v>
+        <v>43.64</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>51.18</v>
+        <v>51.88</v>
       </c>
     </row>
     <row r="25">
@@ -6751,10 +6771,10 @@
         <v>27.29</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>41.18</v>
+        <v>41.74</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>47.74</v>
+        <v>48.39</v>
       </c>
     </row>
     <row r="26">
@@ -6770,10 +6790,10 @@
         <v>32.37</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>46.22</v>
+        <v>46.86</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>56.44</v>
+        <v>57.21</v>
       </c>
     </row>
     <row r="27">
@@ -6789,10 +6809,10 @@
         <v>40.25</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>52.13</v>
+        <v>52.85</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>69.94</v>
+        <v>70.91</v>
       </c>
     </row>
     <row r="28">
@@ -6808,10 +6828,10 @@
         <v>37.44</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>50.47</v>
+        <v>51.17</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>64.84999999999999</v>
+        <v>65.73999999999999</v>
       </c>
     </row>
     <row r="29">
@@ -6827,10 +6847,10 @@
         <v>28.49</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>39.15</v>
+        <v>39.68</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>49.26</v>
+        <v>49.94</v>
       </c>
     </row>
     <row r="30">
@@ -6846,10 +6866,10 @@
         <v>46.39</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>52.99</v>
+        <v>53.72</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>80.06999999999999</v>
+        <v>81.17</v>
       </c>
     </row>
     <row r="31">
@@ -6865,10 +6885,10 @@
         <v>49.23</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>59</v>
+        <v>59.81</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>84.83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="32">
@@ -6884,10 +6904,10 @@
         <v>88.63</v>
       </c>
       <c r="D32" s="5" t="n">
-        <v>91.81999999999999</v>
+        <v>93.08</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>152.28</v>
+        <v>154.38</v>
       </c>
     </row>
     <row r="33">
@@ -6903,10 +6923,10 @@
         <v>105.51</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>95.95</v>
+        <v>97.27</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>180.77</v>
+        <v>183.26</v>
       </c>
     </row>
     <row r="34">
@@ -6922,10 +6942,10 @@
         <v>29.33</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>39.91</v>
+        <v>40.46</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>50.11</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="35">
@@ -6941,10 +6961,10 @@
         <v>27.86</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>38.39</v>
+        <v>38.92</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>47.35</v>
+        <v>48</v>
       </c>
     </row>
     <row r="36">
@@ -6960,10 +6980,10 @@
         <v>37.94</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>47.76</v>
+        <v>48.42</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>64.14</v>
+        <v>65.02</v>
       </c>
     </row>
     <row r="37">
@@ -6979,10 +6999,10 @@
         <v>42.49</v>
       </c>
       <c r="D37" s="5" t="n">
-        <v>58.21</v>
+        <v>59.01</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>71.45999999999999</v>
+        <v>72.44</v>
       </c>
     </row>
     <row r="38">
@@ -6998,10 +7018,10 @@
         <v>71.86</v>
       </c>
       <c r="D38" s="5" t="n">
-        <v>79.15000000000001</v>
+        <v>80.23999999999999</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>120.5</v>
+        <v>122.16</v>
       </c>
     </row>
     <row r="39">
@@ -7017,10 +7037,10 @@
         <v>39.11</v>
       </c>
       <c r="D39" s="5" t="n">
-        <v>53.85</v>
+        <v>54.59</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>65.39</v>
+        <v>66.29000000000001</v>
       </c>
     </row>
     <row r="40">
@@ -7036,10 +7056,10 @@
         <v>38.91</v>
       </c>
       <c r="D40" s="5" t="n">
-        <v>51.34</v>
+        <v>52.05</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>64.86</v>
+        <v>65.76000000000001</v>
       </c>
     </row>
     <row r="41">
@@ -7055,10 +7075,10 @@
         <v>34.69</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>46.13</v>
+        <v>46.76</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>57.85</v>
+        <v>58.65</v>
       </c>
     </row>
     <row r="42">
@@ -7074,10 +7094,10 @@
         <v>42.78</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>54.57</v>
+        <v>55.32</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>71.37</v>
+        <v>72.34999999999999</v>
       </c>
     </row>
     <row r="43">
@@ -7093,10 +7113,10 @@
         <v>28.32</v>
       </c>
       <c r="D43" s="5" t="n">
-        <v>37.18</v>
+        <v>37.7</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>47.26</v>
+        <v>47.91</v>
       </c>
     </row>
     <row r="44">
@@ -7112,10 +7132,10 @@
         <v>165.37</v>
       </c>
       <c r="D44" s="5" t="n">
-        <v>152.6</v>
+        <v>154.7</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>275.92</v>
+        <v>279.71</v>
       </c>
     </row>
     <row r="45">
@@ -7131,10 +7151,10 @@
         <v>69.13</v>
       </c>
       <c r="D45" s="5" t="n">
-        <v>79.13</v>
+        <v>80.22</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>115.31</v>
+        <v>116.9</v>
       </c>
     </row>
     <row r="46">
@@ -7150,10 +7170,10 @@
         <v>74.84999999999999</v>
       </c>
       <c r="D46" s="5" t="n">
-        <v>88.84999999999999</v>
+        <v>90.06999999999999</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>124.82</v>
+        <v>126.53</v>
       </c>
     </row>
     <row r="47">
@@ -7169,10 +7189,10 @@
         <v>81.62</v>
       </c>
       <c r="D47" s="5" t="n">
-        <v>112.53</v>
+        <v>114.08</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>135.55</v>
+        <v>137.41</v>
       </c>
     </row>
     <row r="48">
@@ -7188,10 +7208,10 @@
         <v>75.48999999999999</v>
       </c>
       <c r="D48" s="5" t="n">
-        <v>103.61</v>
+        <v>105.03</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>124.86</v>
+        <v>126.58</v>
       </c>
     </row>
     <row r="49">
@@ -7207,10 +7227,10 @@
         <v>218.05</v>
       </c>
       <c r="D49" s="5" t="n">
-        <v>236.02</v>
+        <v>239.27</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>359.19</v>
+        <v>364.13</v>
       </c>
     </row>
     <row r="50">
@@ -7226,10 +7246,10 @@
         <v>115.22</v>
       </c>
       <c r="D50" s="5" t="n">
-        <v>140.6</v>
+        <v>142.54</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>189.37</v>
+        <v>191.97</v>
       </c>
     </row>
     <row r="51">
@@ -7245,10 +7265,10 @@
         <v>50.83</v>
       </c>
       <c r="D51" s="5" t="n">
-        <v>68.43000000000001</v>
+        <v>69.37</v>
       </c>
       <c r="E51" s="5" t="n">
-        <v>83.34999999999999</v>
+        <v>84.5</v>
       </c>
     </row>
     <row r="52">
@@ -7264,10 +7284,10 @@
         <v>55.04</v>
       </c>
       <c r="D52" s="5" t="n">
-        <v>72.93000000000001</v>
+        <v>73.94</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>90.05</v>
+        <v>91.28</v>
       </c>
     </row>
     <row r="53">
@@ -7283,10 +7303,10 @@
         <v>45.32</v>
       </c>
       <c r="D53" s="5" t="n">
-        <v>57.92</v>
+        <v>58.71</v>
       </c>
       <c r="E53" s="5" t="n">
-        <v>73.91</v>
+        <v>74.93000000000001</v>
       </c>
     </row>
     <row r="54">
@@ -7302,10 +7322,10 @@
         <v>54.55</v>
       </c>
       <c r="D54" s="5" t="n">
-        <v>69.48</v>
+        <v>70.43000000000001</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>88.69</v>
+        <v>89.91</v>
       </c>
     </row>
     <row r="55">
@@ -7321,10 +7341,10 @@
         <v>62.08</v>
       </c>
       <c r="D55" s="5" t="n">
-        <v>72.59999999999999</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="E55" s="5" t="n">
-        <v>100.63</v>
+        <v>102.01</v>
       </c>
     </row>
     <row r="56">
@@ -7340,10 +7360,10 @@
         <v>55.11</v>
       </c>
       <c r="D56" s="5" t="n">
-        <v>65.15000000000001</v>
+        <v>66.04000000000001</v>
       </c>
       <c r="E56" s="5" t="n">
-        <v>88.93000000000001</v>
+        <v>90.16</v>
       </c>
     </row>
     <row r="57">
@@ -7359,10 +7379,10 @@
         <v>52.11</v>
       </c>
       <c r="D57" s="5" t="n">
-        <v>59.25</v>
+        <v>60.07</v>
       </c>
       <c r="E57" s="5" t="n">
-        <v>83.72</v>
+        <v>84.87</v>
       </c>
     </row>
     <row r="58">
@@ -7378,10 +7398,10 @@
         <v>84.56999999999999</v>
       </c>
       <c r="D58" s="5" t="n">
-        <v>83.40000000000001</v>
+        <v>84.54000000000001</v>
       </c>
       <c r="E58" s="5" t="n">
-        <v>135.27</v>
+        <v>137.13</v>
       </c>
     </row>
     <row r="59">
@@ -7397,10 +7417,10 @@
         <v>50.14</v>
       </c>
       <c r="D59" s="5" t="n">
-        <v>63.45</v>
+        <v>64.31999999999999</v>
       </c>
       <c r="E59" s="5" t="n">
-        <v>79.81</v>
+        <v>80.91</v>
       </c>
     </row>
     <row r="60">
@@ -7416,10 +7436,10 @@
         <v>64.59</v>
       </c>
       <c r="D60" s="5" t="n">
-        <v>85.59</v>
+        <v>86.77</v>
       </c>
       <c r="E60" s="5" t="n">
-        <v>102.32</v>
+        <v>103.73</v>
       </c>
     </row>
     <row r="61">
@@ -7435,10 +7455,10 @@
         <v>52.09</v>
       </c>
       <c r="D61" s="5" t="n">
-        <v>66.28</v>
+        <v>67.19</v>
       </c>
       <c r="E61" s="5" t="n">
-        <v>82.13</v>
+        <v>83.26000000000001</v>
       </c>
     </row>
     <row r="62">
@@ -7454,10 +7474,10 @@
         <v>60.12</v>
       </c>
       <c r="D62" s="5" t="n">
-        <v>67.59999999999999</v>
+        <v>68.53</v>
       </c>
       <c r="E62" s="5" t="n">
-        <v>94.42</v>
+        <v>95.72</v>
       </c>
     </row>
     <row r="63">
@@ -7473,10 +7493,10 @@
         <v>50.92</v>
       </c>
       <c r="D63" s="5" t="n">
-        <v>64</v>
+        <v>64.88</v>
       </c>
       <c r="E63" s="5" t="n">
-        <v>79.66</v>
+        <v>80.76000000000001</v>
       </c>
     </row>
     <row r="64">
@@ -7492,10 +7512,10 @@
         <v>47.77</v>
       </c>
       <c r="D64" s="5" t="n">
-        <v>57.07</v>
+        <v>57.86</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>74.45</v>
+        <v>75.47</v>
       </c>
     </row>
     <row r="65">
@@ -7511,10 +7531,10 @@
         <v>51.76</v>
       </c>
       <c r="D65" s="5" t="n">
-        <v>61.42</v>
+        <v>62.27</v>
       </c>
       <c r="E65" s="5" t="n">
-        <v>80.76000000000001</v>
+        <v>81.87</v>
       </c>
     </row>
     <row r="66">
@@ -7530,10 +7550,10 @@
         <v>45.33</v>
       </c>
       <c r="D66" s="5" t="n">
-        <v>53.98</v>
+        <v>54.72</v>
       </c>
       <c r="E66" s="5" t="n">
-        <v>70.8</v>
+        <v>71.77</v>
       </c>
     </row>
     <row r="67">
@@ -7549,10 +7569,10 @@
         <v>27.82</v>
       </c>
       <c r="D67" s="5" t="n">
-        <v>35.17</v>
+        <v>35.65</v>
       </c>
       <c r="E67" s="5" t="n">
-        <v>43.5</v>
+        <v>44.1</v>
       </c>
     </row>
     <row r="68">
@@ -7568,10 +7588,10 @@
         <v>248.2</v>
       </c>
       <c r="D68" s="5" t="n">
-        <v>196.22</v>
+        <v>198.92</v>
       </c>
       <c r="E68" s="5" t="n">
-        <v>387.94</v>
+        <v>393.28</v>
       </c>
     </row>
     <row r="69">
@@ -7587,10 +7607,10 @@
         <v>44.74</v>
       </c>
       <c r="D69" s="5" t="n">
-        <v>52.19</v>
+        <v>52.9</v>
       </c>
       <c r="E69" s="5" t="n">
-        <v>69.90000000000001</v>
+        <v>70.87</v>
       </c>
     </row>
     <row r="70">
@@ -7606,10 +7626,10 @@
         <v>32.56</v>
       </c>
       <c r="D70" s="5" t="n">
-        <v>39.47</v>
+        <v>40.01</v>
       </c>
       <c r="E70" s="5" t="n">
-        <v>50.86</v>
+        <v>51.55</v>
       </c>
     </row>
     <row r="71">
@@ -7625,10 +7645,10 @@
         <v>49.27</v>
       </c>
       <c r="D71" s="5" t="n">
-        <v>58.16</v>
+        <v>58.96</v>
       </c>
       <c r="E71" s="5" t="n">
-        <v>76.83</v>
+        <v>77.88</v>
       </c>
     </row>
     <row r="72">
@@ -7644,10 +7664,10 @@
         <v>37.87</v>
       </c>
       <c r="D72" s="5" t="n">
-        <v>48.96</v>
+        <v>49.63</v>
       </c>
       <c r="E72" s="5" t="n">
-        <v>58.95</v>
+        <v>59.76</v>
       </c>
     </row>
     <row r="73">
@@ -7663,10 +7683,10 @@
         <v>37.13</v>
       </c>
       <c r="D73" s="5" t="n">
-        <v>46.73</v>
+        <v>47.38</v>
       </c>
       <c r="E73" s="5" t="n">
-        <v>57.71</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="74">
@@ -7682,10 +7702,10 @@
         <v>32.55</v>
       </c>
       <c r="D74" s="5" t="n">
-        <v>41.58</v>
+        <v>42.15</v>
       </c>
       <c r="E74" s="5" t="n">
-        <v>50.43</v>
+        <v>51.12</v>
       </c>
     </row>
     <row r="75">
@@ -7701,10 +7721,10 @@
         <v>28.02</v>
       </c>
       <c r="D75" s="5" t="n">
-        <v>34.66</v>
+        <v>35.13</v>
       </c>
       <c r="E75" s="5" t="n">
-        <v>43.27</v>
+        <v>43.87</v>
       </c>
     </row>
     <row r="76">
@@ -7720,10 +7740,10 @@
         <v>27.43</v>
       </c>
       <c r="D76" s="5" t="n">
-        <v>35.32</v>
+        <v>35.8</v>
       </c>
       <c r="E76" s="5" t="n">
-        <v>42.23</v>
+        <v>42.81</v>
       </c>
     </row>
     <row r="77">
@@ -7739,10 +7759,10 @@
         <v>31.55</v>
       </c>
       <c r="D77" s="5" t="n">
-        <v>39.28</v>
+        <v>39.82</v>
       </c>
       <c r="E77" s="5" t="n">
-        <v>48.49</v>
+        <v>49.15</v>
       </c>
     </row>
     <row r="78">
@@ -7758,10 +7778,10 @@
         <v>44.98</v>
       </c>
       <c r="D78" s="5" t="n">
-        <v>49.75</v>
+        <v>50.44</v>
       </c>
       <c r="E78" s="5" t="n">
-        <v>69</v>
+        <v>69.95</v>
       </c>
     </row>
     <row r="79">
@@ -7777,10 +7797,10 @@
         <v>29.49</v>
       </c>
       <c r="D79" s="5" t="n">
-        <v>36</v>
+        <v>36.5</v>
       </c>
       <c r="E79" s="5" t="n">
-        <v>45.16</v>
+        <v>45.78</v>
       </c>
     </row>
     <row r="80">
@@ -7796,10 +7816,10 @@
         <v>114.74</v>
       </c>
       <c r="D80" s="5" t="n">
-        <v>93.05</v>
+        <v>94.33</v>
       </c>
       <c r="E80" s="5" t="n">
-        <v>175.17</v>
+        <v>177.58</v>
       </c>
     </row>
     <row r="81">
@@ -7815,10 +7835,10 @@
         <v>124.09</v>
       </c>
       <c r="D81" s="5" t="n">
-        <v>103.35</v>
+        <v>104.78</v>
       </c>
       <c r="E81" s="5" t="n">
-        <v>188.86</v>
+        <v>191.45</v>
       </c>
     </row>
     <row r="82">
@@ -7834,10 +7854,10 @@
         <v>27.11</v>
       </c>
       <c r="D82" s="5" t="n">
-        <v>34.68</v>
+        <v>35.16</v>
       </c>
       <c r="E82" s="5" t="n">
-        <v>41.13</v>
+        <v>41.7</v>
       </c>
     </row>
     <row r="83">
@@ -7853,10 +7873,10 @@
         <v>131.25</v>
       </c>
       <c r="D83" s="5" t="n">
-        <v>108.36</v>
+        <v>109.85</v>
       </c>
       <c r="E83" s="5" t="n">
-        <v>198.74</v>
+        <v>201.47</v>
       </c>
     </row>
     <row r="84">
@@ -7872,10 +7892,10 @@
         <v>34.97</v>
       </c>
       <c r="D84" s="5" t="n">
-        <v>46.07</v>
+        <v>46.71</v>
       </c>
       <c r="E84" s="5" t="n">
-        <v>52.84</v>
+        <v>53.57</v>
       </c>
     </row>
     <row r="85">
@@ -7891,10 +7911,10 @@
         <v>36.19</v>
       </c>
       <c r="D85" s="5" t="n">
-        <v>47.35</v>
+        <v>48.01</v>
       </c>
       <c r="E85" s="5" t="n">
-        <v>54.58</v>
+        <v>55.33</v>
       </c>
     </row>
     <row r="86">
@@ -7910,10 +7930,10 @@
         <v>30.36</v>
       </c>
       <c r="D86" s="5" t="n">
-        <v>40.09</v>
+        <v>40.65</v>
       </c>
       <c r="E86" s="5" t="n">
-        <v>45.68</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="87">
@@ -7929,10 +7949,10 @@
         <v>30.73</v>
       </c>
       <c r="D87" s="5" t="n">
-        <v>40.6</v>
+        <v>41.16</v>
       </c>
       <c r="E87" s="5" t="n">
-        <v>46.12</v>
+        <v>46.76</v>
       </c>
     </row>
     <row r="88">
@@ -7948,10 +7968,10 @@
         <v>24.89</v>
       </c>
       <c r="D88" s="5" t="n">
-        <v>33.12</v>
+        <v>33.58</v>
       </c>
       <c r="E88" s="5" t="n">
-        <v>37.27</v>
+        <v>37.78</v>
       </c>
     </row>
     <row r="89">
@@ -7967,10 +7987,10 @@
         <v>24.65</v>
       </c>
       <c r="D89" s="5" t="n">
-        <v>31.13</v>
+        <v>31.56</v>
       </c>
       <c r="E89" s="5" t="n">
-        <v>36.86</v>
+        <v>37.37</v>
       </c>
     </row>
     <row r="90">
@@ -7986,10 +8006,10 @@
         <v>21.04</v>
       </c>
       <c r="D90" s="5" t="n">
-        <v>27.51</v>
+        <v>27.89</v>
       </c>
       <c r="E90" s="5" t="n">
-        <v>31.42</v>
+        <v>31.85</v>
       </c>
     </row>
     <row r="91">
@@ -8005,10 +8025,10 @@
         <v>18.96</v>
       </c>
       <c r="D91" s="5" t="n">
-        <v>24.64</v>
+        <v>24.98</v>
       </c>
       <c r="E91" s="5" t="n">
-        <v>28.28</v>
+        <v>28.67</v>
       </c>
     </row>
     <row r="92">
@@ -8024,10 +8044,10 @@
         <v>66.16</v>
       </c>
       <c r="D92" s="5" t="n">
-        <v>60.94</v>
+        <v>61.78</v>
       </c>
       <c r="E92" s="5" t="n">
-        <v>98.17</v>
+        <v>99.52</v>
       </c>
     </row>
     <row r="93">
@@ -8043,10 +8063,10 @@
         <v>59.69</v>
       </c>
       <c r="D93" s="5" t="n">
-        <v>59.73</v>
+        <v>60.55</v>
       </c>
       <c r="E93" s="5" t="n">
-        <v>88.12</v>
+        <v>89.33</v>
       </c>
     </row>
     <row r="94">
@@ -8062,10 +8082,10 @@
         <v>28.62</v>
       </c>
       <c r="D94" s="5" t="n">
-        <v>36.66</v>
+        <v>37.17</v>
       </c>
       <c r="E94" s="5" t="n">
-        <v>42.04</v>
+        <v>42.62</v>
       </c>
     </row>
     <row r="95">
@@ -8081,10 +8101,10 @@
         <v>28.26</v>
       </c>
       <c r="D95" s="5" t="n">
-        <v>37.49</v>
+        <v>38</v>
       </c>
       <c r="E95" s="5" t="n">
-        <v>41.38</v>
+        <v>41.95</v>
       </c>
     </row>
     <row r="96">
@@ -8100,10 +8120,10 @@
         <v>40.58</v>
       </c>
       <c r="D96" s="5" t="n">
-        <v>50.15</v>
+        <v>50.84</v>
       </c>
       <c r="E96" s="5" t="n">
-        <v>59.24</v>
+        <v>60.06</v>
       </c>
     </row>
     <row r="97">
@@ -8119,10 +8139,10 @@
         <v>33.89</v>
       </c>
       <c r="D97" s="5" t="n">
-        <v>40.63</v>
+        <v>41.19</v>
       </c>
       <c r="E97" s="5" t="n">
-        <v>49.32</v>
+        <v>50</v>
       </c>
     </row>
     <row r="98">
@@ -8138,10 +8158,10 @@
         <v>37.84</v>
       </c>
       <c r="D98" s="5" t="n">
-        <v>42.83</v>
+        <v>43.42</v>
       </c>
       <c r="E98" s="5" t="n">
-        <v>54.96</v>
+        <v>55.72</v>
       </c>
     </row>
     <row r="99">
@@ -8157,10 +8177,10 @@
         <v>35.44</v>
       </c>
       <c r="D99" s="5" t="n">
-        <v>43.42</v>
+        <v>44.01</v>
       </c>
       <c r="E99" s="5" t="n">
-        <v>51.38</v>
+        <v>52.08</v>
       </c>
     </row>
     <row r="100">
@@ -8176,10 +8196,10 @@
         <v>31.61</v>
       </c>
       <c r="D100" s="5" t="n">
-        <v>39.03</v>
+        <v>39.57</v>
       </c>
       <c r="E100" s="5" t="n">
-        <v>45.73</v>
+        <v>46.36</v>
       </c>
     </row>
     <row r="101">
@@ -8195,10 +8215,10 @@
         <v>29</v>
       </c>
       <c r="D101" s="5" t="n">
-        <v>34.16</v>
+        <v>34.63</v>
       </c>
       <c r="E101" s="5" t="n">
-        <v>41.96</v>
+        <v>42.53</v>
       </c>
     </row>
     <row r="102">
@@ -8214,10 +8234,10 @@
         <v>30.77</v>
       </c>
       <c r="D102" s="5" t="n">
-        <v>38.46</v>
+        <v>38.98</v>
       </c>
       <c r="E102" s="5" t="n">
-        <v>44.52</v>
+        <v>45.13</v>
       </c>
     </row>
     <row r="103">
@@ -8233,10 +8253,10 @@
         <v>25.62</v>
       </c>
       <c r="D103" s="5" t="n">
-        <v>32.09</v>
+        <v>32.53</v>
       </c>
       <c r="E103" s="5" t="n">
-        <v>37.07</v>
+        <v>37.58</v>
       </c>
     </row>
     <row r="104">
@@ -8252,10 +8272,10 @@
         <v>29.13</v>
       </c>
       <c r="D104" s="5" t="n">
-        <v>34.76</v>
+        <v>35.24</v>
       </c>
       <c r="E104" s="5" t="n">
-        <v>42.14</v>
+        <v>42.72</v>
       </c>
     </row>
     <row r="105">
@@ -8271,10 +8291,10 @@
         <v>30.01</v>
       </c>
       <c r="D105" s="5" t="n">
-        <v>37.38</v>
+        <v>37.9</v>
       </c>
       <c r="E105" s="5" t="n">
-        <v>43.4</v>
+        <v>44</v>
       </c>
     </row>
     <row r="106">
@@ -8290,10 +8310,10 @@
         <v>27.89</v>
       </c>
       <c r="D106" s="5" t="n">
-        <v>34.27</v>
+        <v>34.74</v>
       </c>
       <c r="E106" s="5" t="n">
-        <v>40.33</v>
+        <v>40.88</v>
       </c>
     </row>
     <row r="107">
@@ -8309,10 +8329,10 @@
         <v>36.3</v>
       </c>
       <c r="D107" s="5" t="n">
-        <v>46.2</v>
+        <v>46.84</v>
       </c>
       <c r="E107" s="5" t="n">
-        <v>52.4</v>
+        <v>53.12</v>
       </c>
     </row>
     <row r="108">
@@ -8328,10 +8348,10 @@
         <v>30.09</v>
       </c>
       <c r="D108" s="5" t="n">
-        <v>38.3</v>
+        <v>38.83</v>
       </c>
       <c r="E108" s="5" t="n">
-        <v>43.36</v>
+        <v>43.96</v>
       </c>
     </row>
     <row r="109">
@@ -8347,10 +8367,10 @@
         <v>42.66</v>
       </c>
       <c r="D109" s="5" t="n">
-        <v>52.86</v>
+        <v>53.59</v>
       </c>
       <c r="E109" s="5" t="n">
-        <v>61.37</v>
+        <v>62.21</v>
       </c>
     </row>
     <row r="110">
@@ -8366,10 +8386,10 @@
         <v>90.05</v>
       </c>
       <c r="D110" s="5" t="n">
-        <v>105.19</v>
+        <v>106.64</v>
       </c>
       <c r="E110" s="5" t="n">
-        <v>128.95</v>
+        <v>130.72</v>
       </c>
     </row>
     <row r="111">
@@ -8385,10 +8405,10 @@
         <v>58.79</v>
       </c>
       <c r="D111" s="5" t="n">
-        <v>79.48999999999999</v>
+        <v>80.58</v>
       </c>
       <c r="E111" s="5" t="n">
-        <v>83.81</v>
+        <v>84.95999999999999</v>
       </c>
     </row>
     <row r="112">
@@ -8404,10 +8424,10 @@
         <v>60.96</v>
       </c>
       <c r="D112" s="5" t="n">
-        <v>75.90000000000001</v>
+        <v>76.94</v>
       </c>
       <c r="E112" s="5" t="n">
-        <v>86.51000000000001</v>
+        <v>87.7</v>
       </c>
     </row>
     <row r="113">
@@ -8423,10 +8443,10 @@
         <v>55</v>
       </c>
       <c r="D113" s="5" t="n">
-        <v>72.7</v>
+        <v>73.7</v>
       </c>
       <c r="E113" s="5" t="n">
-        <v>77.98999999999999</v>
+        <v>79.06</v>
       </c>
     </row>
     <row r="114">
@@ -8442,10 +8462,10 @@
         <v>108.73</v>
       </c>
       <c r="D114" s="5" t="n">
-        <v>109.34</v>
+        <v>110.85</v>
       </c>
       <c r="E114" s="5" t="n">
-        <v>154.04</v>
+        <v>156.16</v>
       </c>
     </row>
     <row r="115">
@@ -8461,10 +8481,10 @@
         <v>58.92</v>
       </c>
       <c r="D115" s="5" t="n">
-        <v>73.86</v>
+        <v>74.88</v>
       </c>
       <c r="E115" s="5" t="n">
-        <v>83.40000000000001</v>
+        <v>84.55</v>
       </c>
     </row>
     <row r="116">
@@ -8480,10 +8500,10 @@
         <v>65.31</v>
       </c>
       <c r="D116" s="5" t="n">
-        <v>76.73999999999999</v>
+        <v>77.79000000000001</v>
       </c>
       <c r="E116" s="5" t="n">
-        <v>92.34999999999999</v>
+        <v>93.62</v>
       </c>
     </row>
     <row r="117">
@@ -8499,10 +8519,10 @@
         <v>59.78</v>
       </c>
       <c r="D117" s="5" t="n">
-        <v>75.69</v>
+        <v>76.73</v>
       </c>
       <c r="E117" s="5" t="n">
-        <v>84.43000000000001</v>
+        <v>85.59</v>
       </c>
     </row>
     <row r="118">
@@ -8518,10 +8538,10 @@
         <v>60.03</v>
       </c>
       <c r="D118" s="5" t="n">
-        <v>73.8</v>
+        <v>74.81</v>
       </c>
       <c r="E118" s="5" t="n">
-        <v>84.69</v>
+        <v>85.84999999999999</v>
       </c>
     </row>
     <row r="119">
@@ -8537,10 +8557,10 @@
         <v>53.46</v>
       </c>
       <c r="D119" s="5" t="n">
-        <v>70.48</v>
+        <v>71.45</v>
       </c>
       <c r="E119" s="5" t="n">
-        <v>75.31999999999999</v>
+        <v>76.36</v>
       </c>
     </row>
     <row r="120">
@@ -8556,10 +8576,10 @@
         <v>61.01</v>
       </c>
       <c r="D120" s="5" t="n">
-        <v>77.19</v>
+        <v>78.25</v>
       </c>
       <c r="E120" s="5" t="n">
-        <v>85.84999999999999</v>
+        <v>87.03</v>
       </c>
     </row>
     <row r="121">
@@ -8575,10 +8595,10 @@
         <v>70.51000000000001</v>
       </c>
       <c r="D121" s="5" t="n">
-        <v>85.59</v>
+        <v>86.77</v>
       </c>
       <c r="E121" s="5" t="n">
-        <v>99.09999999999999</v>
+        <v>100.46</v>
       </c>
     </row>
     <row r="122">
@@ -8594,10 +8614,10 @@
         <v>62.4</v>
       </c>
       <c r="D122" s="5" t="n">
-        <v>81.68000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="E122" s="5" t="n">
-        <v>87.34</v>
+        <v>88.55</v>
       </c>
     </row>
     <row r="123">
@@ -8613,10 +8633,10 @@
         <v>57.79</v>
       </c>
       <c r="D123" s="5" t="n">
-        <v>75.45</v>
+        <v>76.48999999999999</v>
       </c>
       <c r="E123" s="5" t="n">
-        <v>80.56999999999999</v>
+        <v>81.67</v>
       </c>
     </row>
     <row r="124">
@@ -8632,10 +8652,10 @@
         <v>52.11</v>
       </c>
       <c r="D124" s="5" t="n">
-        <v>68.38</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="E124" s="5" t="n">
-        <v>72.36</v>
+        <v>73.34999999999999</v>
       </c>
     </row>
     <row r="125">
@@ -8651,10 +8671,10 @@
         <v>51.91</v>
       </c>
       <c r="D125" s="5" t="n">
-        <v>68.53</v>
+        <v>69.47</v>
       </c>
       <c r="E125" s="5" t="n">
-        <v>71.91</v>
+        <v>72.89</v>
       </c>
     </row>
     <row r="126">
@@ -8670,10 +8690,10 @@
         <v>49.47</v>
       </c>
       <c r="D126" s="5" t="n">
-        <v>64.62</v>
+        <v>65.51000000000001</v>
       </c>
       <c r="E126" s="5" t="n">
-        <v>68.36</v>
+        <v>69.3</v>
       </c>
     </row>
     <row r="127">
@@ -8689,10 +8709,10 @@
         <v>57.51</v>
       </c>
       <c r="D127" s="5" t="n">
-        <v>69.38</v>
+        <v>70.34</v>
       </c>
       <c r="E127" s="5" t="n">
-        <v>79.28</v>
+        <v>80.37</v>
       </c>
     </row>
     <row r="128">
@@ -8708,10 +8728,10 @@
         <v>105.62</v>
       </c>
       <c r="D128" s="5" t="n">
-        <v>99.65000000000001</v>
+        <v>101.03</v>
       </c>
       <c r="E128" s="5" t="n">
-        <v>145.32</v>
+        <v>147.32</v>
       </c>
     </row>
     <row r="129">
@@ -8727,10 +8747,10 @@
         <v>51.64</v>
       </c>
       <c r="D129" s="5" t="n">
-        <v>67.63</v>
+        <v>68.56</v>
       </c>
       <c r="E129" s="5" t="n">
-        <v>70.91</v>
+        <v>71.89</v>
       </c>
     </row>
     <row r="130">
@@ -8746,10 +8766,10 @@
         <v>50.99</v>
       </c>
       <c r="D130" s="5" t="n">
-        <v>62.99</v>
+        <v>63.85</v>
       </c>
       <c r="E130" s="5" t="n">
-        <v>69.88</v>
+        <v>70.84</v>
       </c>
     </row>
     <row r="131">
@@ -8765,10 +8785,10 @@
         <v>46.48</v>
       </c>
       <c r="D131" s="5" t="n">
-        <v>59.91</v>
+        <v>60.74</v>
       </c>
       <c r="E131" s="5" t="n">
-        <v>63.59</v>
+        <v>64.47</v>
       </c>
     </row>
     <row r="132">
@@ -8784,10 +8804,10 @@
         <v>53.42</v>
       </c>
       <c r="D132" s="5" t="n">
-        <v>65.84</v>
+        <v>66.73999999999999</v>
       </c>
       <c r="E132" s="5" t="n">
-        <v>72.97</v>
+        <v>73.97</v>
       </c>
     </row>
     <row r="133">
@@ -8803,10 +8823,10 @@
         <v>53.9</v>
       </c>
       <c r="D133" s="5" t="n">
-        <v>67.05</v>
+        <v>67.97</v>
       </c>
       <c r="E133" s="5" t="n">
-        <v>73.5</v>
+        <v>74.51000000000001</v>
       </c>
     </row>
     <row r="134">
@@ -8822,10 +8842,10 @@
         <v>43.69</v>
       </c>
       <c r="D134" s="5" t="n">
-        <v>52.55</v>
+        <v>53.27</v>
       </c>
       <c r="E134" s="5" t="n">
-        <v>59.49</v>
+        <v>60.31</v>
       </c>
     </row>
     <row r="135">
@@ -8841,10 +8861,10 @@
         <v>40.67</v>
       </c>
       <c r="D135" s="5" t="n">
-        <v>46.93</v>
+        <v>47.57</v>
       </c>
       <c r="E135" s="5" t="n">
-        <v>55.3</v>
+        <v>56.06</v>
       </c>
     </row>
     <row r="136">
@@ -8860,10 +8880,10 @@
         <v>42.07</v>
       </c>
       <c r="D136" s="5" t="n">
-        <v>49.24</v>
+        <v>49.91</v>
       </c>
       <c r="E136" s="5" t="n">
-        <v>57.13</v>
+        <v>57.91</v>
       </c>
     </row>
     <row r="137">
@@ -8879,10 +8899,10 @@
         <v>30.63</v>
       </c>
       <c r="D137" s="5" t="n">
-        <v>36.08</v>
+        <v>36.58</v>
       </c>
       <c r="E137" s="5" t="n">
-        <v>41.57</v>
+        <v>42.14</v>
       </c>
     </row>
     <row r="138">
@@ -8898,10 +8918,10 @@
         <v>34.46</v>
       </c>
       <c r="D138" s="5" t="n">
-        <v>38.73</v>
+        <v>39.26</v>
       </c>
       <c r="E138" s="5" t="n">
-        <v>46.73</v>
+        <v>47.38</v>
       </c>
     </row>
     <row r="139">
@@ -8917,10 +8937,10 @@
         <v>31.31</v>
       </c>
       <c r="D139" s="5" t="n">
-        <v>35.97</v>
+        <v>36.46</v>
       </c>
       <c r="E139" s="5" t="n">
-        <v>42.43</v>
+        <v>43.02</v>
       </c>
     </row>
     <row r="140">
@@ -8936,10 +8956,10 @@
         <v>33.61</v>
       </c>
       <c r="D140" s="5" t="n">
-        <v>35.35</v>
+        <v>35.84</v>
       </c>
       <c r="E140" s="5" t="n">
-        <v>45.52</v>
+        <v>46.15</v>
       </c>
     </row>
     <row r="141">
@@ -8955,10 +8975,10 @@
         <v>35.21</v>
       </c>
       <c r="D141" s="5" t="n">
-        <v>37.94</v>
+        <v>38.46</v>
       </c>
       <c r="E141" s="5" t="n">
-        <v>47.66</v>
+        <v>48.32</v>
       </c>
     </row>
     <row r="142">
@@ -8974,10 +8994,10 @@
         <v>31.79</v>
       </c>
       <c r="D142" s="5" t="n">
-        <v>34.91</v>
+        <v>35.39</v>
       </c>
       <c r="E142" s="5" t="n">
-        <v>43</v>
+        <v>43.6</v>
       </c>
     </row>
     <row r="143">
@@ -8993,10 +9013,10 @@
         <v>35.26</v>
       </c>
       <c r="D143" s="5" t="n">
-        <v>39.02</v>
+        <v>39.55</v>
       </c>
       <c r="E143" s="5" t="n">
-        <v>47.58</v>
+        <v>48.24</v>
       </c>
     </row>
     <row r="144">
@@ -9012,10 +9032,10 @@
         <v>38.41</v>
       </c>
       <c r="D144" s="5" t="n">
-        <v>40.19</v>
+        <v>40.74</v>
       </c>
       <c r="E144" s="5" t="n">
-        <v>51.71</v>
+        <v>52.42</v>
       </c>
     </row>
     <row r="145">
@@ -9031,10 +9051,10 @@
         <v>41.52</v>
       </c>
       <c r="D145" s="5" t="n">
-        <v>46.22</v>
+        <v>46.85</v>
       </c>
       <c r="E145" s="5" t="n">
-        <v>55.77</v>
+        <v>56.53</v>
       </c>
     </row>
     <row r="146">
@@ -9050,10 +9070,10 @@
         <v>42.82</v>
       </c>
       <c r="D146" s="5" t="n">
-        <v>46.61</v>
+        <v>47.26</v>
       </c>
       <c r="E146" s="5" t="n">
-        <v>57.44</v>
+        <v>58.23</v>
       </c>
     </row>
     <row r="147">
@@ -9069,10 +9089,10 @@
         <v>42.1</v>
       </c>
       <c r="D147" s="5" t="n">
-        <v>46.94</v>
+        <v>47.59</v>
       </c>
       <c r="E147" s="5" t="n">
-        <v>56.4</v>
+        <v>57.18</v>
       </c>
     </row>
     <row r="148">
@@ -9088,10 +9108,10 @@
         <v>50.84</v>
       </c>
       <c r="D148" s="5" t="n">
-        <v>59.61</v>
+        <v>60.43</v>
       </c>
       <c r="E148" s="5" t="n">
-        <v>68.02</v>
+        <v>68.95999999999999</v>
       </c>
     </row>
     <row r="149">
@@ -9107,10 +9127,10 @@
         <v>45.47</v>
       </c>
       <c r="D149" s="5" t="n">
-        <v>47.61</v>
+        <v>48.26</v>
       </c>
       <c r="E149" s="5" t="n">
-        <v>60.76</v>
+        <v>61.59</v>
       </c>
     </row>
     <row r="150">
@@ -9126,10 +9146,10 @@
         <v>45.23</v>
       </c>
       <c r="D150" s="5" t="n">
-        <v>46.6</v>
+        <v>47.24</v>
       </c>
       <c r="E150" s="5" t="n">
-        <v>60.36</v>
+        <v>61.19</v>
       </c>
     </row>
     <row r="151">
@@ -9145,10 +9165,10 @@
         <v>62.67</v>
       </c>
       <c r="D151" s="5" t="n">
-        <v>63.99</v>
+        <v>64.87</v>
       </c>
       <c r="E151" s="5" t="n">
-        <v>83.53</v>
+        <v>84.68000000000001</v>
       </c>
     </row>
     <row r="152">
@@ -9164,10 +9184,10 @@
         <v>72.90000000000001</v>
       </c>
       <c r="D152" s="5" t="n">
-        <v>62.62</v>
+        <v>63.48</v>
       </c>
       <c r="E152" s="5" t="n">
-        <v>97.23</v>
+        <v>98.56</v>
       </c>
     </row>
     <row r="153">
@@ -9183,10 +9203,10 @@
         <v>44.52</v>
       </c>
       <c r="D153" s="5" t="n">
-        <v>47.27</v>
+        <v>47.92</v>
       </c>
       <c r="E153" s="5" t="n">
-        <v>59.42</v>
+        <v>60.23</v>
       </c>
     </row>
     <row r="154">
@@ -9202,10 +9222,10 @@
         <v>59.65</v>
       </c>
       <c r="D154" s="5" t="n">
-        <v>61.28</v>
+        <v>62.13</v>
       </c>
       <c r="E154" s="5" t="n">
-        <v>79.66</v>
+        <v>80.76000000000001</v>
       </c>
     </row>
     <row r="155">
@@ -9221,10 +9241,10 @@
         <v>61.49</v>
       </c>
       <c r="D155" s="5" t="n">
-        <v>61.18</v>
+        <v>62.02</v>
       </c>
       <c r="E155" s="5" t="n">
-        <v>82</v>
+        <v>83.13</v>
       </c>
     </row>
     <row r="156">
@@ -9240,10 +9260,10 @@
         <v>76.45999999999999</v>
       </c>
       <c r="D156" s="5" t="n">
-        <v>72.22</v>
+        <v>73.22</v>
       </c>
       <c r="E156" s="5" t="n">
-        <v>101.81</v>
+        <v>103.21</v>
       </c>
     </row>
     <row r="157">
@@ -9259,10 +9279,10 @@
         <v>118.54</v>
       </c>
       <c r="D157" s="5" t="n">
-        <v>123.35</v>
+        <v>125.05</v>
       </c>
       <c r="E157" s="5" t="n">
-        <v>157.61</v>
+        <v>159.78</v>
       </c>
     </row>
     <row r="158">
@@ -9278,10 +9298,10 @@
         <v>86.77</v>
       </c>
       <c r="D158" s="5" t="n">
-        <v>85.75</v>
+        <v>86.93000000000001</v>
       </c>
       <c r="E158" s="5" t="n">
-        <v>115.1</v>
+        <v>116.69</v>
       </c>
     </row>
     <row r="159">
@@ -9297,10 +9317,10 @@
         <v>55.76</v>
       </c>
       <c r="D159" s="5" t="n">
-        <v>57.22</v>
+        <v>58.01</v>
       </c>
       <c r="E159" s="5" t="n">
-        <v>73.79000000000001</v>
+        <v>74.81</v>
       </c>
     </row>
     <row r="160">
@@ -9316,10 +9336,10 @@
         <v>48.5</v>
       </c>
       <c r="D160" s="5" t="n">
-        <v>54.16</v>
+        <v>54.91</v>
       </c>
       <c r="E160" s="5" t="n">
-        <v>64.04000000000001</v>
+        <v>64.92</v>
       </c>
     </row>
     <row r="161">
@@ -9335,10 +9355,10 @@
         <v>41.02</v>
       </c>
       <c r="D161" s="5" t="n">
-        <v>43.73</v>
+        <v>44.33</v>
       </c>
       <c r="E161" s="5" t="n">
-        <v>54.07</v>
+        <v>54.81</v>
       </c>
     </row>
     <row r="162">
@@ -9354,10 +9374,10 @@
         <v>46.93</v>
       </c>
       <c r="D162" s="5" t="n">
-        <v>47.46</v>
+        <v>48.11</v>
       </c>
       <c r="E162" s="5" t="n">
-        <v>61.75</v>
+        <v>62.6</v>
       </c>
     </row>
     <row r="163">
@@ -9373,10 +9393,10 @@
         <v>37.59</v>
       </c>
       <c r="D163" s="5" t="n">
-        <v>39.27</v>
+        <v>39.81</v>
       </c>
       <c r="E163" s="5" t="n">
-        <v>49.37</v>
+        <v>50.05</v>
       </c>
     </row>
     <row r="164">
@@ -9392,10 +9412,10 @@
         <v>81.03</v>
       </c>
       <c r="D164" s="5" t="n">
-        <v>81.36</v>
+        <v>82.48</v>
       </c>
       <c r="E164" s="5" t="n">
-        <v>106.27</v>
+        <v>107.73</v>
       </c>
     </row>
     <row r="165">
@@ -9411,10 +9431,10 @@
         <v>114.18</v>
       </c>
       <c r="D165" s="5" t="n">
-        <v>112.68</v>
+        <v>114.23</v>
       </c>
       <c r="E165" s="5" t="n">
-        <v>149.51</v>
+        <v>151.57</v>
       </c>
     </row>
     <row r="166">
@@ -9430,10 +9450,10 @@
         <v>112.64</v>
       </c>
       <c r="D166" s="5" t="n">
-        <v>118.49</v>
+        <v>120.12</v>
       </c>
       <c r="E166" s="5" t="n">
-        <v>147.27</v>
+        <v>149.3</v>
       </c>
     </row>
     <row r="167">
@@ -9449,10 +9469,10 @@
         <v>123.35</v>
       </c>
       <c r="D167" s="5" t="n">
-        <v>141.37</v>
+        <v>143.32</v>
       </c>
       <c r="E167" s="5" t="n">
-        <v>161.17</v>
+        <v>163.38</v>
       </c>
     </row>
     <row r="168">
@@ -9468,10 +9488,10 @@
         <v>123.09</v>
       </c>
       <c r="D168" s="5" t="n">
-        <v>140.95</v>
+        <v>142.89</v>
       </c>
       <c r="E168" s="5" t="n">
-        <v>160.72</v>
+        <v>162.93</v>
       </c>
     </row>
     <row r="169">
@@ -9487,10 +9507,10 @@
         <v>105</v>
       </c>
       <c r="D169" s="5" t="n">
-        <v>128.53</v>
+        <v>130.3</v>
       </c>
       <c r="E169" s="5" t="n">
-        <v>137.01</v>
+        <v>138.9</v>
       </c>
     </row>
     <row r="170">
@@ -9506,10 +9526,10 @@
         <v>131.48</v>
       </c>
       <c r="D170" s="5" t="n">
-        <v>152.86</v>
+        <v>154.96</v>
       </c>
       <c r="E170" s="5" t="n">
-        <v>171.22</v>
+        <v>173.57</v>
       </c>
     </row>
     <row r="171">
@@ -9525,10 +9545,10 @@
         <v>119.74</v>
       </c>
       <c r="D171" s="5" t="n">
-        <v>133.3</v>
+        <v>135.13</v>
       </c>
       <c r="E171" s="5" t="n">
-        <v>155.61</v>
+        <v>157.75</v>
       </c>
     </row>
     <row r="172">
@@ -9544,10 +9564,10 @@
         <v>89.62</v>
       </c>
       <c r="D172" s="5" t="n">
-        <v>103.02</v>
+        <v>104.43</v>
       </c>
       <c r="E172" s="5" t="n">
-        <v>116.23</v>
+        <v>117.83</v>
       </c>
     </row>
     <row r="173">
@@ -9563,10 +9583,10 @@
         <v>82.48</v>
       </c>
       <c r="D173" s="5" t="n">
-        <v>94.87</v>
+        <v>96.17</v>
       </c>
       <c r="E173" s="5" t="n">
-        <v>106.73</v>
+        <v>108.2</v>
       </c>
     </row>
     <row r="174">
@@ -9582,10 +9602,10 @@
         <v>112.43</v>
       </c>
       <c r="D174" s="5" t="n">
-        <v>123.36</v>
+        <v>125.06</v>
       </c>
       <c r="E174" s="5" t="n">
-        <v>145.17</v>
+        <v>147.16</v>
       </c>
     </row>
     <row r="175">
@@ -9601,10 +9621,10 @@
         <v>97.75</v>
       </c>
       <c r="D175" s="5" t="n">
-        <v>109.31</v>
+        <v>110.82</v>
       </c>
       <c r="E175" s="5" t="n">
-        <v>125.93</v>
+        <v>127.66</v>
       </c>
     </row>
     <row r="176">
@@ -9620,10 +9640,10 @@
         <v>183</v>
       </c>
       <c r="D176" s="5" t="n">
-        <v>171.71</v>
+        <v>174.07</v>
       </c>
       <c r="E176" s="5" t="n">
-        <v>235.42</v>
+        <v>238.65</v>
       </c>
     </row>
     <row r="177">
@@ -9639,10 +9659,10 @@
         <v>124.33</v>
       </c>
       <c r="D177" s="5" t="n">
-        <v>125.15</v>
+        <v>126.88</v>
       </c>
       <c r="E177" s="5" t="n">
-        <v>159.71</v>
+        <v>161.91</v>
       </c>
     </row>
     <row r="178">
@@ -9658,10 +9678,10 @@
         <v>82.25</v>
       </c>
       <c r="D178" s="5" t="n">
-        <v>97.5</v>
+        <v>98.84</v>
       </c>
       <c r="E178" s="5" t="n">
-        <v>105.5</v>
+        <v>106.95</v>
       </c>
     </row>
     <row r="179">
@@ -9677,10 +9697,10 @@
         <v>87.09</v>
       </c>
       <c r="D179" s="5" t="n">
-        <v>94.86</v>
+        <v>96.16</v>
       </c>
       <c r="E179" s="5" t="n">
-        <v>111.58</v>
+        <v>113.11</v>
       </c>
     </row>
     <row r="180">
@@ -9696,10 +9716,10 @@
         <v>95.98</v>
       </c>
       <c r="D180" s="5" t="n">
-        <v>102.1</v>
+        <v>103.51</v>
       </c>
       <c r="E180" s="5" t="n">
-        <v>122.82</v>
+        <v>124.51</v>
       </c>
     </row>
     <row r="181">
@@ -9715,10 +9735,10 @@
         <v>112.11</v>
       </c>
       <c r="D181" s="5" t="n">
-        <v>119.79</v>
+        <v>121.43</v>
       </c>
       <c r="E181" s="5" t="n">
-        <v>143.29</v>
+        <v>145.26</v>
       </c>
     </row>
     <row r="182">
@@ -9734,10 +9754,10 @@
         <v>88.33</v>
       </c>
       <c r="D182" s="5" t="n">
-        <v>89.47</v>
+        <v>90.7</v>
       </c>
       <c r="E182" s="5" t="n">
-        <v>112.73</v>
+        <v>114.28</v>
       </c>
     </row>
     <row r="183">
@@ -9753,10 +9773,10 @@
         <v>102.2</v>
       </c>
       <c r="D183" s="5" t="n">
-        <v>100.9</v>
+        <v>102.29</v>
       </c>
       <c r="E183" s="5" t="n">
-        <v>130.25</v>
+        <v>132.04</v>
       </c>
     </row>
     <row r="184">
@@ -9772,10 +9792,10 @@
         <v>108.02</v>
       </c>
       <c r="D184" s="5" t="n">
-        <v>118.16</v>
+        <v>119.79</v>
       </c>
       <c r="E184" s="5" t="n">
-        <v>137.47</v>
+        <v>139.36</v>
       </c>
     </row>
     <row r="185">
@@ -9791,10 +9811,10 @@
         <v>109.7</v>
       </c>
       <c r="D185" s="5" t="n">
-        <v>126.82</v>
+        <v>128.57</v>
       </c>
       <c r="E185" s="5" t="n">
-        <v>139.36</v>
+        <v>141.28</v>
       </c>
     </row>
     <row r="186">
@@ -9810,10 +9830,10 @@
         <v>105.48</v>
       </c>
       <c r="D186" s="5" t="n">
-        <v>124.08</v>
+        <v>125.79</v>
       </c>
       <c r="E186" s="5" t="n">
-        <v>133.77</v>
+        <v>135.61</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9849,10 @@
         <v>113.92</v>
       </c>
       <c r="D187" s="5" t="n">
-        <v>116.21</v>
+        <v>117.81</v>
       </c>
       <c r="E187" s="5" t="n">
-        <v>144.23</v>
+        <v>146.21</v>
       </c>
     </row>
     <row r="188">
@@ -9848,10 +9868,10 @@
         <v>423.33</v>
       </c>
       <c r="D188" s="5" t="n">
-        <v>316.94</v>
+        <v>321.3</v>
       </c>
       <c r="E188" s="5" t="n">
-        <v>535.97</v>
+        <v>543.34</v>
       </c>
     </row>
     <row r="189">
@@ -9867,10 +9887,10 @@
         <v>120.86</v>
       </c>
       <c r="D189" s="5" t="n">
-        <v>140.74</v>
+        <v>142.68</v>
       </c>
       <c r="E189" s="5" t="n">
-        <v>153.02</v>
+        <v>155.13</v>
       </c>
     </row>
     <row r="190">
@@ -9886,10 +9906,10 @@
         <v>177.81</v>
       </c>
       <c r="D190" s="5" t="n">
-        <v>166.01</v>
+        <v>168.29</v>
       </c>
       <c r="E190" s="5" t="n">
-        <v>225.14</v>
+        <v>228.24</v>
       </c>
     </row>
     <row r="191">
@@ -9905,10 +9925,10 @@
         <v>106.79</v>
       </c>
       <c r="D191" s="5" t="n">
-        <v>124.4</v>
+        <v>126.11</v>
       </c>
       <c r="E191" s="5" t="n">
-        <v>134.95</v>
+        <v>136.81</v>
       </c>
     </row>
     <row r="192">
@@ -9924,10 +9944,10 @@
         <v>104.25</v>
       </c>
       <c r="D192" s="5" t="n">
-        <v>115.9</v>
+        <v>117.5</v>
       </c>
       <c r="E192" s="5" t="n">
-        <v>131.48</v>
+        <v>133.29</v>
       </c>
     </row>
     <row r="193">
@@ -9943,10 +9963,10 @@
         <v>122.01</v>
       </c>
       <c r="D193" s="5" t="n">
-        <v>128.15</v>
+        <v>129.91</v>
       </c>
       <c r="E193" s="5" t="n">
-        <v>153.58</v>
+        <v>155.69</v>
       </c>
     </row>
     <row r="194">
@@ -9962,10 +9982,10 @@
         <v>105.02</v>
       </c>
       <c r="D194" s="5" t="n">
-        <v>107.95</v>
+        <v>109.43</v>
       </c>
       <c r="E194" s="5" t="n">
-        <v>131.94</v>
+        <v>133.76</v>
       </c>
     </row>
     <row r="195">
@@ -9981,10 +10001,10 @@
         <v>130.29</v>
       </c>
       <c r="D195" s="5" t="n">
-        <v>131.61</v>
+        <v>133.42</v>
       </c>
       <c r="E195" s="5" t="n">
-        <v>163.38</v>
+        <v>165.63</v>
       </c>
     </row>
     <row r="196">
@@ -10000,10 +10020,10 @@
         <v>121.93</v>
       </c>
       <c r="D196" s="5" t="n">
-        <v>131.12</v>
+        <v>132.93</v>
       </c>
       <c r="E196" s="5" t="n">
-        <v>152.61</v>
+        <v>154.71</v>
       </c>
     </row>
     <row r="197">
@@ -10019,10 +10039,10 @@
         <v>113.03</v>
       </c>
       <c r="D197" s="5" t="n">
-        <v>125.75</v>
+        <v>127.48</v>
       </c>
       <c r="E197" s="5" t="n">
-        <v>141.15</v>
+        <v>143.09</v>
       </c>
     </row>
     <row r="198">
@@ -10038,10 +10058,10 @@
         <v>69.79000000000001</v>
       </c>
       <c r="D198" s="5" t="n">
-        <v>84.7</v>
+        <v>85.87</v>
       </c>
       <c r="E198" s="5" t="n">
-        <v>86.95999999999999</v>
+        <v>88.15000000000001</v>
       </c>
     </row>
     <row r="199">
@@ -10057,10 +10077,10 @@
         <v>77.45999999999999</v>
       </c>
       <c r="D199" s="5" t="n">
-        <v>76.31999999999999</v>
+        <v>77.37</v>
       </c>
       <c r="E199" s="5" t="n">
-        <v>96.29000000000001</v>
+        <v>97.62</v>
       </c>
     </row>
     <row r="200">
@@ -10076,10 +10096,10 @@
         <v>255.88</v>
       </c>
       <c r="D200" s="5" t="n">
-        <v>177.48</v>
+        <v>179.93</v>
       </c>
       <c r="E200" s="5" t="n">
-        <v>317.7</v>
+        <v>322.07</v>
       </c>
     </row>
     <row r="201">
@@ -10095,10 +10115,10 @@
         <v>55.83</v>
       </c>
       <c r="D201" s="5" t="n">
-        <v>59.91</v>
+        <v>60.73</v>
       </c>
       <c r="E201" s="5" t="n">
-        <v>69.23</v>
+        <v>70.18000000000001</v>
       </c>
     </row>
     <row r="202">
@@ -10114,10 +10134,10 @@
         <v>50.47</v>
       </c>
       <c r="D202" s="5" t="n">
-        <v>53.63</v>
+        <v>54.37</v>
       </c>
       <c r="E202" s="5" t="n">
-        <v>62.51</v>
+        <v>63.37</v>
       </c>
     </row>
     <row r="203">
@@ -10133,10 +10153,10 @@
         <v>41.9</v>
       </c>
       <c r="D203" s="5" t="n">
-        <v>43.42</v>
+        <v>44.01</v>
       </c>
       <c r="E203" s="5" t="n">
-        <v>52.23</v>
+        <v>52.95</v>
       </c>
     </row>
     <row r="204">
@@ -10152,10 +10172,10 @@
         <v>47.04</v>
       </c>
       <c r="D204" s="5" t="n">
-        <v>48.04</v>
+        <v>48.7</v>
       </c>
       <c r="E204" s="5" t="n">
-        <v>59.02</v>
+        <v>59.83</v>
       </c>
     </row>
     <row r="205">
@@ -10171,10 +10191,10 @@
         <v>62.91</v>
       </c>
       <c r="D205" s="5" t="n">
-        <v>61.45</v>
+        <v>62.3</v>
       </c>
       <c r="E205" s="5" t="n">
-        <v>79.45</v>
+        <v>80.54000000000001</v>
       </c>
     </row>
     <row r="206">
@@ -10190,10 +10210,10 @@
         <v>75.01000000000001</v>
       </c>
       <c r="D206" s="5" t="n">
-        <v>79.90000000000001</v>
+        <v>81</v>
       </c>
       <c r="E206" s="5" t="n">
-        <v>94.23999999999999</v>
+        <v>95.54000000000001</v>
       </c>
     </row>
     <row r="207">
@@ -10209,10 +10229,10 @@
         <v>66.40000000000001</v>
       </c>
       <c r="D207" s="5" t="n">
-        <v>67.12</v>
+        <v>68.04000000000001</v>
       </c>
       <c r="E207" s="5" t="n">
-        <v>83</v>
+        <v>84.14</v>
       </c>
     </row>
     <row r="208">
@@ -10228,10 +10248,10 @@
         <v>39.08</v>
       </c>
       <c r="D208" s="5" t="n">
-        <v>43.09</v>
+        <v>43.68</v>
       </c>
       <c r="E208" s="5" t="n">
-        <v>48.6</v>
+        <v>49.27</v>
       </c>
     </row>
     <row r="209">
@@ -10247,10 +10267,10 @@
         <v>55.4</v>
       </c>
       <c r="D209" s="5" t="n">
-        <v>55.53</v>
+        <v>56.3</v>
       </c>
       <c r="E209" s="5" t="n">
-        <v>68.69</v>
+        <v>69.63</v>
       </c>
     </row>
     <row r="210">
@@ -10266,10 +10286,10 @@
         <v>49.88</v>
       </c>
       <c r="D210" s="5" t="n">
-        <v>54.48</v>
+        <v>55.23</v>
       </c>
       <c r="E210" s="5" t="n">
-        <v>61.66</v>
+        <v>62.51</v>
       </c>
     </row>
     <row r="211">
@@ -10285,10 +10305,10 @@
         <v>23.5</v>
       </c>
       <c r="D211" s="5" t="n">
-        <v>29.32</v>
+        <v>29.72</v>
       </c>
       <c r="E211" s="5" t="n">
-        <v>28.96</v>
+        <v>29.36</v>
       </c>
     </row>
     <row r="212">
@@ -10304,10 +10324,10 @@
         <v>20.68</v>
       </c>
       <c r="D212" s="5" t="n">
-        <v>28.07</v>
+        <v>28.46</v>
       </c>
       <c r="E212" s="5" t="n">
-        <v>25.44</v>
+        <v>25.79</v>
       </c>
     </row>
     <row r="213">
@@ -10323,10 +10343,10 @@
         <v>24.89</v>
       </c>
       <c r="D213" s="5" t="n">
-        <v>26.83</v>
+        <v>27.19</v>
       </c>
       <c r="E213" s="5" t="n">
-        <v>30.56</v>
+        <v>30.98</v>
       </c>
     </row>
     <row r="214">
@@ -10342,10 +10362,10 @@
         <v>32.84</v>
       </c>
       <c r="D214" s="5" t="n">
-        <v>37.2</v>
+        <v>37.71</v>
       </c>
       <c r="E214" s="5" t="n">
-        <v>40.24</v>
+        <v>40.79</v>
       </c>
     </row>
     <row r="215">
@@ -10361,10 +10381,10 @@
         <v>62.46</v>
       </c>
       <c r="D215" s="5" t="n">
-        <v>60.47</v>
+        <v>61.3</v>
       </c>
       <c r="E215" s="5" t="n">
-        <v>76.34999999999999</v>
+        <v>77.40000000000001</v>
       </c>
     </row>
     <row r="216">
@@ -10380,10 +10400,10 @@
         <v>114.98</v>
       </c>
       <c r="D216" s="5" t="n">
-        <v>88.81999999999999</v>
+        <v>90.04000000000001</v>
       </c>
       <c r="E216" s="5" t="n">
-        <v>140.21</v>
+        <v>142.14</v>
       </c>
     </row>
     <row r="217">
@@ -10399,10 +10419,10 @@
         <v>107.95</v>
       </c>
       <c r="D217" s="5" t="n">
-        <v>106.95</v>
+        <v>108.42</v>
       </c>
       <c r="E217" s="5" t="n">
-        <v>131.31</v>
+        <v>133.12</v>
       </c>
     </row>
     <row r="218">
@@ -10418,10 +10438,10 @@
         <v>126.87</v>
       </c>
       <c r="D218" s="5" t="n">
-        <v>111.26</v>
+        <v>112.79</v>
       </c>
       <c r="E218" s="5" t="n">
-        <v>153.89</v>
+        <v>156.01</v>
       </c>
     </row>
     <row r="219">
@@ -10437,10 +10457,10 @@
         <v>55.18</v>
       </c>
       <c r="D219" s="5" t="n">
-        <v>56.85</v>
+        <v>57.63</v>
       </c>
       <c r="E219" s="5" t="n">
-        <v>66.75</v>
+        <v>67.66</v>
       </c>
     </row>
     <row r="220">
@@ -10456,10 +10476,10 @@
         <v>33.73</v>
       </c>
       <c r="D220" s="5" t="n">
-        <v>33.44</v>
+        <v>33.9</v>
       </c>
       <c r="E220" s="5" t="n">
-        <v>40.69</v>
+        <v>41.24</v>
       </c>
     </row>
     <row r="221">
@@ -10475,10 +10495,10 @@
         <v>15.09</v>
       </c>
       <c r="D221" s="5" t="n">
-        <v>22.17</v>
+        <v>22.48</v>
       </c>
       <c r="E221" s="5" t="n">
-        <v>18.12</v>
+        <v>18.37</v>
       </c>
     </row>
     <row r="222">
@@ -10494,10 +10514,10 @@
         <v>40.78</v>
       </c>
       <c r="D222" s="5" t="n">
-        <v>41.89</v>
+        <v>42.46</v>
       </c>
       <c r="E222" s="5" t="n">
-        <v>48.77</v>
+        <v>49.45</v>
       </c>
     </row>
     <row r="223">
@@ -10513,10 +10533,10 @@
         <v>30.8</v>
       </c>
       <c r="D223" s="5" t="n">
-        <v>38.39</v>
+        <v>38.91</v>
       </c>
       <c r="E223" s="5" t="n">
-        <v>36.68</v>
+        <v>37.19</v>
       </c>
     </row>
     <row r="224">
@@ -10532,10 +10552,10 @@
         <v>75.01000000000001</v>
       </c>
       <c r="D224" s="5" t="n">
-        <v>71.92</v>
+        <v>72.91</v>
       </c>
       <c r="E224" s="5" t="n">
-        <v>88.7</v>
+        <v>89.92</v>
       </c>
     </row>
     <row r="225">
@@ -10551,10 +10571,10 @@
         <v>48.54</v>
       </c>
       <c r="D225" s="5" t="n">
-        <v>63.6</v>
+        <v>64.48</v>
       </c>
       <c r="E225" s="5" t="n">
-        <v>56.99</v>
+        <v>57.78</v>
       </c>
     </row>
     <row r="226">
@@ -10570,10 +10590,10 @@
         <v>56.47</v>
       </c>
       <c r="D226" s="5" t="n">
-        <v>63.86</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="E226" s="5" t="n">
-        <v>65.83</v>
+        <v>66.73999999999999</v>
       </c>
     </row>
     <row r="227">
@@ -10589,10 +10609,10 @@
         <v>168.15</v>
       </c>
       <c r="D227" s="5" t="n">
-        <v>164</v>
+        <v>166.25</v>
       </c>
       <c r="E227" s="5" t="n">
-        <v>194.87</v>
+        <v>197.55</v>
       </c>
     </row>
     <row r="228">
@@ -10608,10 +10628,10 @@
         <v>264.24</v>
       </c>
       <c r="D228" s="5" t="n">
-        <v>269.17</v>
+        <v>272.88</v>
       </c>
       <c r="E228" s="5" t="n">
-        <v>304.43</v>
+        <v>308.62</v>
       </c>
     </row>
     <row r="229">
@@ -10627,10 +10647,10 @@
         <v>375.96</v>
       </c>
       <c r="D229" s="5" t="n">
-        <v>339.58</v>
+        <v>344.25</v>
       </c>
       <c r="E229" s="5" t="n">
-        <v>430.6</v>
+        <v>436.52</v>
       </c>
     </row>
     <row r="230">
@@ -10646,10 +10666,10 @@
         <v>432</v>
       </c>
       <c r="D230" s="5" t="n">
-        <v>387.43</v>
+        <v>392.76</v>
       </c>
       <c r="E230" s="5" t="n">
-        <v>491.77</v>
+        <v>498.54</v>
       </c>
     </row>
     <row r="231">
@@ -10665,10 +10685,10 @@
         <v>137.33</v>
       </c>
       <c r="D231" s="5" t="n">
-        <v>136.92</v>
+        <v>138.8</v>
       </c>
       <c r="E231" s="5" t="n">
-        <v>155.38</v>
+        <v>157.52</v>
       </c>
     </row>
     <row r="232">
@@ -10684,10 +10704,10 @@
         <v>130.9</v>
       </c>
       <c r="D232" s="5" t="n">
-        <v>125.7</v>
+        <v>127.43</v>
       </c>
       <c r="E232" s="5" t="n">
-        <v>147.22</v>
+        <v>149.24</v>
       </c>
     </row>
     <row r="233">
@@ -10703,10 +10723,10 @@
         <v>97.36</v>
       </c>
       <c r="D233" s="5" t="n">
-        <v>110.55</v>
+        <v>112.07</v>
       </c>
       <c r="E233" s="5" t="n">
-        <v>108.83</v>
+        <v>110.32</v>
       </c>
     </row>
     <row r="234">
@@ -10722,10 +10742,10 @@
         <v>58.3</v>
       </c>
       <c r="D234" s="5" t="n">
-        <v>65.14</v>
+        <v>66.03</v>
       </c>
       <c r="E234" s="5" t="n">
-        <v>64.77</v>
+        <v>65.66</v>
       </c>
     </row>
     <row r="235">
@@ -10741,10 +10761,10 @@
         <v>11.57</v>
       </c>
       <c r="D235" s="5" t="n">
-        <v>34.54</v>
+        <v>35.02</v>
       </c>
       <c r="E235" s="5" t="n">
-        <v>12.78</v>
+        <v>12.95</v>
       </c>
     </row>
     <row r="236">
@@ -10760,10 +10780,10 @@
         <v>32.05</v>
       </c>
       <c r="D236" s="5" t="n">
-        <v>52.86</v>
+        <v>53.59</v>
       </c>
       <c r="E236" s="5" t="n">
-        <v>35.23</v>
+        <v>35.72</v>
       </c>
     </row>
     <row r="237">
@@ -10779,10 +10799,10 @@
         <v>55.29</v>
       </c>
       <c r="D237" s="5" t="n">
-        <v>63.48</v>
+        <v>64.36</v>
       </c>
       <c r="E237" s="5" t="n">
-        <v>60.51</v>
+        <v>61.34</v>
       </c>
     </row>
     <row r="238">
@@ -10798,10 +10818,10 @@
         <v>54.59</v>
       </c>
       <c r="D238" s="5" t="n">
-        <v>67.56999999999999</v>
+        <v>68.5</v>
       </c>
       <c r="E238" s="5" t="n">
-        <v>59.48</v>
+        <v>60.29</v>
       </c>
     </row>
     <row r="239">
@@ -10817,10 +10837,10 @@
         <v>86.78</v>
       </c>
       <c r="D239" s="5" t="n">
-        <v>90.84</v>
+        <v>92.09</v>
       </c>
       <c r="E239" s="5" t="n">
-        <v>94.28</v>
+        <v>95.56999999999999</v>
       </c>
     </row>
     <row r="240">
@@ -10836,10 +10856,10 @@
         <v>145.97</v>
       </c>
       <c r="D240" s="5" t="n">
-        <v>137.74</v>
+        <v>139.64</v>
       </c>
       <c r="E240" s="5" t="n">
-        <v>158.13</v>
+        <v>160.3</v>
       </c>
     </row>
     <row r="241">
@@ -10855,10 +10875,10 @@
         <v>85.79000000000001</v>
       </c>
       <c r="D241" s="5" t="n">
-        <v>58.9</v>
+        <v>59.71</v>
       </c>
       <c r="E241" s="5" t="n">
-        <v>92.67</v>
+        <v>93.95</v>
       </c>
     </row>
     <row r="242">
@@ -10874,10 +10894,10 @@
         <v>76.38</v>
       </c>
       <c r="D242" s="5" t="n">
-        <v>59.41</v>
+        <v>60.23</v>
       </c>
       <c r="E242" s="5" t="n">
-        <v>82.19</v>
+        <v>83.31999999999999</v>
       </c>
     </row>
     <row r="243">
@@ -10893,10 +10913,10 @@
         <v>80.04000000000001</v>
       </c>
       <c r="D243" s="5" t="n">
-        <v>69.31</v>
+        <v>70.27</v>
       </c>
       <c r="E243" s="5" t="n">
-        <v>85.8</v>
+        <v>86.98</v>
       </c>
     </row>
     <row r="244">
@@ -10912,10 +10932,10 @@
         <v>28.16</v>
       </c>
       <c r="D244" s="5" t="n">
-        <v>28.1</v>
+        <v>28.48</v>
       </c>
       <c r="E244" s="5" t="n">
-        <v>30.07</v>
+        <v>30.49</v>
       </c>
     </row>
     <row r="245">
@@ -10931,10 +10951,10 @@
         <v>15.14</v>
       </c>
       <c r="D245" s="5" t="n">
-        <v>18.32</v>
+        <v>18.57</v>
       </c>
       <c r="E245" s="5" t="n">
-        <v>16.13</v>
+        <v>16.36</v>
       </c>
     </row>
     <row r="246">
@@ -10950,10 +10970,10 @@
         <v>31.79</v>
       </c>
       <c r="D246" s="5" t="n">
-        <v>37.16</v>
+        <v>37.67</v>
       </c>
       <c r="E246" s="5" t="n">
-        <v>33.81</v>
+        <v>34.27</v>
       </c>
     </row>
     <row r="247">
@@ -10969,10 +10989,10 @@
         <v>25.23</v>
       </c>
       <c r="D247" s="5" t="n">
-        <v>26.84</v>
+        <v>27.21</v>
       </c>
       <c r="E247" s="5" t="n">
-        <v>26.78</v>
+        <v>27.14</v>
       </c>
     </row>
     <row r="248">
@@ -10988,10 +11008,10 @@
         <v>17.65</v>
       </c>
       <c r="D248" s="5" t="n">
-        <v>23.38</v>
+        <v>23.7</v>
       </c>
       <c r="E248" s="5" t="n">
-        <v>18.67</v>
+        <v>18.93</v>
       </c>
     </row>
     <row r="249">
@@ -11007,10 +11027,10 @@
         <v>133.13</v>
       </c>
       <c r="D249" s="5" t="n">
-        <v>87.48</v>
+        <v>88.68000000000001</v>
       </c>
       <c r="E249" s="5" t="n">
-        <v>140.41</v>
+        <v>142.34</v>
       </c>
     </row>
     <row r="250">
@@ -11026,10 +11046,10 @@
         <v>46.25</v>
       </c>
       <c r="D250" s="5" t="n">
-        <v>54.67</v>
+        <v>55.42</v>
       </c>
       <c r="E250" s="5" t="n">
-        <v>48.63</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="251">
@@ -11045,10 +11065,10 @@
         <v>80.23</v>
       </c>
       <c r="D251" s="5" t="n">
-        <v>88.84999999999999</v>
+        <v>90.08</v>
       </c>
       <c r="E251" s="5" t="n">
-        <v>84.06999999999999</v>
+        <v>85.22</v>
       </c>
     </row>
     <row r="252">
@@ -11064,10 +11084,10 @@
         <v>146.58</v>
       </c>
       <c r="D252" s="5" t="n">
-        <v>138.84</v>
+        <v>140.75</v>
       </c>
       <c r="E252" s="5" t="n">
-        <v>153.05</v>
+        <v>155.16</v>
       </c>
     </row>
     <row r="253">
@@ -11083,10 +11103,10 @@
         <v>198.82</v>
       </c>
       <c r="D253" s="5" t="n">
-        <v>170.89</v>
+        <v>173.24</v>
       </c>
       <c r="E253" s="5" t="n">
-        <v>206.88</v>
+        <v>209.73</v>
       </c>
     </row>
     <row r="254">
@@ -11102,10 +11122,10 @@
         <v>191.83</v>
       </c>
       <c r="D254" s="5" t="n">
-        <v>155.08</v>
+        <v>157.21</v>
       </c>
       <c r="E254" s="5" t="n">
-        <v>199.47</v>
+        <v>202.21</v>
       </c>
     </row>
     <row r="255">
@@ -11121,10 +11141,10 @@
         <v>216.14</v>
       </c>
       <c r="D255" s="5" t="n">
-        <v>149</v>
+        <v>151.05</v>
       </c>
       <c r="E255" s="5" t="n">
-        <v>224.58</v>
+        <v>227.67</v>
       </c>
     </row>
     <row r="256">
@@ -11140,10 +11160,10 @@
         <v>26.5</v>
       </c>
       <c r="D256" s="5" t="n">
-        <v>18.06</v>
+        <v>18.3</v>
       </c>
       <c r="E256" s="5" t="n">
-        <v>27.51</v>
+        <v>27.89</v>
       </c>
     </row>
     <row r="257">
@@ -11159,10 +11179,10 @@
         <v>10.18</v>
       </c>
       <c r="D257" s="5" t="n">
-        <v>21.13</v>
+        <v>21.42</v>
       </c>
       <c r="E257" s="5" t="n">
-        <v>10.56</v>
+        <v>10.71</v>
       </c>
     </row>
     <row r="258">
@@ -11178,10 +11198,10 @@
         <v>52.94</v>
       </c>
       <c r="D258" s="5" t="n">
-        <v>66.45</v>
+        <v>67.36</v>
       </c>
       <c r="E258" s="5" t="n">
-        <v>54.9</v>
+        <v>55.65</v>
       </c>
     </row>
     <row r="259">
@@ -11197,10 +11217,10 @@
         <v>39.93</v>
       </c>
       <c r="D259" s="5" t="n">
-        <v>54.14</v>
+        <v>54.89</v>
       </c>
       <c r="E259" s="5" t="n">
-        <v>41.38</v>
+        <v>41.95</v>
       </c>
     </row>
     <row r="260">
@@ -11216,10 +11236,10 @@
         <v>23.72</v>
       </c>
       <c r="D260" s="5" t="n">
-        <v>49.95</v>
+        <v>50.64</v>
       </c>
       <c r="E260" s="5" t="n">
-        <v>24.5</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="261">
@@ -11235,10 +11255,10 @@
         <v>76.73</v>
       </c>
       <c r="D261" s="5" t="n">
-        <v>70.59999999999999</v>
+        <v>71.56999999999999</v>
       </c>
       <c r="E261" s="5" t="n">
-        <v>79.03</v>
+        <v>80.11</v>
       </c>
     </row>
     <row r="262">
@@ -11254,10 +11274,10 @@
         <v>62.93</v>
       </c>
       <c r="D262" s="5" t="n">
-        <v>63.41</v>
+        <v>64.28</v>
       </c>
       <c r="E262" s="5" t="n">
-        <v>64.62</v>
+        <v>65.51000000000001</v>
       </c>
     </row>
     <row r="263">
@@ -11273,10 +11293,10 @@
         <v>70.56</v>
       </c>
       <c r="D263" s="5" t="n">
-        <v>76.56999999999999</v>
+        <v>77.63</v>
       </c>
       <c r="E263" s="5" t="n">
-        <v>72.27</v>
+        <v>73.27</v>
       </c>
     </row>
     <row r="264">
@@ -11292,10 +11312,10 @@
         <v>93.92</v>
       </c>
       <c r="D264" s="5" t="n">
-        <v>79.75</v>
+        <v>80.84</v>
       </c>
       <c r="E264" s="5" t="n">
-        <v>95.95999999999999</v>
+        <v>97.28</v>
       </c>
     </row>
     <row r="265">
@@ -11311,10 +11331,10 @@
         <v>463.18</v>
       </c>
       <c r="D265" s="5" t="n">
-        <v>269.68</v>
+        <v>273.39</v>
       </c>
       <c r="E265" s="5" t="n">
-        <v>472.07</v>
+        <v>478.57</v>
       </c>
     </row>
     <row r="266">
@@ -11330,10 +11350,10 @@
         <v>107.96</v>
       </c>
       <c r="D266" s="5" t="n">
-        <v>83.34</v>
+        <v>84.48999999999999</v>
       </c>
       <c r="E266" s="5" t="n">
-        <v>109.55</v>
+        <v>111.06</v>
       </c>
     </row>
     <row r="267">
@@ -11349,10 +11369,10 @@
         <v>107.79</v>
       </c>
       <c r="D267" s="5" t="n">
-        <v>94.15000000000001</v>
+        <v>95.45</v>
       </c>
       <c r="E267" s="5" t="n">
-        <v>108.9</v>
+        <v>110.4</v>
       </c>
     </row>
     <row r="268">
@@ -11368,10 +11388,10 @@
         <v>61.8</v>
       </c>
       <c r="D268" s="5" t="n">
-        <v>55.6</v>
+        <v>56.36</v>
       </c>
       <c r="E268" s="5" t="n">
-        <v>62.17</v>
+        <v>63.02</v>
       </c>
     </row>
     <row r="269">
@@ -11387,10 +11407,10 @@
         <v>45.13</v>
       </c>
       <c r="D269" s="5" t="n">
-        <v>51.57</v>
+        <v>52.28</v>
       </c>
       <c r="E269" s="5" t="n">
-        <v>45.31</v>
+        <v>45.93</v>
       </c>
     </row>
     <row r="270">
@@ -11406,10 +11426,10 @@
         <v>13.79</v>
       </c>
       <c r="D270" s="5" t="n">
-        <v>31.98</v>
+        <v>32.42</v>
       </c>
       <c r="E270" s="5" t="n">
-        <v>13.82</v>
+        <v>14.01</v>
       </c>
     </row>
     <row r="271">
@@ -11425,10 +11445,10 @@
         <v>16.99</v>
       </c>
       <c r="D271" s="5" t="n">
-        <v>27.51</v>
+        <v>27.89</v>
       </c>
       <c r="E271" s="5" t="n">
-        <v>16.99</v>
+        <v>17.22</v>
       </c>
     </row>
     <row r="272">
@@ -11444,10 +11464,10 @@
         <v>43.74</v>
       </c>
       <c r="D272" s="5" t="n">
-        <v>38.55</v>
+        <v>38.9</v>
       </c>
       <c r="E272" s="5" t="n">
-        <v>43.74</v>
+        <v>44.14</v>
       </c>
     </row>
     <row r="273">
@@ -11463,10 +11483,10 @@
         <v>40.2</v>
       </c>
       <c r="D273" s="5" t="n">
-        <v>45.06</v>
+        <v>45.26</v>
       </c>
       <c r="E273" s="5" t="n">
-        <v>40.2</v>
+        <v>40.38</v>
       </c>
     </row>
     <row r="274">
@@ -11507,8 +11527,27 @@
         <v>39.73</v>
       </c>
     </row>
+    <row r="276">
+      <c r="A276" s="4" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="B276" s="5" t="n">
+        <v>42.63</v>
+      </c>
+      <c r="C276" s="5" t="n">
+        <v>44.24</v>
+      </c>
+      <c r="D276" s="5" t="n">
+        <v>42.63</v>
+      </c>
+      <c r="E276" s="5" t="n">
+        <v>44.24</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B275">
+  <conditionalFormatting sqref="B2:B276">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -11520,7 +11559,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C275">
+  <conditionalFormatting sqref="C2:C276">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -11532,7 +11571,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D275">
+  <conditionalFormatting sqref="D2:D276">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -11544,7 +11583,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E275">
+  <conditionalFormatting sqref="E2:E276">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>

--- a/outputs/VIC_historical_prices.xlsx
+++ b/outputs/VIC_historical_prices.xlsx
@@ -528,16 +528,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>67.18000000000001</v>
+        <v>48.54</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>85.73999999999999</v>
+        <v>50.57</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>68.58</v>
+        <v>49.21</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>87.76000000000001</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="6">
@@ -547,16 +547,16 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>72.84999999999999</v>
+        <v>67.72</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>87.20999999999999</v>
+        <v>80.64</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>75.48</v>
+        <v>69.95999999999999</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>90.41</v>
+        <v>83.38</v>
       </c>
     </row>
     <row r="7">
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>66.70999999999999</v>
+        <v>66.33</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>79.43000000000001</v>
+        <v>78.19</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>69.78</v>
+        <v>69.26000000000001</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>83.15000000000001</v>
+        <v>81.68000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -585,16 +585,16 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>78.73</v>
+        <v>77.95</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>91.67</v>
+        <v>90.56</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>86.73999999999999</v>
+        <v>85.62</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>101.02</v>
+        <v>99.48</v>
       </c>
     </row>
     <row r="9">
@@ -604,22 +604,22 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>78.20999999999999</v>
+        <v>77.78</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>94.09999999999999</v>
+        <v>93.45999999999999</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>93.56999999999999</v>
+        <v>92.87</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>112.85</v>
+        <v>111.86</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Data through: May 2026</t>
+          <t>Data through: Jun 2026</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F276"/>
+  <dimension ref="A1:F277"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6273,6 +6273,26 @@
       </c>
       <c r="F276" s="7" t="inlineStr"/>
     </row>
+    <row r="277">
+      <c r="A277" s="4" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="B277" s="5" t="n">
+        <v>40.95</v>
+      </c>
+      <c r="C277" s="5" t="n">
+        <v>41.06</v>
+      </c>
+      <c r="D277" s="5" t="n">
+        <v>40.95</v>
+      </c>
+      <c r="E277" s="5" t="n">
+        <v>41.06</v>
+      </c>
+      <c r="F277" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6284,7 +6304,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E276"/>
+  <dimension ref="A1:E277"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -11546,8 +11566,27 @@
         <v>44.24</v>
       </c>
     </row>
+    <row r="277">
+      <c r="A277" s="4" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="B277" s="5" t="n">
+        <v>40.95</v>
+      </c>
+      <c r="C277" s="5" t="n">
+        <v>41.06</v>
+      </c>
+      <c r="D277" s="5" t="n">
+        <v>40.95</v>
+      </c>
+      <c r="E277" s="5" t="n">
+        <v>41.06</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B276">
+  <conditionalFormatting sqref="B2:B277">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -11559,7 +11598,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C276">
+  <conditionalFormatting sqref="C2:C277">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -11571,7 +11610,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D276">
+  <conditionalFormatting sqref="D2:D277">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -11583,7 +11622,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E276">
+  <conditionalFormatting sqref="E2:E277">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>

--- a/outputs/VIC_historical_prices.xlsx
+++ b/outputs/VIC_historical_prices.xlsx
@@ -528,16 +528,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>48.54</v>
+        <v>47.98</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>50.57</v>
+        <v>50.78</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>49.21</v>
+        <v>48.45</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>51.3</v>
+        <v>51.25</v>
       </c>
     </row>
     <row r="6">
@@ -547,16 +547,16 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>67.72</v>
+        <v>64.64</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>80.64</v>
+        <v>77.25</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>69.95999999999999</v>
+        <v>66.55</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>83.38</v>
+        <v>79.56</v>
       </c>
     </row>
     <row r="7">
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>66.33</v>
+        <v>66.89</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>78.19</v>
+        <v>79.14</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>69.26000000000001</v>
+        <v>69.68000000000001</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>81.68000000000001</v>
+        <v>82.44</v>
       </c>
     </row>
     <row r="8">
@@ -585,16 +585,16 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>77.95</v>
+        <v>77.67</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>90.56</v>
+        <v>90.29000000000001</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>85.62</v>
+        <v>84.98999999999999</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>99.48</v>
+        <v>98.72</v>
       </c>
     </row>
     <row r="9">
@@ -604,22 +604,22 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>77.78</v>
+        <v>77.87</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>93.45999999999999</v>
+        <v>93.66</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>92.87</v>
+        <v>92.77</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>111.86</v>
+        <v>111.81</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Data through: Jun 2026</t>
+          <t>Data through: Jul 2026</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F277"/>
+  <dimension ref="A1:F278"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6293,6 +6293,26 @@
       </c>
       <c r="F277" s="7" t="inlineStr"/>
     </row>
+    <row r="278">
+      <c r="A278" s="4" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="B278" s="5" t="n">
+        <v>75.33</v>
+      </c>
+      <c r="C278" s="5" t="n">
+        <v>110.53</v>
+      </c>
+      <c r="D278" s="5" t="n">
+        <v>75.33</v>
+      </c>
+      <c r="E278" s="5" t="n">
+        <v>110.53</v>
+      </c>
+      <c r="F278" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6304,7 +6324,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E277"/>
+  <dimension ref="A1:E278"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -11585,8 +11605,27 @@
         <v>41.06</v>
       </c>
     </row>
+    <row r="278">
+      <c r="A278" s="4" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="B278" s="5" t="n">
+        <v>75.33</v>
+      </c>
+      <c r="C278" s="5" t="n">
+        <v>110.53</v>
+      </c>
+      <c r="D278" s="5" t="n">
+        <v>75.33</v>
+      </c>
+      <c r="E278" s="5" t="n">
+        <v>110.53</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B277">
+  <conditionalFormatting sqref="B2:B278">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -11598,7 +11637,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C277">
+  <conditionalFormatting sqref="C2:C278">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -11610,7 +11649,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D277">
+  <conditionalFormatting sqref="D2:D278">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -11622,7 +11661,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E277">
+  <conditionalFormatting sqref="E2:E278">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>

--- a/outputs/VIC_historical_prices.xlsx
+++ b/outputs/VIC_historical_prices.xlsx
@@ -528,16 +528,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>47.98</v>
+        <v>45.38</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>50.78</v>
+        <v>48.52</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>48.45</v>
+        <v>45.84</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>51.25</v>
+        <v>48.93</v>
       </c>
     </row>
     <row r="6">
@@ -547,16 +547,16 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>64.64</v>
+        <v>61.25</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>77.25</v>
+        <v>71.61</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>66.55</v>
+        <v>63.17</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>79.56</v>
+        <v>73.81</v>
       </c>
     </row>
     <row r="7">
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>66.89</v>
+        <v>66.81999999999999</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>79.14</v>
+        <v>79.15000000000001</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>69.68000000000001</v>
+        <v>69.83</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>82.44</v>
+        <v>82.70999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -585,16 +585,16 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>77.67</v>
+        <v>77.92</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>90.29000000000001</v>
+        <v>90.70999999999999</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>84.98999999999999</v>
+        <v>85.56</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>98.72</v>
+        <v>99.51000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -604,22 +604,22 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>77.87</v>
+        <v>78.03</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>93.66</v>
+        <v>93.86</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>92.77</v>
+        <v>93.34999999999999</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>111.81</v>
+        <v>112.51</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Data through: Jul 2026</t>
+          <t>Data through: Aug 2026</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F278"/>
+  <dimension ref="A1:F279"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -690,10 +690,10 @@
         <v>32.99</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>47.61</v>
+        <v>47.9</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>61.31</v>
+        <v>61.68</v>
       </c>
       <c r="F2" s="7" t="inlineStr"/>
     </row>
@@ -710,10 +710,10 @@
         <v>23.45</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>37.38</v>
+        <v>37.6</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>43.5</v>
+        <v>43.76</v>
       </c>
       <c r="F3" s="7" t="inlineStr"/>
     </row>
@@ -730,10 +730,10 @@
         <v>25.19</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>38.38</v>
+        <v>38.61</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>46.64</v>
+        <v>46.92</v>
       </c>
       <c r="F4" s="7" t="inlineStr"/>
     </row>
@@ -750,10 +750,10 @@
         <v>25.19</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>38.33</v>
+        <v>38.56</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>46.56</v>
+        <v>46.84</v>
       </c>
       <c r="F5" s="7" t="inlineStr"/>
     </row>
@@ -770,10 +770,10 @@
         <v>26.23</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>39.08</v>
+        <v>39.31</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>48.39</v>
+        <v>48.68</v>
       </c>
       <c r="F6" s="7" t="inlineStr"/>
     </row>
@@ -790,10 +790,10 @@
         <v>34.01</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>45.99</v>
+        <v>46.26</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>62.64</v>
+        <v>63.01</v>
       </c>
       <c r="F7" s="7" t="inlineStr"/>
     </row>
@@ -810,10 +810,10 @@
         <v>30.37</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>41.35</v>
+        <v>41.6</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>55.77</v>
+        <v>56.1</v>
       </c>
       <c r="F8" s="7" t="inlineStr"/>
     </row>
@@ -830,10 +830,10 @@
         <v>48.76</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>70.70999999999999</v>
+        <v>71.13</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>89.27</v>
+        <v>89.81</v>
       </c>
       <c r="F9" s="7" t="inlineStr"/>
     </row>
@@ -850,10 +850,10 @@
         <v>28.54</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>39.21</v>
+        <v>39.45</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>52.1</v>
+        <v>52.41</v>
       </c>
       <c r="F10" s="7" t="inlineStr"/>
     </row>
@@ -870,10 +870,10 @@
         <v>36.99</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>53.7</v>
+        <v>54.02</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>67.42</v>
+        <v>67.83</v>
       </c>
       <c r="F11" s="7" t="inlineStr"/>
     </row>
@@ -890,10 +890,10 @@
         <v>39.67</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>56.94</v>
+        <v>57.29</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>72.19</v>
+        <v>72.63</v>
       </c>
       <c r="F12" s="7" t="inlineStr"/>
     </row>
@@ -910,10 +910,10 @@
         <v>34.73</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>52.02</v>
+        <v>52.33</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>63.11</v>
+        <v>63.48</v>
       </c>
       <c r="F13" s="7" t="inlineStr"/>
     </row>
@@ -930,10 +930,10 @@
         <v>43.7</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>56.92</v>
+        <v>57.26</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>79.3</v>
+        <v>79.77</v>
       </c>
       <c r="F14" s="7" t="inlineStr"/>
     </row>
@@ -950,10 +950,10 @@
         <v>27.37</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>40.86</v>
+        <v>41.11</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>49.6</v>
+        <v>49.89</v>
       </c>
       <c r="F15" s="7" t="inlineStr"/>
     </row>
@@ -970,10 +970,10 @@
         <v>31.48</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>49.22</v>
+        <v>49.52</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>56.97</v>
+        <v>57.31</v>
       </c>
       <c r="F16" s="7" t="inlineStr"/>
     </row>
@@ -990,10 +990,10 @@
         <v>70.45</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>81.01000000000001</v>
+        <v>81.48999999999999</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>127.16</v>
+        <v>127.93</v>
       </c>
       <c r="F17" s="7" t="inlineStr"/>
     </row>
@@ -1010,10 +1010,10 @@
         <v>44.55</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>64.2</v>
+        <v>64.59</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>80.20999999999999</v>
+        <v>80.69</v>
       </c>
       <c r="F18" s="7" t="inlineStr"/>
     </row>
@@ -1030,10 +1030,10 @@
         <v>33</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>49.13</v>
+        <v>49.43</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>59.26</v>
+        <v>59.62</v>
       </c>
       <c r="F19" s="7" t="inlineStr"/>
     </row>
@@ -1050,10 +1050,10 @@
         <v>29.72</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>40.93</v>
+        <v>41.17</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>53.25</v>
+        <v>53.57</v>
       </c>
       <c r="F20" s="7" t="inlineStr"/>
     </row>
@@ -1070,10 +1070,10 @@
         <v>27.43</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>39.03</v>
+        <v>39.26</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>49.04</v>
+        <v>49.34</v>
       </c>
       <c r="F21" s="7" t="inlineStr"/>
     </row>
@@ -1090,10 +1090,10 @@
         <v>21.15</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>33.36</v>
+        <v>33.56</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>37.73</v>
+        <v>37.96</v>
       </c>
       <c r="F22" s="7" t="inlineStr"/>
     </row>
@@ -1110,10 +1110,10 @@
         <v>37.8</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>54.53</v>
+        <v>54.86</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>67.3</v>
+        <v>67.7</v>
       </c>
       <c r="F23" s="7" t="inlineStr"/>
     </row>
@@ -1130,10 +1130,10 @@
         <v>29.2</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>43.64</v>
+        <v>43.9</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>51.88</v>
+        <v>52.19</v>
       </c>
       <c r="F24" s="7" t="inlineStr"/>
     </row>
@@ -1150,10 +1150,10 @@
         <v>27.29</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>41.74</v>
+        <v>41.99</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>48.39</v>
+        <v>48.68</v>
       </c>
       <c r="F25" s="7" t="inlineStr"/>
     </row>
@@ -1170,10 +1170,10 @@
         <v>32.37</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>46.86</v>
+        <v>47.14</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>57.21</v>
+        <v>57.56</v>
       </c>
       <c r="F26" s="7" t="inlineStr"/>
     </row>
@@ -1190,10 +1190,10 @@
         <v>40.25</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>52.85</v>
+        <v>53.17</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>70.91</v>
+        <v>71.33</v>
       </c>
       <c r="F27" s="7" t="inlineStr"/>
     </row>
@@ -1210,10 +1210,10 @@
         <v>37.44</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>51.17</v>
+        <v>51.47</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>65.73999999999999</v>
+        <v>66.13</v>
       </c>
       <c r="F28" s="7" t="inlineStr"/>
     </row>
@@ -1230,10 +1230,10 @@
         <v>28.49</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>39.68</v>
+        <v>39.92</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>49.94</v>
+        <v>50.24</v>
       </c>
       <c r="F29" s="7" t="inlineStr"/>
     </row>
@@ -1250,10 +1250,10 @@
         <v>46.39</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>53.72</v>
+        <v>54.04</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>81.17</v>
+        <v>81.66</v>
       </c>
       <c r="F30" s="7" t="inlineStr"/>
     </row>
@@ -1270,10 +1270,10 @@
         <v>49.23</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>59.81</v>
+        <v>60.17</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>86</v>
+        <v>86.51000000000001</v>
       </c>
       <c r="F31" s="7" t="inlineStr"/>
     </row>
@@ -1290,10 +1290,10 @@
         <v>88.63</v>
       </c>
       <c r="D32" s="5" t="n">
-        <v>93.08</v>
+        <v>93.64</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>154.38</v>
+        <v>155.3</v>
       </c>
       <c r="F32" s="7" t="inlineStr"/>
     </row>
@@ -1310,10 +1310,10 @@
         <v>105.51</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>97.27</v>
+        <v>97.84999999999999</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>183.26</v>
+        <v>184.36</v>
       </c>
       <c r="F33" s="7" t="inlineStr"/>
     </row>
@@ -1330,10 +1330,10 @@
         <v>29.33</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>40.46</v>
+        <v>40.7</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>50.8</v>
+        <v>51.1</v>
       </c>
       <c r="F34" s="7" t="inlineStr"/>
     </row>
@@ -1350,10 +1350,10 @@
         <v>27.86</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>38.92</v>
+        <v>39.15</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>48</v>
+        <v>48.29</v>
       </c>
       <c r="F35" s="7" t="inlineStr"/>
     </row>
@@ -1370,10 +1370,10 @@
         <v>37.94</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>48.42</v>
+        <v>48.71</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>65.02</v>
+        <v>65.41</v>
       </c>
       <c r="F36" s="7" t="inlineStr"/>
     </row>
@@ -1390,10 +1390,10 @@
         <v>42.49</v>
       </c>
       <c r="D37" s="5" t="n">
-        <v>59.01</v>
+        <v>59.36</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>72.44</v>
+        <v>72.88</v>
       </c>
       <c r="F37" s="7" t="inlineStr"/>
     </row>
@@ -1410,10 +1410,10 @@
         <v>71.86</v>
       </c>
       <c r="D38" s="5" t="n">
-        <v>80.23999999999999</v>
+        <v>80.72</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>122.16</v>
+        <v>122.89</v>
       </c>
       <c r="F38" s="7" t="inlineStr"/>
     </row>
@@ -1430,10 +1430,10 @@
         <v>39.11</v>
       </c>
       <c r="D39" s="5" t="n">
-        <v>54.59</v>
+        <v>54.92</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>66.29000000000001</v>
+        <v>66.69</v>
       </c>
       <c r="F39" s="7" t="inlineStr"/>
     </row>
@@ -1450,10 +1450,10 @@
         <v>38.91</v>
       </c>
       <c r="D40" s="5" t="n">
-        <v>52.05</v>
+        <v>52.36</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>65.76000000000001</v>
+        <v>66.15000000000001</v>
       </c>
       <c r="F40" s="7" t="inlineStr"/>
     </row>
@@ -1470,10 +1470,10 @@
         <v>34.69</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>46.76</v>
+        <v>47.04</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>58.65</v>
+        <v>59</v>
       </c>
       <c r="F41" s="7" t="inlineStr"/>
     </row>
@@ -1490,10 +1490,10 @@
         <v>42.78</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>55.32</v>
+        <v>55.65</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>72.34999999999999</v>
+        <v>72.79000000000001</v>
       </c>
       <c r="F42" s="7" t="inlineStr"/>
     </row>
@@ -1510,10 +1510,10 @@
         <v>28.32</v>
       </c>
       <c r="D43" s="5" t="n">
-        <v>37.7</v>
+        <v>37.92</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>47.91</v>
+        <v>48.2</v>
       </c>
       <c r="F43" s="7" t="inlineStr"/>
     </row>
@@ -1530,10 +1530,10 @@
         <v>165.37</v>
       </c>
       <c r="D44" s="5" t="n">
-        <v>154.7</v>
+        <v>155.63</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>279.71</v>
+        <v>281.39</v>
       </c>
       <c r="F44" s="7" t="inlineStr"/>
     </row>
@@ -1550,10 +1550,10 @@
         <v>69.13</v>
       </c>
       <c r="D45" s="5" t="n">
-        <v>80.22</v>
+        <v>80.7</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>116.9</v>
+        <v>117.6</v>
       </c>
       <c r="F45" s="7" t="inlineStr"/>
     </row>
@@ -1570,10 +1570,10 @@
         <v>74.84999999999999</v>
       </c>
       <c r="D46" s="5" t="n">
-        <v>90.06999999999999</v>
+        <v>90.61</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>126.53</v>
+        <v>127.29</v>
       </c>
       <c r="F46" s="7" t="inlineStr"/>
     </row>
@@ -1590,10 +1590,10 @@
         <v>81.62</v>
       </c>
       <c r="D47" s="5" t="n">
-        <v>114.08</v>
+        <v>114.76</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>137.41</v>
+        <v>138.24</v>
       </c>
       <c r="F47" s="7" t="inlineStr"/>
     </row>
@@ -1610,10 +1610,10 @@
         <v>75.48999999999999</v>
       </c>
       <c r="D48" s="5" t="n">
-        <v>105.03</v>
+        <v>105.66</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>126.58</v>
+        <v>127.34</v>
       </c>
       <c r="F48" s="7" t="inlineStr"/>
     </row>
@@ -1630,10 +1630,10 @@
         <v>218.05</v>
       </c>
       <c r="D49" s="5" t="n">
-        <v>239.27</v>
+        <v>240.71</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>364.13</v>
+        <v>366.32</v>
       </c>
       <c r="F49" s="7" t="inlineStr"/>
     </row>
@@ -1650,10 +1650,10 @@
         <v>115.22</v>
       </c>
       <c r="D50" s="5" t="n">
-        <v>142.54</v>
+        <v>143.39</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>191.97</v>
+        <v>193.12</v>
       </c>
       <c r="F50" s="7" t="inlineStr"/>
     </row>
@@ -1670,10 +1670,10 @@
         <v>50.83</v>
       </c>
       <c r="D51" s="5" t="n">
-        <v>69.37</v>
+        <v>69.78</v>
       </c>
       <c r="E51" s="5" t="n">
-        <v>84.5</v>
+        <v>85</v>
       </c>
       <c r="F51" s="7" t="inlineStr"/>
     </row>
@@ -1690,10 +1690,10 @@
         <v>55.04</v>
       </c>
       <c r="D52" s="5" t="n">
-        <v>73.94</v>
+        <v>74.38</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>91.28</v>
+        <v>91.83</v>
       </c>
       <c r="F52" s="7" t="inlineStr"/>
     </row>
@@ -1710,10 +1710,10 @@
         <v>45.32</v>
       </c>
       <c r="D53" s="5" t="n">
-        <v>58.71</v>
+        <v>59.06</v>
       </c>
       <c r="E53" s="5" t="n">
-        <v>74.93000000000001</v>
+        <v>75.38</v>
       </c>
       <c r="F53" s="7" t="inlineStr"/>
     </row>
@@ -1730,10 +1730,10 @@
         <v>54.55</v>
       </c>
       <c r="D54" s="5" t="n">
-        <v>70.43000000000001</v>
+        <v>70.84999999999999</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>89.91</v>
+        <v>90.45</v>
       </c>
       <c r="F54" s="7" t="inlineStr"/>
     </row>
@@ -1750,10 +1750,10 @@
         <v>62.08</v>
       </c>
       <c r="D55" s="5" t="n">
-        <v>73.59999999999999</v>
+        <v>74.04000000000001</v>
       </c>
       <c r="E55" s="5" t="n">
-        <v>102.01</v>
+        <v>102.62</v>
       </c>
       <c r="F55" s="7" t="inlineStr"/>
     </row>
@@ -1770,10 +1770,10 @@
         <v>55.11</v>
       </c>
       <c r="D56" s="5" t="n">
-        <v>66.04000000000001</v>
+        <v>66.44</v>
       </c>
       <c r="E56" s="5" t="n">
-        <v>90.16</v>
+        <v>90.7</v>
       </c>
       <c r="F56" s="7" t="inlineStr"/>
     </row>
@@ -1790,10 +1790,10 @@
         <v>52.11</v>
       </c>
       <c r="D57" s="5" t="n">
-        <v>60.07</v>
+        <v>60.43</v>
       </c>
       <c r="E57" s="5" t="n">
-        <v>84.87</v>
+        <v>85.38</v>
       </c>
       <c r="F57" s="7" t="inlineStr"/>
     </row>
@@ -1810,10 +1810,10 @@
         <v>84.56999999999999</v>
       </c>
       <c r="D58" s="5" t="n">
-        <v>84.54000000000001</v>
+        <v>85.05</v>
       </c>
       <c r="E58" s="5" t="n">
-        <v>137.13</v>
+        <v>137.95</v>
       </c>
       <c r="F58" s="7" t="inlineStr"/>
     </row>
@@ -1830,10 +1830,10 @@
         <v>50.14</v>
       </c>
       <c r="D59" s="5" t="n">
-        <v>64.31999999999999</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="E59" s="5" t="n">
-        <v>80.91</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="F59" s="7" t="inlineStr"/>
     </row>
@@ -1850,10 +1850,10 @@
         <v>64.59</v>
       </c>
       <c r="D60" s="5" t="n">
-        <v>86.77</v>
+        <v>87.29000000000001</v>
       </c>
       <c r="E60" s="5" t="n">
-        <v>103.73</v>
+        <v>104.35</v>
       </c>
       <c r="F60" s="7" t="inlineStr"/>
     </row>
@@ -1870,10 +1870,10 @@
         <v>52.09</v>
       </c>
       <c r="D61" s="5" t="n">
-        <v>67.19</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="E61" s="5" t="n">
-        <v>83.26000000000001</v>
+        <v>83.75</v>
       </c>
       <c r="F61" s="7" t="inlineStr"/>
     </row>
@@ -1890,10 +1890,10 @@
         <v>60.12</v>
       </c>
       <c r="D62" s="5" t="n">
-        <v>68.53</v>
+        <v>68.94</v>
       </c>
       <c r="E62" s="5" t="n">
-        <v>95.72</v>
+        <v>96.29000000000001</v>
       </c>
       <c r="F62" s="7" t="inlineStr"/>
     </row>
@@ -1910,10 +1910,10 @@
         <v>50.92</v>
       </c>
       <c r="D63" s="5" t="n">
-        <v>64.88</v>
+        <v>65.27</v>
       </c>
       <c r="E63" s="5" t="n">
-        <v>80.76000000000001</v>
+        <v>81.23999999999999</v>
       </c>
       <c r="F63" s="7" t="inlineStr"/>
     </row>
@@ -1930,10 +1930,10 @@
         <v>47.77</v>
       </c>
       <c r="D64" s="5" t="n">
-        <v>57.86</v>
+        <v>58.2</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>75.47</v>
+        <v>75.93000000000001</v>
       </c>
       <c r="F64" s="7" t="inlineStr"/>
     </row>
@@ -1950,10 +1950,10 @@
         <v>51.76</v>
       </c>
       <c r="D65" s="5" t="n">
-        <v>62.27</v>
+        <v>62.64</v>
       </c>
       <c r="E65" s="5" t="n">
-        <v>81.87</v>
+        <v>82.36</v>
       </c>
       <c r="F65" s="7" t="inlineStr"/>
     </row>
@@ -1970,10 +1970,10 @@
         <v>45.33</v>
       </c>
       <c r="D66" s="5" t="n">
-        <v>54.72</v>
+        <v>55.05</v>
       </c>
       <c r="E66" s="5" t="n">
-        <v>71.77</v>
+        <v>72.2</v>
       </c>
       <c r="F66" s="7" t="inlineStr"/>
     </row>
@@ -1990,10 +1990,10 @@
         <v>27.82</v>
       </c>
       <c r="D67" s="5" t="n">
-        <v>35.65</v>
+        <v>35.86</v>
       </c>
       <c r="E67" s="5" t="n">
-        <v>44.1</v>
+        <v>44.36</v>
       </c>
       <c r="F67" s="7" t="inlineStr"/>
     </row>
@@ -2010,10 +2010,10 @@
         <v>248.2</v>
       </c>
       <c r="D68" s="5" t="n">
-        <v>198.92</v>
+        <v>200.11</v>
       </c>
       <c r="E68" s="5" t="n">
-        <v>393.28</v>
+        <v>395.64</v>
       </c>
       <c r="F68" s="7" t="inlineStr"/>
     </row>
@@ -2030,10 +2030,10 @@
         <v>44.74</v>
       </c>
       <c r="D69" s="5" t="n">
-        <v>52.9</v>
+        <v>53.22</v>
       </c>
       <c r="E69" s="5" t="n">
-        <v>70.87</v>
+        <v>71.29000000000001</v>
       </c>
       <c r="F69" s="7" t="inlineStr"/>
     </row>
@@ -2050,10 +2050,10 @@
         <v>32.56</v>
       </c>
       <c r="D70" s="5" t="n">
-        <v>40.01</v>
+        <v>40.25</v>
       </c>
       <c r="E70" s="5" t="n">
-        <v>51.55</v>
+        <v>51.86</v>
       </c>
       <c r="F70" s="7" t="inlineStr"/>
     </row>
@@ -2070,10 +2070,10 @@
         <v>49.27</v>
       </c>
       <c r="D71" s="5" t="n">
-        <v>58.96</v>
+        <v>59.32</v>
       </c>
       <c r="E71" s="5" t="n">
-        <v>77.88</v>
+        <v>78.34999999999999</v>
       </c>
       <c r="F71" s="7" t="inlineStr"/>
     </row>
@@ -2090,10 +2090,10 @@
         <v>37.87</v>
       </c>
       <c r="D72" s="5" t="n">
-        <v>49.63</v>
+        <v>49.93</v>
       </c>
       <c r="E72" s="5" t="n">
-        <v>59.76</v>
+        <v>60.12</v>
       </c>
       <c r="F72" s="7" t="inlineStr"/>
     </row>
@@ -2110,10 +2110,10 @@
         <v>37.13</v>
       </c>
       <c r="D73" s="5" t="n">
-        <v>47.38</v>
+        <v>47.66</v>
       </c>
       <c r="E73" s="5" t="n">
-        <v>58.5</v>
+        <v>58.85</v>
       </c>
       <c r="F73" s="7" t="inlineStr"/>
     </row>
@@ -2130,10 +2130,10 @@
         <v>32.55</v>
       </c>
       <c r="D74" s="5" t="n">
-        <v>42.15</v>
+        <v>42.41</v>
       </c>
       <c r="E74" s="5" t="n">
-        <v>51.12</v>
+        <v>51.43</v>
       </c>
       <c r="F74" s="7" t="inlineStr"/>
     </row>
@@ -2150,10 +2150,10 @@
         <v>28.02</v>
       </c>
       <c r="D75" s="5" t="n">
-        <v>35.13</v>
+        <v>35.34</v>
       </c>
       <c r="E75" s="5" t="n">
-        <v>43.87</v>
+        <v>44.13</v>
       </c>
       <c r="F75" s="7" t="inlineStr"/>
     </row>
@@ -2170,10 +2170,10 @@
         <v>27.43</v>
       </c>
       <c r="D76" s="5" t="n">
-        <v>35.8</v>
+        <v>36.02</v>
       </c>
       <c r="E76" s="5" t="n">
-        <v>42.81</v>
+        <v>43.07</v>
       </c>
       <c r="F76" s="7" t="inlineStr"/>
     </row>
@@ -2190,10 +2190,10 @@
         <v>31.55</v>
       </c>
       <c r="D77" s="5" t="n">
-        <v>39.82</v>
+        <v>40.06</v>
       </c>
       <c r="E77" s="5" t="n">
-        <v>49.15</v>
+        <v>49.45</v>
       </c>
       <c r="F77" s="7" t="inlineStr"/>
     </row>
@@ -2210,10 +2210,10 @@
         <v>44.98</v>
       </c>
       <c r="D78" s="5" t="n">
-        <v>50.44</v>
+        <v>50.74</v>
       </c>
       <c r="E78" s="5" t="n">
-        <v>69.95</v>
+        <v>70.37</v>
       </c>
       <c r="F78" s="7" t="inlineStr"/>
     </row>
@@ -2230,10 +2230,10 @@
         <v>29.49</v>
       </c>
       <c r="D79" s="5" t="n">
-        <v>36.5</v>
+        <v>36.72</v>
       </c>
       <c r="E79" s="5" t="n">
-        <v>45.78</v>
+        <v>46.06</v>
       </c>
       <c r="F79" s="7" t="inlineStr"/>
     </row>
@@ -2250,10 +2250,10 @@
         <v>114.74</v>
       </c>
       <c r="D80" s="5" t="n">
-        <v>94.33</v>
+        <v>94.89</v>
       </c>
       <c r="E80" s="5" t="n">
-        <v>177.58</v>
+        <v>178.64</v>
       </c>
       <c r="F80" s="7" t="inlineStr"/>
     </row>
@@ -2270,10 +2270,10 @@
         <v>124.09</v>
       </c>
       <c r="D81" s="5" t="n">
-        <v>104.78</v>
+        <v>105.4</v>
       </c>
       <c r="E81" s="5" t="n">
-        <v>191.45</v>
+        <v>192.6</v>
       </c>
       <c r="F81" s="7" t="inlineStr"/>
     </row>
@@ -2290,10 +2290,10 @@
         <v>27.11</v>
       </c>
       <c r="D82" s="5" t="n">
-        <v>35.16</v>
+        <v>35.37</v>
       </c>
       <c r="E82" s="5" t="n">
-        <v>41.7</v>
+        <v>41.95</v>
       </c>
       <c r="F82" s="7" t="inlineStr"/>
     </row>
@@ -2310,10 +2310,10 @@
         <v>131.25</v>
       </c>
       <c r="D83" s="5" t="n">
-        <v>109.85</v>
+        <v>110.5</v>
       </c>
       <c r="E83" s="5" t="n">
-        <v>201.47</v>
+        <v>202.68</v>
       </c>
       <c r="F83" s="7" t="inlineStr"/>
     </row>
@@ -2330,10 +2330,10 @@
         <v>34.97</v>
       </c>
       <c r="D84" s="5" t="n">
-        <v>46.71</v>
+        <v>46.99</v>
       </c>
       <c r="E84" s="5" t="n">
-        <v>53.57</v>
+        <v>53.89</v>
       </c>
       <c r="F84" s="7" t="inlineStr"/>
     </row>
@@ -2350,10 +2350,10 @@
         <v>36.19</v>
       </c>
       <c r="D85" s="5" t="n">
-        <v>48.01</v>
+        <v>48.29</v>
       </c>
       <c r="E85" s="5" t="n">
-        <v>55.33</v>
+        <v>55.66</v>
       </c>
       <c r="F85" s="7" t="inlineStr"/>
     </row>
@@ -2370,10 +2370,10 @@
         <v>30.36</v>
       </c>
       <c r="D86" s="5" t="n">
-        <v>40.65</v>
+        <v>40.89</v>
       </c>
       <c r="E86" s="5" t="n">
-        <v>46.3</v>
+        <v>46.58</v>
       </c>
       <c r="F86" s="7" t="inlineStr"/>
     </row>
@@ -2390,10 +2390,10 @@
         <v>30.73</v>
       </c>
       <c r="D87" s="5" t="n">
-        <v>41.16</v>
+        <v>41.4</v>
       </c>
       <c r="E87" s="5" t="n">
-        <v>46.76</v>
+        <v>47.04</v>
       </c>
       <c r="F87" s="7" t="inlineStr"/>
     </row>
@@ -2410,10 +2410,10 @@
         <v>24.89</v>
       </c>
       <c r="D88" s="5" t="n">
-        <v>33.58</v>
+        <v>33.78</v>
       </c>
       <c r="E88" s="5" t="n">
-        <v>37.78</v>
+        <v>38.01</v>
       </c>
       <c r="F88" s="7" t="inlineStr"/>
     </row>
@@ -2430,10 +2430,10 @@
         <v>24.65</v>
       </c>
       <c r="D89" s="5" t="n">
-        <v>31.56</v>
+        <v>31.75</v>
       </c>
       <c r="E89" s="5" t="n">
-        <v>37.37</v>
+        <v>37.59</v>
       </c>
       <c r="F89" s="7" t="inlineStr"/>
     </row>
@@ -2450,10 +2450,10 @@
         <v>21.04</v>
       </c>
       <c r="D90" s="5" t="n">
-        <v>27.89</v>
+        <v>28.06</v>
       </c>
       <c r="E90" s="5" t="n">
-        <v>31.85</v>
+        <v>32.05</v>
       </c>
       <c r="F90" s="7" t="inlineStr"/>
     </row>
@@ -2470,10 +2470,10 @@
         <v>18.96</v>
       </c>
       <c r="D91" s="5" t="n">
-        <v>24.98</v>
+        <v>25.13</v>
       </c>
       <c r="E91" s="5" t="n">
-        <v>28.67</v>
+        <v>28.84</v>
       </c>
       <c r="F91" s="7" t="inlineStr"/>
     </row>
@@ -2490,10 +2490,10 @@
         <v>66.16</v>
       </c>
       <c r="D92" s="5" t="n">
-        <v>61.78</v>
+        <v>62.15</v>
       </c>
       <c r="E92" s="5" t="n">
-        <v>99.52</v>
+        <v>100.12</v>
       </c>
       <c r="F92" s="7" t="inlineStr"/>
     </row>
@@ -2510,10 +2510,10 @@
         <v>59.69</v>
       </c>
       <c r="D93" s="5" t="n">
-        <v>60.55</v>
+        <v>60.92</v>
       </c>
       <c r="E93" s="5" t="n">
-        <v>89.33</v>
+        <v>89.87</v>
       </c>
       <c r="F93" s="7" t="inlineStr"/>
     </row>
@@ -2530,10 +2530,10 @@
         <v>28.62</v>
       </c>
       <c r="D94" s="5" t="n">
-        <v>37.17</v>
+        <v>37.39</v>
       </c>
       <c r="E94" s="5" t="n">
-        <v>42.62</v>
+        <v>42.87</v>
       </c>
       <c r="F94" s="7" t="inlineStr"/>
     </row>
@@ -2550,10 +2550,10 @@
         <v>28.26</v>
       </c>
       <c r="D95" s="5" t="n">
-        <v>38</v>
+        <v>38.23</v>
       </c>
       <c r="E95" s="5" t="n">
-        <v>41.95</v>
+        <v>42.2</v>
       </c>
       <c r="F95" s="7" t="inlineStr"/>
     </row>
@@ -2570,10 +2570,10 @@
         <v>40.58</v>
       </c>
       <c r="D96" s="5" t="n">
-        <v>50.84</v>
+        <v>51.14</v>
       </c>
       <c r="E96" s="5" t="n">
-        <v>60.06</v>
+        <v>60.42</v>
       </c>
       <c r="F96" s="7" t="inlineStr"/>
     </row>
@@ -2590,10 +2590,10 @@
         <v>33.89</v>
       </c>
       <c r="D97" s="5" t="n">
-        <v>41.19</v>
+        <v>41.44</v>
       </c>
       <c r="E97" s="5" t="n">
-        <v>50</v>
+        <v>50.3</v>
       </c>
       <c r="F97" s="7" t="inlineStr"/>
     </row>
@@ -2610,10 +2610,10 @@
         <v>37.84</v>
       </c>
       <c r="D98" s="5" t="n">
-        <v>43.42</v>
+        <v>43.68</v>
       </c>
       <c r="E98" s="5" t="n">
-        <v>55.72</v>
+        <v>56.05</v>
       </c>
       <c r="F98" s="7" t="inlineStr"/>
     </row>
@@ -2630,10 +2630,10 @@
         <v>35.44</v>
       </c>
       <c r="D99" s="5" t="n">
-        <v>44.01</v>
+        <v>44.28</v>
       </c>
       <c r="E99" s="5" t="n">
-        <v>52.08</v>
+        <v>52.39</v>
       </c>
       <c r="F99" s="7" t="inlineStr"/>
     </row>
@@ -2650,10 +2650,10 @@
         <v>31.61</v>
       </c>
       <c r="D100" s="5" t="n">
-        <v>39.57</v>
+        <v>39.81</v>
       </c>
       <c r="E100" s="5" t="n">
-        <v>46.36</v>
+        <v>46.64</v>
       </c>
       <c r="F100" s="7" t="inlineStr"/>
     </row>
@@ -2670,10 +2670,10 @@
         <v>29</v>
       </c>
       <c r="D101" s="5" t="n">
-        <v>34.63</v>
+        <v>34.84</v>
       </c>
       <c r="E101" s="5" t="n">
-        <v>42.53</v>
+        <v>42.79</v>
       </c>
       <c r="F101" s="7" t="inlineStr"/>
     </row>
@@ -2690,10 +2690,10 @@
         <v>30.77</v>
       </c>
       <c r="D102" s="5" t="n">
-        <v>38.98</v>
+        <v>39.22</v>
       </c>
       <c r="E102" s="5" t="n">
-        <v>45.13</v>
+        <v>45.4</v>
       </c>
       <c r="F102" s="7" t="inlineStr"/>
     </row>
@@ -2710,10 +2710,10 @@
         <v>25.62</v>
       </c>
       <c r="D103" s="5" t="n">
-        <v>32.53</v>
+        <v>32.73</v>
       </c>
       <c r="E103" s="5" t="n">
-        <v>37.58</v>
+        <v>37.8</v>
       </c>
       <c r="F103" s="7" t="inlineStr"/>
     </row>
@@ -2730,10 +2730,10 @@
         <v>29.13</v>
       </c>
       <c r="D104" s="5" t="n">
-        <v>35.24</v>
+        <v>35.45</v>
       </c>
       <c r="E104" s="5" t="n">
-        <v>42.72</v>
+        <v>42.97</v>
       </c>
       <c r="F104" s="7" t="inlineStr"/>
     </row>
@@ -2750,10 +2750,10 @@
         <v>30.01</v>
       </c>
       <c r="D105" s="5" t="n">
-        <v>37.9</v>
+        <v>38.13</v>
       </c>
       <c r="E105" s="5" t="n">
-        <v>44</v>
+        <v>44.26</v>
       </c>
       <c r="F105" s="7" t="inlineStr"/>
     </row>
@@ -2770,10 +2770,10 @@
         <v>27.89</v>
       </c>
       <c r="D106" s="5" t="n">
-        <v>34.74</v>
+        <v>34.95</v>
       </c>
       <c r="E106" s="5" t="n">
-        <v>40.88</v>
+        <v>41.13</v>
       </c>
       <c r="F106" s="7" t="inlineStr"/>
     </row>
@@ -2790,10 +2790,10 @@
         <v>36.3</v>
       </c>
       <c r="D107" s="5" t="n">
-        <v>46.84</v>
+        <v>47.12</v>
       </c>
       <c r="E107" s="5" t="n">
-        <v>53.12</v>
+        <v>53.44</v>
       </c>
       <c r="F107" s="7" t="inlineStr"/>
     </row>
@@ -2810,10 +2810,10 @@
         <v>30.09</v>
       </c>
       <c r="D108" s="5" t="n">
-        <v>38.83</v>
+        <v>39.06</v>
       </c>
       <c r="E108" s="5" t="n">
-        <v>43.96</v>
+        <v>44.22</v>
       </c>
       <c r="F108" s="7" t="inlineStr"/>
     </row>
@@ -2830,10 +2830,10 @@
         <v>42.66</v>
       </c>
       <c r="D109" s="5" t="n">
-        <v>53.59</v>
+        <v>53.91</v>
       </c>
       <c r="E109" s="5" t="n">
-        <v>62.21</v>
+        <v>62.58</v>
       </c>
       <c r="F109" s="7" t="inlineStr"/>
     </row>
@@ -2850,10 +2850,10 @@
         <v>90.05</v>
       </c>
       <c r="D110" s="9" t="n">
-        <v>106.64</v>
+        <v>107.28</v>
       </c>
       <c r="E110" s="9" t="n">
-        <v>130.72</v>
+        <v>131.51</v>
       </c>
       <c r="F110" s="10" t="inlineStr">
         <is>
@@ -2874,10 +2874,10 @@
         <v>58.79</v>
       </c>
       <c r="D111" s="9" t="n">
-        <v>80.58</v>
+        <v>81.06</v>
       </c>
       <c r="E111" s="9" t="n">
-        <v>84.95999999999999</v>
+        <v>85.47</v>
       </c>
       <c r="F111" s="10" t="inlineStr">
         <is>
@@ -2898,10 +2898,10 @@
         <v>60.96</v>
       </c>
       <c r="D112" s="9" t="n">
-        <v>76.94</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="E112" s="9" t="n">
-        <v>87.7</v>
+        <v>88.23</v>
       </c>
       <c r="F112" s="10" t="inlineStr">
         <is>
@@ -2922,10 +2922,10 @@
         <v>55</v>
       </c>
       <c r="D113" s="9" t="n">
-        <v>73.7</v>
+        <v>74.14</v>
       </c>
       <c r="E113" s="9" t="n">
-        <v>79.06</v>
+        <v>79.53</v>
       </c>
       <c r="F113" s="10" t="inlineStr">
         <is>
@@ -2946,10 +2946,10 @@
         <v>108.73</v>
       </c>
       <c r="D114" s="9" t="n">
-        <v>110.85</v>
+        <v>111.51</v>
       </c>
       <c r="E114" s="9" t="n">
-        <v>156.16</v>
+        <v>157.1</v>
       </c>
       <c r="F114" s="10" t="inlineStr">
         <is>
@@ -2970,10 +2970,10 @@
         <v>58.92</v>
       </c>
       <c r="D115" s="9" t="n">
-        <v>74.88</v>
+        <v>75.33</v>
       </c>
       <c r="E115" s="9" t="n">
-        <v>84.55</v>
+        <v>85.06</v>
       </c>
       <c r="F115" s="10" t="inlineStr">
         <is>
@@ -2994,10 +2994,10 @@
         <v>65.31</v>
       </c>
       <c r="D116" s="9" t="n">
-        <v>77.79000000000001</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="E116" s="9" t="n">
-        <v>93.62</v>
+        <v>94.18000000000001</v>
       </c>
       <c r="F116" s="10" t="inlineStr">
         <is>
@@ -3018,10 +3018,10 @@
         <v>59.78</v>
       </c>
       <c r="D117" s="9" t="n">
-        <v>76.73</v>
+        <v>77.19</v>
       </c>
       <c r="E117" s="9" t="n">
-        <v>85.59</v>
+        <v>86.11</v>
       </c>
       <c r="F117" s="10" t="inlineStr">
         <is>
@@ -3042,10 +3042,10 @@
         <v>60.03</v>
       </c>
       <c r="D118" s="9" t="n">
-        <v>74.81</v>
+        <v>75.26000000000001</v>
       </c>
       <c r="E118" s="9" t="n">
-        <v>85.84999999999999</v>
+        <v>86.37</v>
       </c>
       <c r="F118" s="10" t="inlineStr">
         <is>
@@ -3066,10 +3066,10 @@
         <v>53.46</v>
       </c>
       <c r="D119" s="9" t="n">
-        <v>71.45</v>
+        <v>71.88</v>
       </c>
       <c r="E119" s="9" t="n">
-        <v>76.36</v>
+        <v>76.81999999999999</v>
       </c>
       <c r="F119" s="10" t="inlineStr">
         <is>
@@ -3090,10 +3090,10 @@
         <v>61.01</v>
       </c>
       <c r="D120" s="9" t="n">
-        <v>78.25</v>
+        <v>78.72</v>
       </c>
       <c r="E120" s="9" t="n">
-        <v>87.03</v>
+        <v>87.56</v>
       </c>
       <c r="F120" s="10" t="inlineStr">
         <is>
@@ -3114,10 +3114,10 @@
         <v>70.51000000000001</v>
       </c>
       <c r="D121" s="9" t="n">
-        <v>86.77</v>
+        <v>87.29000000000001</v>
       </c>
       <c r="E121" s="9" t="n">
-        <v>100.46</v>
+        <v>101.06</v>
       </c>
       <c r="F121" s="10" t="inlineStr">
         <is>
@@ -3138,10 +3138,10 @@
         <v>62.4</v>
       </c>
       <c r="D122" s="9" t="n">
-        <v>82.8</v>
+        <v>83.3</v>
       </c>
       <c r="E122" s="9" t="n">
-        <v>88.55</v>
+        <v>89.08</v>
       </c>
       <c r="F122" s="10" t="inlineStr">
         <is>
@@ -3162,10 +3162,10 @@
         <v>57.79</v>
       </c>
       <c r="D123" s="9" t="n">
-        <v>76.48999999999999</v>
+        <v>76.95</v>
       </c>
       <c r="E123" s="9" t="n">
-        <v>81.67</v>
+        <v>82.16</v>
       </c>
       <c r="F123" s="10" t="inlineStr">
         <is>
@@ -3186,10 +3186,10 @@
         <v>52.11</v>
       </c>
       <c r="D124" s="9" t="n">
-        <v>69.31999999999999</v>
+        <v>69.73999999999999</v>
       </c>
       <c r="E124" s="9" t="n">
-        <v>73.34999999999999</v>
+        <v>73.79000000000001</v>
       </c>
       <c r="F124" s="10" t="inlineStr">
         <is>
@@ -3210,10 +3210,10 @@
         <v>51.91</v>
       </c>
       <c r="D125" s="9" t="n">
-        <v>69.47</v>
+        <v>69.88</v>
       </c>
       <c r="E125" s="9" t="n">
-        <v>72.89</v>
+        <v>73.33</v>
       </c>
       <c r="F125" s="10" t="inlineStr">
         <is>
@@ -3234,10 +3234,10 @@
         <v>49.47</v>
       </c>
       <c r="D126" s="9" t="n">
-        <v>65.51000000000001</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="E126" s="9" t="n">
-        <v>69.3</v>
+        <v>69.72</v>
       </c>
       <c r="F126" s="10" t="inlineStr">
         <is>
@@ -3258,10 +3258,10 @@
         <v>57.51</v>
       </c>
       <c r="D127" s="9" t="n">
-        <v>70.34</v>
+        <v>70.76000000000001</v>
       </c>
       <c r="E127" s="9" t="n">
-        <v>80.37</v>
+        <v>80.86</v>
       </c>
       <c r="F127" s="10" t="inlineStr">
         <is>
@@ -3282,10 +3282,10 @@
         <v>105.62</v>
       </c>
       <c r="D128" s="9" t="n">
-        <v>101.03</v>
+        <v>101.63</v>
       </c>
       <c r="E128" s="9" t="n">
-        <v>147.32</v>
+        <v>148.2</v>
       </c>
       <c r="F128" s="10" t="inlineStr">
         <is>
@@ -3306,10 +3306,10 @@
         <v>51.64</v>
       </c>
       <c r="D129" s="9" t="n">
-        <v>68.56</v>
+        <v>68.97</v>
       </c>
       <c r="E129" s="9" t="n">
-        <v>71.89</v>
+        <v>72.31999999999999</v>
       </c>
       <c r="F129" s="10" t="inlineStr">
         <is>
@@ -3330,10 +3330,10 @@
         <v>50.99</v>
       </c>
       <c r="D130" s="9" t="n">
-        <v>63.85</v>
+        <v>64.23999999999999</v>
       </c>
       <c r="E130" s="9" t="n">
-        <v>70.84</v>
+        <v>71.27</v>
       </c>
       <c r="F130" s="10" t="inlineStr">
         <is>
@@ -3354,10 +3354,10 @@
         <v>46.48</v>
       </c>
       <c r="D131" s="9" t="n">
-        <v>60.74</v>
+        <v>61.1</v>
       </c>
       <c r="E131" s="9" t="n">
-        <v>64.47</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="F131" s="10" t="inlineStr">
         <is>
@@ -3378,10 +3378,10 @@
         <v>53.42</v>
       </c>
       <c r="D132" s="9" t="n">
-        <v>66.73999999999999</v>
+        <v>67.14</v>
       </c>
       <c r="E132" s="9" t="n">
-        <v>73.97</v>
+        <v>74.41</v>
       </c>
       <c r="F132" s="10" t="inlineStr">
         <is>
@@ -3402,10 +3402,10 @@
         <v>53.9</v>
       </c>
       <c r="D133" s="9" t="n">
-        <v>67.97</v>
+        <v>68.38</v>
       </c>
       <c r="E133" s="9" t="n">
-        <v>74.51000000000001</v>
+        <v>74.95999999999999</v>
       </c>
       <c r="F133" s="10" t="inlineStr">
         <is>
@@ -3426,10 +3426,10 @@
         <v>43.69</v>
       </c>
       <c r="D134" s="5" t="n">
-        <v>53.27</v>
+        <v>53.59</v>
       </c>
       <c r="E134" s="5" t="n">
-        <v>60.31</v>
+        <v>60.67</v>
       </c>
       <c r="F134" s="7" t="inlineStr"/>
     </row>
@@ -3446,10 +3446,10 @@
         <v>40.67</v>
       </c>
       <c r="D135" s="5" t="n">
-        <v>47.57</v>
+        <v>47.86</v>
       </c>
       <c r="E135" s="5" t="n">
-        <v>56.06</v>
+        <v>56.4</v>
       </c>
       <c r="F135" s="7" t="inlineStr"/>
     </row>
@@ -3466,10 +3466,10 @@
         <v>42.07</v>
       </c>
       <c r="D136" s="5" t="n">
-        <v>49.91</v>
+        <v>50.21</v>
       </c>
       <c r="E136" s="5" t="n">
-        <v>57.91</v>
+        <v>58.26</v>
       </c>
       <c r="F136" s="7" t="inlineStr"/>
     </row>
@@ -3486,10 +3486,10 @@
         <v>30.63</v>
       </c>
       <c r="D137" s="5" t="n">
-        <v>36.58</v>
+        <v>36.8</v>
       </c>
       <c r="E137" s="5" t="n">
-        <v>42.14</v>
+        <v>42.39</v>
       </c>
       <c r="F137" s="7" t="inlineStr"/>
     </row>
@@ -3506,10 +3506,10 @@
         <v>34.46</v>
       </c>
       <c r="D138" s="5" t="n">
-        <v>39.26</v>
+        <v>39.5</v>
       </c>
       <c r="E138" s="5" t="n">
-        <v>47.38</v>
+        <v>47.66</v>
       </c>
       <c r="F138" s="7" t="inlineStr"/>
     </row>
@@ -3526,10 +3526,10 @@
         <v>31.31</v>
       </c>
       <c r="D139" s="5" t="n">
-        <v>36.46</v>
+        <v>36.68</v>
       </c>
       <c r="E139" s="5" t="n">
-        <v>43.02</v>
+        <v>43.28</v>
       </c>
       <c r="F139" s="7" t="inlineStr"/>
     </row>
@@ -3546,10 +3546,10 @@
         <v>33.61</v>
       </c>
       <c r="D140" s="5" t="n">
-        <v>35.84</v>
+        <v>36.05</v>
       </c>
       <c r="E140" s="5" t="n">
-        <v>46.15</v>
+        <v>46.43</v>
       </c>
       <c r="F140" s="7" t="inlineStr"/>
     </row>
@@ -3566,10 +3566,10 @@
         <v>35.21</v>
       </c>
       <c r="D141" s="5" t="n">
-        <v>38.46</v>
+        <v>38.69</v>
       </c>
       <c r="E141" s="5" t="n">
-        <v>48.32</v>
+        <v>48.61</v>
       </c>
       <c r="F141" s="7" t="inlineStr"/>
     </row>
@@ -3586,10 +3586,10 @@
         <v>31.79</v>
       </c>
       <c r="D142" s="5" t="n">
-        <v>35.39</v>
+        <v>35.61</v>
       </c>
       <c r="E142" s="5" t="n">
-        <v>43.6</v>
+        <v>43.86</v>
       </c>
       <c r="F142" s="7" t="inlineStr"/>
     </row>
@@ -3606,10 +3606,10 @@
         <v>35.26</v>
       </c>
       <c r="D143" s="5" t="n">
-        <v>39.55</v>
+        <v>39.79</v>
       </c>
       <c r="E143" s="5" t="n">
-        <v>48.24</v>
+        <v>48.53</v>
       </c>
       <c r="F143" s="7" t="inlineStr"/>
     </row>
@@ -3626,10 +3626,10 @@
         <v>38.41</v>
       </c>
       <c r="D144" s="5" t="n">
-        <v>40.74</v>
+        <v>40.99</v>
       </c>
       <c r="E144" s="5" t="n">
-        <v>52.42</v>
+        <v>52.74</v>
       </c>
       <c r="F144" s="7" t="inlineStr"/>
     </row>
@@ -3646,10 +3646,10 @@
         <v>41.52</v>
       </c>
       <c r="D145" s="5" t="n">
-        <v>46.85</v>
+        <v>47.13</v>
       </c>
       <c r="E145" s="5" t="n">
-        <v>56.53</v>
+        <v>56.87</v>
       </c>
       <c r="F145" s="7" t="inlineStr"/>
     </row>
@@ -3666,10 +3666,10 @@
         <v>42.82</v>
       </c>
       <c r="D146" s="5" t="n">
-        <v>47.26</v>
+        <v>47.54</v>
       </c>
       <c r="E146" s="5" t="n">
-        <v>58.23</v>
+        <v>58.58</v>
       </c>
       <c r="F146" s="7" t="inlineStr"/>
     </row>
@@ -3686,10 +3686,10 @@
         <v>42.1</v>
       </c>
       <c r="D147" s="5" t="n">
-        <v>47.59</v>
+        <v>47.87</v>
       </c>
       <c r="E147" s="5" t="n">
-        <v>57.18</v>
+        <v>57.52</v>
       </c>
       <c r="F147" s="7" t="inlineStr"/>
     </row>
@@ -3706,10 +3706,10 @@
         <v>50.84</v>
       </c>
       <c r="D148" s="5" t="n">
-        <v>60.43</v>
+        <v>60.79</v>
       </c>
       <c r="E148" s="5" t="n">
-        <v>68.95999999999999</v>
+        <v>69.37</v>
       </c>
       <c r="F148" s="7" t="inlineStr"/>
     </row>
@@ -3726,10 +3726,10 @@
         <v>45.47</v>
       </c>
       <c r="D149" s="5" t="n">
-        <v>48.26</v>
+        <v>48.55</v>
       </c>
       <c r="E149" s="5" t="n">
-        <v>61.59</v>
+        <v>61.96</v>
       </c>
       <c r="F149" s="7" t="inlineStr"/>
     </row>
@@ -3746,10 +3746,10 @@
         <v>45.23</v>
       </c>
       <c r="D150" s="5" t="n">
-        <v>47.24</v>
+        <v>47.53</v>
       </c>
       <c r="E150" s="5" t="n">
-        <v>61.19</v>
+        <v>61.56</v>
       </c>
       <c r="F150" s="7" t="inlineStr"/>
     </row>
@@ -3766,10 +3766,10 @@
         <v>62.67</v>
       </c>
       <c r="D151" s="5" t="n">
-        <v>64.87</v>
+        <v>65.26000000000001</v>
       </c>
       <c r="E151" s="5" t="n">
-        <v>84.68000000000001</v>
+        <v>85.18000000000001</v>
       </c>
       <c r="F151" s="7" t="inlineStr"/>
     </row>
@@ -3786,10 +3786,10 @@
         <v>72.90000000000001</v>
       </c>
       <c r="D152" s="5" t="n">
-        <v>63.48</v>
+        <v>63.86</v>
       </c>
       <c r="E152" s="5" t="n">
-        <v>98.56</v>
+        <v>99.15000000000001</v>
       </c>
       <c r="F152" s="7" t="inlineStr"/>
     </row>
@@ -3806,10 +3806,10 @@
         <v>44.52</v>
       </c>
       <c r="D153" s="5" t="n">
-        <v>47.92</v>
+        <v>48.21</v>
       </c>
       <c r="E153" s="5" t="n">
-        <v>60.23</v>
+        <v>60.59</v>
       </c>
       <c r="F153" s="7" t="inlineStr"/>
     </row>
@@ -3826,10 +3826,10 @@
         <v>59.65</v>
       </c>
       <c r="D154" s="5" t="n">
-        <v>62.13</v>
+        <v>62.5</v>
       </c>
       <c r="E154" s="5" t="n">
-        <v>80.76000000000001</v>
+        <v>81.23999999999999</v>
       </c>
       <c r="F154" s="7" t="inlineStr"/>
     </row>
@@ -3846,10 +3846,10 @@
         <v>61.49</v>
       </c>
       <c r="D155" s="5" t="n">
-        <v>62.02</v>
+        <v>62.4</v>
       </c>
       <c r="E155" s="5" t="n">
-        <v>83.13</v>
+        <v>83.62</v>
       </c>
       <c r="F155" s="7" t="inlineStr"/>
     </row>
@@ -3866,10 +3866,10 @@
         <v>76.45999999999999</v>
       </c>
       <c r="D156" s="5" t="n">
-        <v>73.22</v>
+        <v>73.66</v>
       </c>
       <c r="E156" s="5" t="n">
-        <v>103.21</v>
+        <v>103.83</v>
       </c>
       <c r="F156" s="7" t="inlineStr"/>
     </row>
@@ -3886,10 +3886,10 @@
         <v>118.54</v>
       </c>
       <c r="D157" s="5" t="n">
-        <v>125.05</v>
+        <v>125.8</v>
       </c>
       <c r="E157" s="5" t="n">
-        <v>159.78</v>
+        <v>160.74</v>
       </c>
       <c r="F157" s="7" t="inlineStr"/>
     </row>
@@ -3906,10 +3906,10 @@
         <v>86.77</v>
       </c>
       <c r="D158" s="5" t="n">
-        <v>86.93000000000001</v>
+        <v>87.45</v>
       </c>
       <c r="E158" s="5" t="n">
-        <v>116.69</v>
+        <v>117.39</v>
       </c>
       <c r="F158" s="7" t="inlineStr"/>
     </row>
@@ -3926,10 +3926,10 @@
         <v>55.76</v>
       </c>
       <c r="D159" s="5" t="n">
-        <v>58.01</v>
+        <v>58.36</v>
       </c>
       <c r="E159" s="5" t="n">
-        <v>74.81</v>
+        <v>75.26000000000001</v>
       </c>
       <c r="F159" s="7" t="inlineStr"/>
     </row>
@@ -3946,10 +3946,10 @@
         <v>48.5</v>
       </c>
       <c r="D160" s="5" t="n">
-        <v>54.91</v>
+        <v>55.24</v>
       </c>
       <c r="E160" s="5" t="n">
-        <v>64.92</v>
+        <v>65.31</v>
       </c>
       <c r="F160" s="7" t="inlineStr"/>
     </row>
@@ -3966,10 +3966,10 @@
         <v>41.02</v>
       </c>
       <c r="D161" s="5" t="n">
-        <v>44.33</v>
+        <v>44.6</v>
       </c>
       <c r="E161" s="5" t="n">
-        <v>54.81</v>
+        <v>55.14</v>
       </c>
       <c r="F161" s="7" t="inlineStr"/>
     </row>
@@ -3986,10 +3986,10 @@
         <v>46.93</v>
       </c>
       <c r="D162" s="5" t="n">
-        <v>48.11</v>
+        <v>48.4</v>
       </c>
       <c r="E162" s="5" t="n">
-        <v>62.6</v>
+        <v>62.97</v>
       </c>
       <c r="F162" s="7" t="inlineStr"/>
     </row>
@@ -4006,10 +4006,10 @@
         <v>37.59</v>
       </c>
       <c r="D163" s="5" t="n">
-        <v>39.81</v>
+        <v>40.05</v>
       </c>
       <c r="E163" s="5" t="n">
-        <v>50.05</v>
+        <v>50.35</v>
       </c>
       <c r="F163" s="7" t="inlineStr"/>
     </row>
@@ -4026,10 +4026,10 @@
         <v>81.03</v>
       </c>
       <c r="D164" s="5" t="n">
-        <v>82.48</v>
+        <v>82.98</v>
       </c>
       <c r="E164" s="5" t="n">
-        <v>107.73</v>
+        <v>108.37</v>
       </c>
       <c r="F164" s="7" t="inlineStr"/>
     </row>
@@ -4046,10 +4046,10 @@
         <v>114.18</v>
       </c>
       <c r="D165" s="5" t="n">
-        <v>114.23</v>
+        <v>114.91</v>
       </c>
       <c r="E165" s="5" t="n">
-        <v>151.57</v>
+        <v>152.48</v>
       </c>
       <c r="F165" s="7" t="inlineStr"/>
     </row>
@@ -4066,10 +4066,10 @@
         <v>112.64</v>
       </c>
       <c r="D166" s="5" t="n">
-        <v>120.12</v>
+        <v>120.84</v>
       </c>
       <c r="E166" s="5" t="n">
-        <v>149.3</v>
+        <v>150.19</v>
       </c>
       <c r="F166" s="7" t="inlineStr"/>
     </row>
@@ -4086,10 +4086,10 @@
         <v>123.35</v>
       </c>
       <c r="D167" s="5" t="n">
-        <v>143.32</v>
+        <v>144.18</v>
       </c>
       <c r="E167" s="5" t="n">
-        <v>163.38</v>
+        <v>164.36</v>
       </c>
       <c r="F167" s="7" t="inlineStr"/>
     </row>
@@ -4106,10 +4106,10 @@
         <v>123.09</v>
       </c>
       <c r="D168" s="5" t="n">
-        <v>142.89</v>
+        <v>143.75</v>
       </c>
       <c r="E168" s="5" t="n">
-        <v>162.93</v>
+        <v>163.91</v>
       </c>
       <c r="F168" s="7" t="inlineStr"/>
     </row>
@@ -4126,10 +4126,10 @@
         <v>105</v>
       </c>
       <c r="D169" s="5" t="n">
-        <v>130.3</v>
+        <v>131.08</v>
       </c>
       <c r="E169" s="5" t="n">
-        <v>138.9</v>
+        <v>139.73</v>
       </c>
       <c r="F169" s="7" t="inlineStr"/>
     </row>
@@ -4146,10 +4146,10 @@
         <v>131.48</v>
       </c>
       <c r="D170" s="5" t="n">
-        <v>154.96</v>
+        <v>155.89</v>
       </c>
       <c r="E170" s="5" t="n">
-        <v>173.57</v>
+        <v>174.61</v>
       </c>
       <c r="F170" s="7" t="inlineStr"/>
     </row>
@@ -4166,10 +4166,10 @@
         <v>119.74</v>
       </c>
       <c r="D171" s="5" t="n">
-        <v>135.13</v>
+        <v>135.94</v>
       </c>
       <c r="E171" s="5" t="n">
-        <v>157.75</v>
+        <v>158.7</v>
       </c>
       <c r="F171" s="7" t="inlineStr"/>
     </row>
@@ -4186,10 +4186,10 @@
         <v>89.62</v>
       </c>
       <c r="D172" s="5" t="n">
-        <v>104.43</v>
+        <v>105.06</v>
       </c>
       <c r="E172" s="5" t="n">
-        <v>117.83</v>
+        <v>118.54</v>
       </c>
       <c r="F172" s="7" t="inlineStr"/>
     </row>
@@ -4206,10 +4206,10 @@
         <v>82.48</v>
       </c>
       <c r="D173" s="5" t="n">
-        <v>96.17</v>
+        <v>96.75</v>
       </c>
       <c r="E173" s="5" t="n">
-        <v>108.2</v>
+        <v>108.85</v>
       </c>
       <c r="F173" s="7" t="inlineStr"/>
     </row>
@@ -4226,10 +4226,10 @@
         <v>112.43</v>
       </c>
       <c r="D174" s="5" t="n">
-        <v>125.06</v>
+        <v>125.81</v>
       </c>
       <c r="E174" s="5" t="n">
-        <v>147.16</v>
+        <v>148.05</v>
       </c>
       <c r="F174" s="7" t="inlineStr"/>
     </row>
@@ -4246,10 +4246,10 @@
         <v>97.75</v>
       </c>
       <c r="D175" s="5" t="n">
-        <v>110.82</v>
+        <v>111.48</v>
       </c>
       <c r="E175" s="5" t="n">
-        <v>127.66</v>
+        <v>128.43</v>
       </c>
       <c r="F175" s="7" t="inlineStr"/>
     </row>
@@ -4266,10 +4266,10 @@
         <v>183</v>
       </c>
       <c r="D176" s="5" t="n">
-        <v>174.07</v>
+        <v>175.12</v>
       </c>
       <c r="E176" s="5" t="n">
-        <v>238.65</v>
+        <v>240.09</v>
       </c>
       <c r="F176" s="7" t="inlineStr"/>
     </row>
@@ -4286,10 +4286,10 @@
         <v>124.33</v>
       </c>
       <c r="D177" s="5" t="n">
-        <v>126.88</v>
+        <v>127.64</v>
       </c>
       <c r="E177" s="5" t="n">
-        <v>161.91</v>
+        <v>162.88</v>
       </c>
       <c r="F177" s="7" t="inlineStr"/>
     </row>
@@ -4306,10 +4306,10 @@
         <v>82.25</v>
       </c>
       <c r="D178" s="5" t="n">
-        <v>98.84</v>
+        <v>99.43000000000001</v>
       </c>
       <c r="E178" s="5" t="n">
-        <v>106.95</v>
+        <v>107.59</v>
       </c>
       <c r="F178" s="7" t="inlineStr"/>
     </row>
@@ -4326,10 +4326,10 @@
         <v>87.09</v>
       </c>
       <c r="D179" s="5" t="n">
-        <v>96.16</v>
+        <v>96.73999999999999</v>
       </c>
       <c r="E179" s="5" t="n">
-        <v>113.11</v>
+        <v>113.79</v>
       </c>
       <c r="F179" s="7" t="inlineStr"/>
     </row>
@@ -4346,10 +4346,10 @@
         <v>95.98</v>
       </c>
       <c r="D180" s="5" t="n">
-        <v>103.51</v>
+        <v>104.13</v>
       </c>
       <c r="E180" s="5" t="n">
-        <v>124.51</v>
+        <v>125.26</v>
       </c>
       <c r="F180" s="7" t="inlineStr"/>
     </row>
@@ -4366,10 +4366,10 @@
         <v>112.11</v>
       </c>
       <c r="D181" s="5" t="n">
-        <v>121.43</v>
+        <v>122.16</v>
       </c>
       <c r="E181" s="5" t="n">
-        <v>145.26</v>
+        <v>146.13</v>
       </c>
       <c r="F181" s="7" t="inlineStr"/>
     </row>
@@ -4386,10 +4386,10 @@
         <v>88.33</v>
       </c>
       <c r="D182" s="5" t="n">
-        <v>90.7</v>
+        <v>91.23999999999999</v>
       </c>
       <c r="E182" s="5" t="n">
-        <v>114.28</v>
+        <v>114.97</v>
       </c>
       <c r="F182" s="7" t="inlineStr"/>
     </row>
@@ -4406,10 +4406,10 @@
         <v>102.2</v>
       </c>
       <c r="D183" s="5" t="n">
-        <v>102.29</v>
+        <v>102.9</v>
       </c>
       <c r="E183" s="5" t="n">
-        <v>132.04</v>
+        <v>132.83</v>
       </c>
       <c r="F183" s="7" t="inlineStr"/>
     </row>
@@ -4426,10 +4426,10 @@
         <v>108.02</v>
       </c>
       <c r="D184" s="5" t="n">
-        <v>119.79</v>
+        <v>120.51</v>
       </c>
       <c r="E184" s="5" t="n">
-        <v>139.36</v>
+        <v>140.19</v>
       </c>
       <c r="F184" s="7" t="inlineStr"/>
     </row>
@@ -4446,10 +4446,10 @@
         <v>109.7</v>
       </c>
       <c r="D185" s="5" t="n">
-        <v>128.57</v>
+        <v>129.34</v>
       </c>
       <c r="E185" s="5" t="n">
-        <v>141.28</v>
+        <v>142.13</v>
       </c>
       <c r="F185" s="7" t="inlineStr"/>
     </row>
@@ -4466,10 +4466,10 @@
         <v>105.48</v>
       </c>
       <c r="D186" s="5" t="n">
-        <v>125.79</v>
+        <v>126.54</v>
       </c>
       <c r="E186" s="5" t="n">
-        <v>135.61</v>
+        <v>136.42</v>
       </c>
       <c r="F186" s="7" t="inlineStr"/>
     </row>
@@ -4486,10 +4486,10 @@
         <v>113.92</v>
       </c>
       <c r="D187" s="5" t="n">
-        <v>117.81</v>
+        <v>118.51</v>
       </c>
       <c r="E187" s="5" t="n">
-        <v>146.21</v>
+        <v>147.09</v>
       </c>
       <c r="F187" s="7" t="inlineStr"/>
     </row>
@@ -4506,10 +4506,10 @@
         <v>423.33</v>
       </c>
       <c r="D188" s="5" t="n">
-        <v>321.3</v>
+        <v>323.22</v>
       </c>
       <c r="E188" s="5" t="n">
-        <v>543.34</v>
+        <v>546.6</v>
       </c>
       <c r="F188" s="7" t="inlineStr"/>
     </row>
@@ -4526,10 +4526,10 @@
         <v>120.86</v>
       </c>
       <c r="D189" s="5" t="n">
-        <v>142.68</v>
+        <v>143.54</v>
       </c>
       <c r="E189" s="5" t="n">
-        <v>155.13</v>
+        <v>156.06</v>
       </c>
       <c r="F189" s="7" t="inlineStr"/>
     </row>
@@ -4546,10 +4546,10 @@
         <v>177.81</v>
       </c>
       <c r="D190" s="5" t="n">
-        <v>168.29</v>
+        <v>169.3</v>
       </c>
       <c r="E190" s="5" t="n">
-        <v>228.24</v>
+        <v>229.61</v>
       </c>
       <c r="F190" s="7" t="inlineStr"/>
     </row>
@@ -4566,10 +4566,10 @@
         <v>106.79</v>
       </c>
       <c r="D191" s="5" t="n">
-        <v>126.11</v>
+        <v>126.87</v>
       </c>
       <c r="E191" s="5" t="n">
-        <v>136.81</v>
+        <v>137.63</v>
       </c>
       <c r="F191" s="7" t="inlineStr"/>
     </row>
@@ -4586,10 +4586,10 @@
         <v>104.25</v>
       </c>
       <c r="D192" s="5" t="n">
-        <v>117.5</v>
+        <v>118.2</v>
       </c>
       <c r="E192" s="5" t="n">
-        <v>133.29</v>
+        <v>134.09</v>
       </c>
       <c r="F192" s="7" t="inlineStr"/>
     </row>
@@ -4606,10 +4606,10 @@
         <v>122.01</v>
       </c>
       <c r="D193" s="5" t="n">
-        <v>129.91</v>
+        <v>130.69</v>
       </c>
       <c r="E193" s="5" t="n">
-        <v>155.69</v>
+        <v>156.62</v>
       </c>
       <c r="F193" s="7" t="inlineStr"/>
     </row>
@@ -4626,10 +4626,10 @@
         <v>105.02</v>
       </c>
       <c r="D194" s="5" t="n">
-        <v>109.43</v>
+        <v>110.09</v>
       </c>
       <c r="E194" s="5" t="n">
-        <v>133.76</v>
+        <v>134.56</v>
       </c>
       <c r="F194" s="7" t="inlineStr"/>
     </row>
@@ -4646,10 +4646,10 @@
         <v>130.29</v>
       </c>
       <c r="D195" s="5" t="n">
-        <v>133.42</v>
+        <v>134.22</v>
       </c>
       <c r="E195" s="5" t="n">
-        <v>165.63</v>
+        <v>166.62</v>
       </c>
       <c r="F195" s="7" t="inlineStr"/>
     </row>
@@ -4666,10 +4666,10 @@
         <v>121.93</v>
       </c>
       <c r="D196" s="5" t="n">
-        <v>132.93</v>
+        <v>133.72</v>
       </c>
       <c r="E196" s="5" t="n">
-        <v>154.71</v>
+        <v>155.64</v>
       </c>
       <c r="F196" s="7" t="inlineStr"/>
     </row>
@@ -4686,10 +4686,10 @@
         <v>113.03</v>
       </c>
       <c r="D197" s="5" t="n">
-        <v>127.48</v>
+        <v>128.25</v>
       </c>
       <c r="E197" s="5" t="n">
-        <v>143.09</v>
+        <v>143.95</v>
       </c>
       <c r="F197" s="7" t="inlineStr"/>
     </row>
@@ -4706,10 +4706,10 @@
         <v>69.79000000000001</v>
       </c>
       <c r="D198" s="5" t="n">
-        <v>85.87</v>
+        <v>86.38</v>
       </c>
       <c r="E198" s="5" t="n">
-        <v>88.15000000000001</v>
+        <v>88.68000000000001</v>
       </c>
       <c r="F198" s="7" t="inlineStr"/>
     </row>
@@ -4726,10 +4726,10 @@
         <v>77.45999999999999</v>
       </c>
       <c r="D199" s="5" t="n">
-        <v>77.37</v>
+        <v>77.83</v>
       </c>
       <c r="E199" s="5" t="n">
-        <v>97.62</v>
+        <v>98.2</v>
       </c>
       <c r="F199" s="7" t="inlineStr"/>
     </row>
@@ -4746,10 +4746,10 @@
         <v>255.88</v>
       </c>
       <c r="D200" s="5" t="n">
-        <v>179.93</v>
+        <v>181.01</v>
       </c>
       <c r="E200" s="5" t="n">
-        <v>322.07</v>
+        <v>324</v>
       </c>
       <c r="F200" s="7" t="inlineStr"/>
     </row>
@@ -4766,10 +4766,10 @@
         <v>55.83</v>
       </c>
       <c r="D201" s="5" t="n">
-        <v>60.73</v>
+        <v>61.1</v>
       </c>
       <c r="E201" s="5" t="n">
-        <v>70.18000000000001</v>
+        <v>70.61</v>
       </c>
       <c r="F201" s="7" t="inlineStr"/>
     </row>
@@ -4786,10 +4786,10 @@
         <v>50.47</v>
       </c>
       <c r="D202" s="5" t="n">
-        <v>54.37</v>
+        <v>54.69</v>
       </c>
       <c r="E202" s="5" t="n">
-        <v>63.37</v>
+        <v>63.75</v>
       </c>
       <c r="F202" s="7" t="inlineStr"/>
     </row>
@@ -4806,10 +4806,10 @@
         <v>41.9</v>
       </c>
       <c r="D203" s="5" t="n">
-        <v>44.01</v>
+        <v>44.28</v>
       </c>
       <c r="E203" s="5" t="n">
-        <v>52.95</v>
+        <v>53.27</v>
       </c>
       <c r="F203" s="7" t="inlineStr"/>
     </row>
@@ -4826,10 +4826,10 @@
         <v>47.04</v>
       </c>
       <c r="D204" s="5" t="n">
-        <v>48.7</v>
+        <v>48.99</v>
       </c>
       <c r="E204" s="5" t="n">
-        <v>59.83</v>
+        <v>60.19</v>
       </c>
       <c r="F204" s="7" t="inlineStr"/>
     </row>
@@ -4846,10 +4846,10 @@
         <v>62.91</v>
       </c>
       <c r="D205" s="5" t="n">
-        <v>62.3</v>
+        <v>62.67</v>
       </c>
       <c r="E205" s="5" t="n">
-        <v>80.54000000000001</v>
+        <v>81.02</v>
       </c>
       <c r="F205" s="7" t="inlineStr"/>
     </row>
@@ -4866,10 +4866,10 @@
         <v>75.01000000000001</v>
       </c>
       <c r="D206" s="5" t="n">
-        <v>81</v>
+        <v>81.48999999999999</v>
       </c>
       <c r="E206" s="5" t="n">
-        <v>95.54000000000001</v>
+        <v>96.11</v>
       </c>
       <c r="F206" s="7" t="inlineStr"/>
     </row>
@@ -4886,10 +4886,10 @@
         <v>66.40000000000001</v>
       </c>
       <c r="D207" s="5" t="n">
-        <v>68.04000000000001</v>
+        <v>68.45</v>
       </c>
       <c r="E207" s="5" t="n">
-        <v>84.14</v>
+        <v>84.64</v>
       </c>
       <c r="F207" s="7" t="inlineStr"/>
     </row>
@@ -4906,10 +4906,10 @@
         <v>39.08</v>
       </c>
       <c r="D208" s="5" t="n">
-        <v>43.68</v>
+        <v>43.94</v>
       </c>
       <c r="E208" s="5" t="n">
-        <v>49.27</v>
+        <v>49.56</v>
       </c>
       <c r="F208" s="7" t="inlineStr"/>
     </row>
@@ -4926,10 +4926,10 @@
         <v>55.4</v>
       </c>
       <c r="D209" s="5" t="n">
-        <v>56.3</v>
+        <v>56.63</v>
       </c>
       <c r="E209" s="5" t="n">
-        <v>69.63</v>
+        <v>70.05</v>
       </c>
       <c r="F209" s="7" t="inlineStr"/>
     </row>
@@ -4946,10 +4946,10 @@
         <v>49.88</v>
       </c>
       <c r="D210" s="5" t="n">
-        <v>55.23</v>
+        <v>55.56</v>
       </c>
       <c r="E210" s="5" t="n">
-        <v>62.51</v>
+        <v>62.88</v>
       </c>
       <c r="F210" s="7" t="inlineStr"/>
     </row>
@@ -4966,10 +4966,10 @@
         <v>23.5</v>
       </c>
       <c r="D211" s="5" t="n">
-        <v>29.72</v>
+        <v>29.9</v>
       </c>
       <c r="E211" s="5" t="n">
-        <v>29.36</v>
+        <v>29.54</v>
       </c>
       <c r="F211" s="7" t="inlineStr"/>
     </row>
@@ -4986,10 +4986,10 @@
         <v>20.68</v>
       </c>
       <c r="D212" s="5" t="n">
-        <v>28.46</v>
+        <v>28.63</v>
       </c>
       <c r="E212" s="5" t="n">
-        <v>25.79</v>
+        <v>25.94</v>
       </c>
       <c r="F212" s="7" t="inlineStr"/>
     </row>
@@ -5006,10 +5006,10 @@
         <v>24.89</v>
       </c>
       <c r="D213" s="5" t="n">
-        <v>27.19</v>
+        <v>27.36</v>
       </c>
       <c r="E213" s="5" t="n">
-        <v>30.98</v>
+        <v>31.16</v>
       </c>
       <c r="F213" s="7" t="inlineStr"/>
     </row>
@@ -5026,10 +5026,10 @@
         <v>32.84</v>
       </c>
       <c r="D214" s="5" t="n">
-        <v>37.71</v>
+        <v>37.94</v>
       </c>
       <c r="E214" s="5" t="n">
-        <v>40.79</v>
+        <v>41.04</v>
       </c>
       <c r="F214" s="7" t="inlineStr"/>
     </row>
@@ -5046,10 +5046,10 @@
         <v>62.46</v>
       </c>
       <c r="D215" s="5" t="n">
-        <v>61.3</v>
+        <v>61.67</v>
       </c>
       <c r="E215" s="5" t="n">
-        <v>77.40000000000001</v>
+        <v>77.86</v>
       </c>
       <c r="F215" s="7" t="inlineStr"/>
     </row>
@@ -5066,10 +5066,10 @@
         <v>114.98</v>
       </c>
       <c r="D216" s="5" t="n">
-        <v>90.04000000000001</v>
+        <v>90.58</v>
       </c>
       <c r="E216" s="5" t="n">
-        <v>142.14</v>
+        <v>142.99</v>
       </c>
       <c r="F216" s="7" t="inlineStr"/>
     </row>
@@ -5086,10 +5086,10 @@
         <v>107.95</v>
       </c>
       <c r="D217" s="5" t="n">
-        <v>108.42</v>
+        <v>109.07</v>
       </c>
       <c r="E217" s="5" t="n">
-        <v>133.12</v>
+        <v>133.92</v>
       </c>
       <c r="F217" s="7" t="inlineStr"/>
     </row>
@@ -5106,10 +5106,10 @@
         <v>126.87</v>
       </c>
       <c r="D218" s="5" t="n">
-        <v>112.79</v>
+        <v>113.46</v>
       </c>
       <c r="E218" s="5" t="n">
-        <v>156.01</v>
+        <v>156.95</v>
       </c>
       <c r="F218" s="7" t="inlineStr"/>
     </row>
@@ -5126,10 +5126,10 @@
         <v>55.18</v>
       </c>
       <c r="D219" s="5" t="n">
-        <v>57.63</v>
+        <v>57.98</v>
       </c>
       <c r="E219" s="5" t="n">
-        <v>67.66</v>
+        <v>68.06999999999999</v>
       </c>
       <c r="F219" s="7" t="inlineStr"/>
     </row>
@@ -5146,10 +5146,10 @@
         <v>33.73</v>
       </c>
       <c r="D220" s="5" t="n">
-        <v>33.9</v>
+        <v>34.1</v>
       </c>
       <c r="E220" s="5" t="n">
-        <v>41.24</v>
+        <v>41.49</v>
       </c>
       <c r="F220" s="7" t="inlineStr"/>
     </row>
@@ -5166,10 +5166,10 @@
         <v>15.09</v>
       </c>
       <c r="D221" s="5" t="n">
-        <v>22.48</v>
+        <v>22.61</v>
       </c>
       <c r="E221" s="5" t="n">
-        <v>18.37</v>
+        <v>18.48</v>
       </c>
       <c r="F221" s="7" t="inlineStr"/>
     </row>
@@ -5186,10 +5186,10 @@
         <v>40.78</v>
       </c>
       <c r="D222" s="5" t="n">
-        <v>42.46</v>
+        <v>42.72</v>
       </c>
       <c r="E222" s="5" t="n">
-        <v>49.45</v>
+        <v>49.74</v>
       </c>
       <c r="F222" s="7" t="inlineStr"/>
     </row>
@@ -5206,10 +5206,10 @@
         <v>30.8</v>
       </c>
       <c r="D223" s="5" t="n">
-        <v>38.91</v>
+        <v>39.15</v>
       </c>
       <c r="E223" s="5" t="n">
-        <v>37.19</v>
+        <v>37.41</v>
       </c>
       <c r="F223" s="7" t="inlineStr"/>
     </row>
@@ -5226,10 +5226,10 @@
         <v>75.01000000000001</v>
       </c>
       <c r="D224" s="5" t="n">
-        <v>72.91</v>
+        <v>73.34999999999999</v>
       </c>
       <c r="E224" s="5" t="n">
-        <v>89.92</v>
+        <v>90.45999999999999</v>
       </c>
       <c r="F224" s="7" t="inlineStr"/>
     </row>
@@ -5246,10 +5246,10 @@
         <v>48.54</v>
       </c>
       <c r="D225" s="5" t="n">
-        <v>64.48</v>
+        <v>64.86</v>
       </c>
       <c r="E225" s="5" t="n">
-        <v>57.78</v>
+        <v>58.12</v>
       </c>
       <c r="F225" s="7" t="inlineStr"/>
     </row>
@@ -5266,10 +5266,10 @@
         <v>56.47</v>
       </c>
       <c r="D226" s="5" t="n">
-        <v>64.73999999999999</v>
+        <v>65.13</v>
       </c>
       <c r="E226" s="5" t="n">
-        <v>66.73999999999999</v>
+        <v>67.14</v>
       </c>
       <c r="F226" s="7" t="inlineStr"/>
     </row>
@@ -5286,10 +5286,10 @@
         <v>168.15</v>
       </c>
       <c r="D227" s="5" t="n">
-        <v>166.25</v>
+        <v>167.25</v>
       </c>
       <c r="E227" s="5" t="n">
-        <v>197.55</v>
+        <v>198.74</v>
       </c>
       <c r="F227" s="7" t="inlineStr"/>
     </row>
@@ -5306,10 +5306,10 @@
         <v>264.24</v>
       </c>
       <c r="D228" s="5" t="n">
-        <v>272.88</v>
+        <v>274.51</v>
       </c>
       <c r="E228" s="5" t="n">
-        <v>308.62</v>
+        <v>310.47</v>
       </c>
       <c r="F228" s="7" t="inlineStr"/>
     </row>
@@ -5326,10 +5326,10 @@
         <v>375.96</v>
       </c>
       <c r="D229" s="5" t="n">
-        <v>344.25</v>
+        <v>346.32</v>
       </c>
       <c r="E229" s="5" t="n">
-        <v>436.52</v>
+        <v>439.14</v>
       </c>
       <c r="F229" s="7" t="inlineStr"/>
     </row>
@@ -5346,10 +5346,10 @@
         <v>432</v>
       </c>
       <c r="D230" s="5" t="n">
-        <v>392.76</v>
+        <v>395.12</v>
       </c>
       <c r="E230" s="5" t="n">
-        <v>498.54</v>
+        <v>501.53</v>
       </c>
       <c r="F230" s="7" t="inlineStr"/>
     </row>
@@ -5366,10 +5366,10 @@
         <v>137.33</v>
       </c>
       <c r="D231" s="5" t="n">
-        <v>138.8</v>
+        <v>139.64</v>
       </c>
       <c r="E231" s="5" t="n">
-        <v>157.52</v>
+        <v>158.47</v>
       </c>
       <c r="F231" s="7" t="inlineStr"/>
     </row>
@@ -5386,10 +5386,10 @@
         <v>130.9</v>
       </c>
       <c r="D232" s="5" t="n">
-        <v>127.43</v>
+        <v>128.2</v>
       </c>
       <c r="E232" s="5" t="n">
-        <v>149.24</v>
+        <v>150.14</v>
       </c>
       <c r="F232" s="7" t="inlineStr"/>
     </row>
@@ -5406,10 +5406,10 @@
         <v>97.36</v>
       </c>
       <c r="D233" s="5" t="n">
-        <v>112.07</v>
+        <v>112.74</v>
       </c>
       <c r="E233" s="5" t="n">
-        <v>110.32</v>
+        <v>110.98</v>
       </c>
       <c r="F233" s="7" t="inlineStr"/>
     </row>
@@ -5426,10 +5426,10 @@
         <v>58.3</v>
       </c>
       <c r="D234" s="5" t="n">
-        <v>66.03</v>
+        <v>66.43000000000001</v>
       </c>
       <c r="E234" s="5" t="n">
-        <v>65.66</v>
+        <v>66.05</v>
       </c>
       <c r="F234" s="7" t="inlineStr"/>
     </row>
@@ -5446,10 +5446,10 @@
         <v>11.57</v>
       </c>
       <c r="D235" s="5" t="n">
-        <v>35.02</v>
+        <v>35.23</v>
       </c>
       <c r="E235" s="5" t="n">
-        <v>12.95</v>
+        <v>13.03</v>
       </c>
       <c r="F235" s="7" t="inlineStr"/>
     </row>
@@ -5466,10 +5466,10 @@
         <v>32.05</v>
       </c>
       <c r="D236" s="5" t="n">
-        <v>53.59</v>
+        <v>53.91</v>
       </c>
       <c r="E236" s="5" t="n">
-        <v>35.72</v>
+        <v>35.93</v>
       </c>
       <c r="F236" s="7" t="inlineStr"/>
     </row>
@@ -5486,10 +5486,10 @@
         <v>55.29</v>
       </c>
       <c r="D237" s="5" t="n">
-        <v>64.36</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="E237" s="5" t="n">
-        <v>61.34</v>
+        <v>61.71</v>
       </c>
       <c r="F237" s="7" t="inlineStr"/>
     </row>
@@ -5506,10 +5506,10 @@
         <v>54.59</v>
       </c>
       <c r="D238" s="5" t="n">
-        <v>68.5</v>
+        <v>68.91</v>
       </c>
       <c r="E238" s="5" t="n">
-        <v>60.29</v>
+        <v>60.65</v>
       </c>
       <c r="F238" s="7" t="inlineStr"/>
     </row>
@@ -5526,10 +5526,10 @@
         <v>86.78</v>
       </c>
       <c r="D239" s="5" t="n">
-        <v>92.09</v>
+        <v>92.65000000000001</v>
       </c>
       <c r="E239" s="5" t="n">
-        <v>95.56999999999999</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="F239" s="7" t="inlineStr"/>
     </row>
@@ -5546,10 +5546,10 @@
         <v>145.97</v>
       </c>
       <c r="D240" s="5" t="n">
-        <v>139.64</v>
+        <v>140.47</v>
       </c>
       <c r="E240" s="5" t="n">
-        <v>160.3</v>
+        <v>161.26</v>
       </c>
       <c r="F240" s="7" t="inlineStr"/>
     </row>
@@ -5566,10 +5566,10 @@
         <v>85.79000000000001</v>
       </c>
       <c r="D241" s="5" t="n">
-        <v>59.71</v>
+        <v>60.07</v>
       </c>
       <c r="E241" s="5" t="n">
-        <v>93.95</v>
+        <v>94.51000000000001</v>
       </c>
       <c r="F241" s="7" t="inlineStr"/>
     </row>
@@ -5586,10 +5586,10 @@
         <v>76.38</v>
       </c>
       <c r="D242" s="5" t="n">
-        <v>60.23</v>
+        <v>60.59</v>
       </c>
       <c r="E242" s="5" t="n">
-        <v>83.31999999999999</v>
+        <v>83.81999999999999</v>
       </c>
       <c r="F242" s="7" t="inlineStr"/>
     </row>
@@ -5606,10 +5606,10 @@
         <v>80.04000000000001</v>
       </c>
       <c r="D243" s="5" t="n">
-        <v>70.27</v>
+        <v>70.69</v>
       </c>
       <c r="E243" s="5" t="n">
-        <v>86.98</v>
+        <v>87.5</v>
       </c>
       <c r="F243" s="7" t="inlineStr"/>
     </row>
@@ -5626,10 +5626,10 @@
         <v>28.16</v>
       </c>
       <c r="D244" s="5" t="n">
-        <v>28.48</v>
+        <v>28.65</v>
       </c>
       <c r="E244" s="5" t="n">
-        <v>30.49</v>
+        <v>30.67</v>
       </c>
       <c r="F244" s="7" t="inlineStr"/>
     </row>
@@ -5646,10 +5646,10 @@
         <v>15.14</v>
       </c>
       <c r="D245" s="5" t="n">
-        <v>18.57</v>
+        <v>18.68</v>
       </c>
       <c r="E245" s="5" t="n">
-        <v>16.36</v>
+        <v>16.45</v>
       </c>
       <c r="F245" s="7" t="inlineStr"/>
     </row>
@@ -5666,10 +5666,10 @@
         <v>31.79</v>
       </c>
       <c r="D246" s="5" t="n">
-        <v>37.67</v>
+        <v>37.89</v>
       </c>
       <c r="E246" s="5" t="n">
-        <v>34.27</v>
+        <v>34.48</v>
       </c>
       <c r="F246" s="7" t="inlineStr"/>
     </row>
@@ -5686,10 +5686,10 @@
         <v>25.23</v>
       </c>
       <c r="D247" s="5" t="n">
-        <v>27.21</v>
+        <v>27.37</v>
       </c>
       <c r="E247" s="5" t="n">
-        <v>27.14</v>
+        <v>27.31</v>
       </c>
       <c r="F247" s="7" t="inlineStr"/>
     </row>
@@ -5706,10 +5706,10 @@
         <v>17.65</v>
       </c>
       <c r="D248" s="5" t="n">
-        <v>23.7</v>
+        <v>23.84</v>
       </c>
       <c r="E248" s="5" t="n">
-        <v>18.93</v>
+        <v>19.04</v>
       </c>
       <c r="F248" s="7" t="inlineStr"/>
     </row>
@@ -5726,10 +5726,10 @@
         <v>133.13</v>
       </c>
       <c r="D249" s="5" t="n">
-        <v>88.68000000000001</v>
+        <v>89.20999999999999</v>
       </c>
       <c r="E249" s="5" t="n">
-        <v>142.34</v>
+        <v>143.2</v>
       </c>
       <c r="F249" s="7" t="inlineStr"/>
     </row>
@@ -5746,10 +5746,10 @@
         <v>46.25</v>
       </c>
       <c r="D250" s="5" t="n">
-        <v>55.42</v>
+        <v>55.75</v>
       </c>
       <c r="E250" s="5" t="n">
-        <v>49.3</v>
+        <v>49.59</v>
       </c>
       <c r="F250" s="7" t="inlineStr"/>
     </row>
@@ -5766,10 +5766,10 @@
         <v>80.23</v>
       </c>
       <c r="D251" s="5" t="n">
-        <v>90.08</v>
+        <v>90.62</v>
       </c>
       <c r="E251" s="5" t="n">
-        <v>85.22</v>
+        <v>85.73</v>
       </c>
       <c r="F251" s="7" t="inlineStr"/>
     </row>
@@ -5786,10 +5786,10 @@
         <v>146.58</v>
       </c>
       <c r="D252" s="5" t="n">
-        <v>140.75</v>
+        <v>141.6</v>
       </c>
       <c r="E252" s="5" t="n">
-        <v>155.16</v>
+        <v>156.09</v>
       </c>
       <c r="F252" s="7" t="inlineStr"/>
     </row>
@@ -5806,10 +5806,10 @@
         <v>198.82</v>
       </c>
       <c r="D253" s="5" t="n">
-        <v>173.24</v>
+        <v>174.28</v>
       </c>
       <c r="E253" s="5" t="n">
-        <v>209.73</v>
+        <v>210.99</v>
       </c>
       <c r="F253" s="7" t="inlineStr"/>
     </row>
@@ -5826,10 +5826,10 @@
         <v>191.83</v>
       </c>
       <c r="D254" s="5" t="n">
-        <v>157.21</v>
+        <v>158.15</v>
       </c>
       <c r="E254" s="5" t="n">
-        <v>202.21</v>
+        <v>203.42</v>
       </c>
       <c r="F254" s="7" t="inlineStr"/>
     </row>
@@ -5846,10 +5846,10 @@
         <v>216.14</v>
       </c>
       <c r="D255" s="5" t="n">
-        <v>151.05</v>
+        <v>151.95</v>
       </c>
       <c r="E255" s="5" t="n">
-        <v>227.67</v>
+        <v>229.03</v>
       </c>
       <c r="F255" s="7" t="inlineStr"/>
     </row>
@@ -5866,10 +5866,10 @@
         <v>26.5</v>
       </c>
       <c r="D256" s="5" t="n">
-        <v>18.3</v>
+        <v>18.41</v>
       </c>
       <c r="E256" s="5" t="n">
-        <v>27.89</v>
+        <v>28.06</v>
       </c>
       <c r="F256" s="7" t="inlineStr"/>
     </row>
@@ -5886,10 +5886,10 @@
         <v>10.18</v>
       </c>
       <c r="D257" s="5" t="n">
-        <v>21.42</v>
+        <v>21.54</v>
       </c>
       <c r="E257" s="5" t="n">
-        <v>10.71</v>
+        <v>10.77</v>
       </c>
       <c r="F257" s="7" t="inlineStr"/>
     </row>
@@ -5906,10 +5906,10 @@
         <v>52.94</v>
       </c>
       <c r="D258" s="5" t="n">
-        <v>67.36</v>
+        <v>67.76000000000001</v>
       </c>
       <c r="E258" s="5" t="n">
-        <v>55.65</v>
+        <v>55.98</v>
       </c>
       <c r="F258" s="7" t="inlineStr"/>
     </row>
@@ -5926,10 +5926,10 @@
         <v>39.93</v>
       </c>
       <c r="D259" s="5" t="n">
-        <v>54.89</v>
+        <v>55.22</v>
       </c>
       <c r="E259" s="5" t="n">
-        <v>41.95</v>
+        <v>42.2</v>
       </c>
       <c r="F259" s="7" t="inlineStr"/>
     </row>
@@ -5946,10 +5946,10 @@
         <v>23.72</v>
       </c>
       <c r="D260" s="5" t="n">
-        <v>50.64</v>
+        <v>50.94</v>
       </c>
       <c r="E260" s="5" t="n">
-        <v>24.84</v>
+        <v>24.99</v>
       </c>
       <c r="F260" s="7" t="inlineStr"/>
     </row>
@@ -5966,10 +5966,10 @@
         <v>76.73</v>
       </c>
       <c r="D261" s="5" t="n">
-        <v>71.56999999999999</v>
+        <v>72</v>
       </c>
       <c r="E261" s="5" t="n">
-        <v>80.11</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="F261" s="7" t="inlineStr"/>
     </row>
@@ -5986,10 +5986,10 @@
         <v>62.93</v>
       </c>
       <c r="D262" s="5" t="n">
-        <v>64.28</v>
+        <v>64.66</v>
       </c>
       <c r="E262" s="5" t="n">
-        <v>65.51000000000001</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="F262" s="7" t="inlineStr"/>
     </row>
@@ -6006,10 +6006,10 @@
         <v>70.56</v>
       </c>
       <c r="D263" s="5" t="n">
-        <v>77.63</v>
+        <v>78.09</v>
       </c>
       <c r="E263" s="5" t="n">
-        <v>73.27</v>
+        <v>73.70999999999999</v>
       </c>
       <c r="F263" s="7" t="inlineStr"/>
     </row>
@@ -6026,10 +6026,10 @@
         <v>93.92</v>
       </c>
       <c r="D264" s="5" t="n">
-        <v>80.84</v>
+        <v>81.33</v>
       </c>
       <c r="E264" s="5" t="n">
-        <v>97.28</v>
+        <v>97.86</v>
       </c>
       <c r="F264" s="7" t="inlineStr"/>
     </row>
@@ -6046,10 +6046,10 @@
         <v>463.18</v>
       </c>
       <c r="D265" s="5" t="n">
-        <v>273.39</v>
+        <v>275.03</v>
       </c>
       <c r="E265" s="5" t="n">
-        <v>478.57</v>
+        <v>481.44</v>
       </c>
       <c r="F265" s="7" t="inlineStr"/>
     </row>
@@ -6066,10 +6066,10 @@
         <v>107.96</v>
       </c>
       <c r="D266" s="5" t="n">
-        <v>84.48999999999999</v>
+        <v>84.98999999999999</v>
       </c>
       <c r="E266" s="5" t="n">
-        <v>111.06</v>
+        <v>111.72</v>
       </c>
       <c r="F266" s="7" t="inlineStr"/>
     </row>
@@ -6086,10 +6086,10 @@
         <v>107.79</v>
       </c>
       <c r="D267" s="5" t="n">
-        <v>95.45</v>
+        <v>96.02</v>
       </c>
       <c r="E267" s="5" t="n">
-        <v>110.4</v>
+        <v>111.06</v>
       </c>
       <c r="F267" s="7" t="inlineStr"/>
     </row>
@@ -6106,10 +6106,10 @@
         <v>61.8</v>
       </c>
       <c r="D268" s="5" t="n">
-        <v>56.36</v>
+        <v>56.7</v>
       </c>
       <c r="E268" s="5" t="n">
-        <v>63.02</v>
+        <v>63.4</v>
       </c>
       <c r="F268" s="7" t="inlineStr"/>
     </row>
@@ -6126,10 +6126,10 @@
         <v>45.13</v>
       </c>
       <c r="D269" s="5" t="n">
-        <v>52.28</v>
+        <v>52.6</v>
       </c>
       <c r="E269" s="5" t="n">
-        <v>45.93</v>
+        <v>46.21</v>
       </c>
       <c r="F269" s="7" t="inlineStr"/>
     </row>
@@ -6146,10 +6146,10 @@
         <v>13.79</v>
       </c>
       <c r="D270" s="5" t="n">
-        <v>32.42</v>
+        <v>32.62</v>
       </c>
       <c r="E270" s="5" t="n">
-        <v>14.01</v>
+        <v>14.09</v>
       </c>
       <c r="F270" s="7" t="inlineStr"/>
     </row>
@@ -6166,10 +6166,10 @@
         <v>16.99</v>
       </c>
       <c r="D271" s="5" t="n">
-        <v>27.89</v>
+        <v>28.06</v>
       </c>
       <c r="E271" s="5" t="n">
-        <v>17.22</v>
+        <v>17.33</v>
       </c>
       <c r="F271" s="7" t="inlineStr"/>
     </row>
@@ -6186,10 +6186,10 @@
         <v>43.74</v>
       </c>
       <c r="D272" s="5" t="n">
-        <v>38.9</v>
+        <v>39.14</v>
       </c>
       <c r="E272" s="5" t="n">
-        <v>44.14</v>
+        <v>44.4</v>
       </c>
       <c r="F272" s="7" t="inlineStr"/>
     </row>
@@ -6206,10 +6206,10 @@
         <v>40.2</v>
       </c>
       <c r="D273" s="5" t="n">
-        <v>45.26</v>
+        <v>45.54</v>
       </c>
       <c r="E273" s="5" t="n">
-        <v>40.38</v>
+        <v>40.62</v>
       </c>
       <c r="F273" s="7" t="inlineStr"/>
     </row>
@@ -6226,10 +6226,10 @@
         <v>44.39</v>
       </c>
       <c r="D274" s="5" t="n">
-        <v>41.17</v>
+        <v>41.42</v>
       </c>
       <c r="E274" s="5" t="n">
-        <v>44.39</v>
+        <v>44.66</v>
       </c>
       <c r="F274" s="7" t="inlineStr"/>
     </row>
@@ -6246,10 +6246,10 @@
         <v>39.73</v>
       </c>
       <c r="D275" s="5" t="n">
-        <v>32.76</v>
+        <v>32.89</v>
       </c>
       <c r="E275" s="5" t="n">
-        <v>39.73</v>
+        <v>39.89</v>
       </c>
       <c r="F275" s="7" t="inlineStr"/>
     </row>
@@ -6266,10 +6266,10 @@
         <v>44.24</v>
       </c>
       <c r="D276" s="5" t="n">
-        <v>42.63</v>
+        <v>42.71</v>
       </c>
       <c r="E276" s="5" t="n">
-        <v>44.24</v>
+        <v>44.33</v>
       </c>
       <c r="F276" s="7" t="inlineStr"/>
     </row>
@@ -6312,6 +6312,26 @@
         <v>110.53</v>
       </c>
       <c r="F278" s="7" t="inlineStr"/>
+    </row>
+    <row r="279">
+      <c r="A279" s="4" t="inlineStr">
+        <is>
+          <t>Aug 2026</t>
+        </is>
+      </c>
+      <c r="B279" s="5" t="n">
+        <v>62.06</v>
+      </c>
+      <c r="C279" s="5" t="n">
+        <v>80.65000000000001</v>
+      </c>
+      <c r="D279" s="5" t="n">
+        <v>62.06</v>
+      </c>
+      <c r="E279" s="5" t="n">
+        <v>80.65000000000001</v>
+      </c>
+      <c r="F279" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6324,7 +6344,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E278"/>
+  <dimension ref="A1:E279"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6374,10 +6394,10 @@
         <v>32.99</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>47.61</v>
+        <v>47.9</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>61.31</v>
+        <v>61.68</v>
       </c>
     </row>
     <row r="3">
@@ -6393,10 +6413,10 @@
         <v>23.45</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>37.38</v>
+        <v>37.6</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>43.5</v>
+        <v>43.76</v>
       </c>
     </row>
     <row r="4">
@@ -6412,10 +6432,10 @@
         <v>25.19</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>38.38</v>
+        <v>38.61</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>46.64</v>
+        <v>46.92</v>
       </c>
     </row>
     <row r="5">
@@ -6431,10 +6451,10 @@
         <v>25.19</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>38.33</v>
+        <v>38.56</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>46.56</v>
+        <v>46.84</v>
       </c>
     </row>
     <row r="6">
@@ -6450,10 +6470,10 @@
         <v>26.23</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>39.08</v>
+        <v>39.31</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>48.39</v>
+        <v>48.68</v>
       </c>
     </row>
     <row r="7">
@@ -6469,10 +6489,10 @@
         <v>34.01</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>45.99</v>
+        <v>46.26</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>62.64</v>
+        <v>63.01</v>
       </c>
     </row>
     <row r="8">
@@ -6488,10 +6508,10 @@
         <v>30.37</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>41.35</v>
+        <v>41.6</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>55.77</v>
+        <v>56.1</v>
       </c>
     </row>
     <row r="9">
@@ -6507,10 +6527,10 @@
         <v>48.76</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>70.70999999999999</v>
+        <v>71.13</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>89.27</v>
+        <v>89.81</v>
       </c>
     </row>
     <row r="10">
@@ -6526,10 +6546,10 @@
         <v>28.54</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>39.21</v>
+        <v>39.45</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>52.1</v>
+        <v>52.41</v>
       </c>
     </row>
     <row r="11">
@@ -6545,10 +6565,10 @@
         <v>36.99</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>53.7</v>
+        <v>54.02</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>67.42</v>
+        <v>67.83</v>
       </c>
     </row>
     <row r="12">
@@ -6564,10 +6584,10 @@
         <v>39.67</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>56.94</v>
+        <v>57.29</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>72.19</v>
+        <v>72.63</v>
       </c>
     </row>
     <row r="13">
@@ -6583,10 +6603,10 @@
         <v>34.73</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>52.02</v>
+        <v>52.33</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>63.11</v>
+        <v>63.48</v>
       </c>
     </row>
     <row r="14">
@@ -6602,10 +6622,10 @@
         <v>43.7</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>56.92</v>
+        <v>57.26</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>79.3</v>
+        <v>79.77</v>
       </c>
     </row>
     <row r="15">
@@ -6621,10 +6641,10 @@
         <v>27.37</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>40.86</v>
+        <v>41.11</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>49.6</v>
+        <v>49.89</v>
       </c>
     </row>
     <row r="16">
@@ -6640,10 +6660,10 @@
         <v>31.48</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>49.22</v>
+        <v>49.52</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>56.97</v>
+        <v>57.31</v>
       </c>
     </row>
     <row r="17">
@@ -6659,10 +6679,10 @@
         <v>70.45</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>81.01000000000001</v>
+        <v>81.48999999999999</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>127.16</v>
+        <v>127.93</v>
       </c>
     </row>
     <row r="18">
@@ -6678,10 +6698,10 @@
         <v>44.55</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>64.2</v>
+        <v>64.59</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>80.20999999999999</v>
+        <v>80.69</v>
       </c>
     </row>
     <row r="19">
@@ -6697,10 +6717,10 @@
         <v>33</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>49.13</v>
+        <v>49.43</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>59.26</v>
+        <v>59.62</v>
       </c>
     </row>
     <row r="20">
@@ -6716,10 +6736,10 @@
         <v>29.72</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>40.93</v>
+        <v>41.17</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>53.25</v>
+        <v>53.57</v>
       </c>
     </row>
     <row r="21">
@@ -6735,10 +6755,10 @@
         <v>27.43</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>39.03</v>
+        <v>39.26</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>49.04</v>
+        <v>49.34</v>
       </c>
     </row>
     <row r="22">
@@ -6754,10 +6774,10 @@
         <v>21.15</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>33.36</v>
+        <v>33.56</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>37.73</v>
+        <v>37.96</v>
       </c>
     </row>
     <row r="23">
@@ -6773,10 +6793,10 @@
         <v>37.8</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>54.53</v>
+        <v>54.86</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>67.3</v>
+        <v>67.7</v>
       </c>
     </row>
     <row r="24">
@@ -6792,10 +6812,10 @@
         <v>29.2</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>43.64</v>
+        <v>43.9</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>51.88</v>
+        <v>52.19</v>
       </c>
     </row>
     <row r="25">
@@ -6811,10 +6831,10 @@
         <v>27.29</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>41.74</v>
+        <v>41.99</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>48.39</v>
+        <v>48.68</v>
       </c>
     </row>
     <row r="26">
@@ -6830,10 +6850,10 @@
         <v>32.37</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>46.86</v>
+        <v>47.14</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>57.21</v>
+        <v>57.56</v>
       </c>
     </row>
     <row r="27">
@@ -6849,10 +6869,10 @@
         <v>40.25</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>52.85</v>
+        <v>53.17</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>70.91</v>
+        <v>71.33</v>
       </c>
     </row>
     <row r="28">
@@ -6868,10 +6888,10 @@
         <v>37.44</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>51.17</v>
+        <v>51.47</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>65.73999999999999</v>
+        <v>66.13</v>
       </c>
     </row>
     <row r="29">
@@ -6887,10 +6907,10 @@
         <v>28.49</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>39.68</v>
+        <v>39.92</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>49.94</v>
+        <v>50.24</v>
       </c>
     </row>
     <row r="30">
@@ -6906,10 +6926,10 @@
         <v>46.39</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>53.72</v>
+        <v>54.04</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>81.17</v>
+        <v>81.66</v>
       </c>
     </row>
     <row r="31">
@@ -6925,10 +6945,10 @@
         <v>49.23</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>59.81</v>
+        <v>60.17</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>86</v>
+        <v>86.51000000000001</v>
       </c>
     </row>
     <row r="32">
@@ -6944,10 +6964,10 @@
         <v>88.63</v>
       </c>
       <c r="D32" s="5" t="n">
-        <v>93.08</v>
+        <v>93.64</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>154.38</v>
+        <v>155.3</v>
       </c>
     </row>
     <row r="33">
@@ -6963,10 +6983,10 @@
         <v>105.51</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>97.27</v>
+        <v>97.84999999999999</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>183.26</v>
+        <v>184.36</v>
       </c>
     </row>
     <row r="34">
@@ -6982,10 +7002,10 @@
         <v>29.33</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>40.46</v>
+        <v>40.7</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>50.8</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="35">
@@ -7001,10 +7021,10 @@
         <v>27.86</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>38.92</v>
+        <v>39.15</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>48</v>
+        <v>48.29</v>
       </c>
     </row>
     <row r="36">
@@ -7020,10 +7040,10 @@
         <v>37.94</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>48.42</v>
+        <v>48.71</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>65.02</v>
+        <v>65.41</v>
       </c>
     </row>
     <row r="37">
@@ -7039,10 +7059,10 @@
         <v>42.49</v>
       </c>
       <c r="D37" s="5" t="n">
-        <v>59.01</v>
+        <v>59.36</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>72.44</v>
+        <v>72.88</v>
       </c>
     </row>
     <row r="38">
@@ -7058,10 +7078,10 @@
         <v>71.86</v>
       </c>
       <c r="D38" s="5" t="n">
-        <v>80.23999999999999</v>
+        <v>80.72</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>122.16</v>
+        <v>122.89</v>
       </c>
     </row>
     <row r="39">
@@ -7077,10 +7097,10 @@
         <v>39.11</v>
       </c>
       <c r="D39" s="5" t="n">
-        <v>54.59</v>
+        <v>54.92</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>66.29000000000001</v>
+        <v>66.69</v>
       </c>
     </row>
     <row r="40">
@@ -7096,10 +7116,10 @@
         <v>38.91</v>
       </c>
       <c r="D40" s="5" t="n">
-        <v>52.05</v>
+        <v>52.36</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>65.76000000000001</v>
+        <v>66.15000000000001</v>
       </c>
     </row>
     <row r="41">
@@ -7115,10 +7135,10 @@
         <v>34.69</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>46.76</v>
+        <v>47.04</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>58.65</v>
+        <v>59</v>
       </c>
     </row>
     <row r="42">
@@ -7134,10 +7154,10 @@
         <v>42.78</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>55.32</v>
+        <v>55.65</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>72.34999999999999</v>
+        <v>72.79000000000001</v>
       </c>
     </row>
     <row r="43">
@@ -7153,10 +7173,10 @@
         <v>28.32</v>
       </c>
       <c r="D43" s="5" t="n">
-        <v>37.7</v>
+        <v>37.92</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>47.91</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="44">
@@ -7172,10 +7192,10 @@
         <v>165.37</v>
       </c>
       <c r="D44" s="5" t="n">
-        <v>154.7</v>
+        <v>155.63</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>279.71</v>
+        <v>281.39</v>
       </c>
     </row>
     <row r="45">
@@ -7191,10 +7211,10 @@
         <v>69.13</v>
       </c>
       <c r="D45" s="5" t="n">
-        <v>80.22</v>
+        <v>80.7</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>116.9</v>
+        <v>117.6</v>
       </c>
     </row>
     <row r="46">
@@ -7210,10 +7230,10 @@
         <v>74.84999999999999</v>
       </c>
       <c r="D46" s="5" t="n">
-        <v>90.06999999999999</v>
+        <v>90.61</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>126.53</v>
+        <v>127.29</v>
       </c>
     </row>
     <row r="47">
@@ -7229,10 +7249,10 @@
         <v>81.62</v>
       </c>
       <c r="D47" s="5" t="n">
-        <v>114.08</v>
+        <v>114.76</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>137.41</v>
+        <v>138.24</v>
       </c>
     </row>
     <row r="48">
@@ -7248,10 +7268,10 @@
         <v>75.48999999999999</v>
       </c>
       <c r="D48" s="5" t="n">
-        <v>105.03</v>
+        <v>105.66</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>126.58</v>
+        <v>127.34</v>
       </c>
     </row>
     <row r="49">
@@ -7267,10 +7287,10 @@
         <v>218.05</v>
       </c>
       <c r="D49" s="5" t="n">
-        <v>239.27</v>
+        <v>240.71</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>364.13</v>
+        <v>366.32</v>
       </c>
     </row>
     <row r="50">
@@ -7286,10 +7306,10 @@
         <v>115.22</v>
       </c>
       <c r="D50" s="5" t="n">
-        <v>142.54</v>
+        <v>143.39</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>191.97</v>
+        <v>193.12</v>
       </c>
     </row>
     <row r="51">
@@ -7305,10 +7325,10 @@
         <v>50.83</v>
       </c>
       <c r="D51" s="5" t="n">
-        <v>69.37</v>
+        <v>69.78</v>
       </c>
       <c r="E51" s="5" t="n">
-        <v>84.5</v>
+        <v>85</v>
       </c>
     </row>
     <row r="52">
@@ -7324,10 +7344,10 @@
         <v>55.04</v>
       </c>
       <c r="D52" s="5" t="n">
-        <v>73.94</v>
+        <v>74.38</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>91.28</v>
+        <v>91.83</v>
       </c>
     </row>
     <row r="53">
@@ -7343,10 +7363,10 @@
         <v>45.32</v>
       </c>
       <c r="D53" s="5" t="n">
-        <v>58.71</v>
+        <v>59.06</v>
       </c>
       <c r="E53" s="5" t="n">
-        <v>74.93000000000001</v>
+        <v>75.38</v>
       </c>
     </row>
     <row r="54">
@@ -7362,10 +7382,10 @@
         <v>54.55</v>
       </c>
       <c r="D54" s="5" t="n">
-        <v>70.43000000000001</v>
+        <v>70.84999999999999</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>89.91</v>
+        <v>90.45</v>
       </c>
     </row>
     <row r="55">
@@ -7381,10 +7401,10 @@
         <v>62.08</v>
       </c>
       <c r="D55" s="5" t="n">
-        <v>73.59999999999999</v>
+        <v>74.04000000000001</v>
       </c>
       <c r="E55" s="5" t="n">
-        <v>102.01</v>
+        <v>102.62</v>
       </c>
     </row>
     <row r="56">
@@ -7400,10 +7420,10 @@
         <v>55.11</v>
       </c>
       <c r="D56" s="5" t="n">
-        <v>66.04000000000001</v>
+        <v>66.44</v>
       </c>
       <c r="E56" s="5" t="n">
-        <v>90.16</v>
+        <v>90.7</v>
       </c>
     </row>
     <row r="57">
@@ -7419,10 +7439,10 @@
         <v>52.11</v>
       </c>
       <c r="D57" s="5" t="n">
-        <v>60.07</v>
+        <v>60.43</v>
       </c>
       <c r="E57" s="5" t="n">
-        <v>84.87</v>
+        <v>85.38</v>
       </c>
     </row>
     <row r="58">
@@ -7438,10 +7458,10 @@
         <v>84.56999999999999</v>
       </c>
       <c r="D58" s="5" t="n">
-        <v>84.54000000000001</v>
+        <v>85.05</v>
       </c>
       <c r="E58" s="5" t="n">
-        <v>137.13</v>
+        <v>137.95</v>
       </c>
     </row>
     <row r="59">
@@ -7457,10 +7477,10 @@
         <v>50.14</v>
       </c>
       <c r="D59" s="5" t="n">
-        <v>64.31999999999999</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="E59" s="5" t="n">
-        <v>80.91</v>
+        <v>81.40000000000001</v>
       </c>
     </row>
     <row r="60">
@@ -7476,10 +7496,10 @@
         <v>64.59</v>
       </c>
       <c r="D60" s="5" t="n">
-        <v>86.77</v>
+        <v>87.29000000000001</v>
       </c>
       <c r="E60" s="5" t="n">
-        <v>103.73</v>
+        <v>104.35</v>
       </c>
     </row>
     <row r="61">
@@ -7495,10 +7515,10 @@
         <v>52.09</v>
       </c>
       <c r="D61" s="5" t="n">
-        <v>67.19</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="E61" s="5" t="n">
-        <v>83.26000000000001</v>
+        <v>83.75</v>
       </c>
     </row>
     <row r="62">
@@ -7514,10 +7534,10 @@
         <v>60.12</v>
       </c>
       <c r="D62" s="5" t="n">
-        <v>68.53</v>
+        <v>68.94</v>
       </c>
       <c r="E62" s="5" t="n">
-        <v>95.72</v>
+        <v>96.29000000000001</v>
       </c>
     </row>
     <row r="63">
@@ -7533,10 +7553,10 @@
         <v>50.92</v>
       </c>
       <c r="D63" s="5" t="n">
-        <v>64.88</v>
+        <v>65.27</v>
       </c>
       <c r="E63" s="5" t="n">
-        <v>80.76000000000001</v>
+        <v>81.23999999999999</v>
       </c>
     </row>
     <row r="64">
@@ -7552,10 +7572,10 @@
         <v>47.77</v>
       </c>
       <c r="D64" s="5" t="n">
-        <v>57.86</v>
+        <v>58.2</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>75.47</v>
+        <v>75.93000000000001</v>
       </c>
     </row>
     <row r="65">
@@ -7571,10 +7591,10 @@
         <v>51.76</v>
       </c>
       <c r="D65" s="5" t="n">
-        <v>62.27</v>
+        <v>62.64</v>
       </c>
       <c r="E65" s="5" t="n">
-        <v>81.87</v>
+        <v>82.36</v>
       </c>
     </row>
     <row r="66">
@@ -7590,10 +7610,10 @@
         <v>45.33</v>
       </c>
       <c r="D66" s="5" t="n">
-        <v>54.72</v>
+        <v>55.05</v>
       </c>
       <c r="E66" s="5" t="n">
-        <v>71.77</v>
+        <v>72.2</v>
       </c>
     </row>
     <row r="67">
@@ -7609,10 +7629,10 @@
         <v>27.82</v>
       </c>
       <c r="D67" s="5" t="n">
-        <v>35.65</v>
+        <v>35.86</v>
       </c>
       <c r="E67" s="5" t="n">
-        <v>44.1</v>
+        <v>44.36</v>
       </c>
     </row>
     <row r="68">
@@ -7628,10 +7648,10 @@
         <v>248.2</v>
       </c>
       <c r="D68" s="5" t="n">
-        <v>198.92</v>
+        <v>200.11</v>
       </c>
       <c r="E68" s="5" t="n">
-        <v>393.28</v>
+        <v>395.64</v>
       </c>
     </row>
     <row r="69">
@@ -7647,10 +7667,10 @@
         <v>44.74</v>
       </c>
       <c r="D69" s="5" t="n">
-        <v>52.9</v>
+        <v>53.22</v>
       </c>
       <c r="E69" s="5" t="n">
-        <v>70.87</v>
+        <v>71.29000000000001</v>
       </c>
     </row>
     <row r="70">
@@ -7666,10 +7686,10 @@
         <v>32.56</v>
       </c>
       <c r="D70" s="5" t="n">
-        <v>40.01</v>
+        <v>40.25</v>
       </c>
       <c r="E70" s="5" t="n">
-        <v>51.55</v>
+        <v>51.86</v>
       </c>
     </row>
     <row r="71">
@@ -7685,10 +7705,10 @@
         <v>49.27</v>
       </c>
       <c r="D71" s="5" t="n">
-        <v>58.96</v>
+        <v>59.32</v>
       </c>
       <c r="E71" s="5" t="n">
-        <v>77.88</v>
+        <v>78.34999999999999</v>
       </c>
     </row>
     <row r="72">
@@ -7704,10 +7724,10 @@
         <v>37.87</v>
       </c>
       <c r="D72" s="5" t="n">
-        <v>49.63</v>
+        <v>49.93</v>
       </c>
       <c r="E72" s="5" t="n">
-        <v>59.76</v>
+        <v>60.12</v>
       </c>
     </row>
     <row r="73">
@@ -7723,10 +7743,10 @@
         <v>37.13</v>
       </c>
       <c r="D73" s="5" t="n">
-        <v>47.38</v>
+        <v>47.66</v>
       </c>
       <c r="E73" s="5" t="n">
-        <v>58.5</v>
+        <v>58.85</v>
       </c>
     </row>
     <row r="74">
@@ -7742,10 +7762,10 @@
         <v>32.55</v>
       </c>
       <c r="D74" s="5" t="n">
-        <v>42.15</v>
+        <v>42.41</v>
       </c>
       <c r="E74" s="5" t="n">
-        <v>51.12</v>
+        <v>51.43</v>
       </c>
     </row>
     <row r="75">
@@ -7761,10 +7781,10 @@
         <v>28.02</v>
       </c>
       <c r="D75" s="5" t="n">
-        <v>35.13</v>
+        <v>35.34</v>
       </c>
       <c r="E75" s="5" t="n">
-        <v>43.87</v>
+        <v>44.13</v>
       </c>
     </row>
     <row r="76">
@@ -7780,10 +7800,10 @@
         <v>27.43</v>
       </c>
       <c r="D76" s="5" t="n">
-        <v>35.8</v>
+        <v>36.02</v>
       </c>
       <c r="E76" s="5" t="n">
-        <v>42.81</v>
+        <v>43.07</v>
       </c>
     </row>
     <row r="77">
@@ -7799,10 +7819,10 @@
         <v>31.55</v>
       </c>
       <c r="D77" s="5" t="n">
-        <v>39.82</v>
+        <v>40.06</v>
       </c>
       <c r="E77" s="5" t="n">
-        <v>49.15</v>
+        <v>49.45</v>
       </c>
     </row>
     <row r="78">
@@ -7818,10 +7838,10 @@
         <v>44.98</v>
       </c>
       <c r="D78" s="5" t="n">
-        <v>50.44</v>
+        <v>50.74</v>
       </c>
       <c r="E78" s="5" t="n">
-        <v>69.95</v>
+        <v>70.37</v>
       </c>
     </row>
     <row r="79">
@@ -7837,10 +7857,10 @@
         <v>29.49</v>
       </c>
       <c r="D79" s="5" t="n">
-        <v>36.5</v>
+        <v>36.72</v>
       </c>
       <c r="E79" s="5" t="n">
-        <v>45.78</v>
+        <v>46.06</v>
       </c>
     </row>
     <row r="80">
@@ -7856,10 +7876,10 @@
         <v>114.74</v>
       </c>
       <c r="D80" s="5" t="n">
-        <v>94.33</v>
+        <v>94.89</v>
       </c>
       <c r="E80" s="5" t="n">
-        <v>177.58</v>
+        <v>178.64</v>
       </c>
     </row>
     <row r="81">
@@ -7875,10 +7895,10 @@
         <v>124.09</v>
       </c>
       <c r="D81" s="5" t="n">
-        <v>104.78</v>
+        <v>105.4</v>
       </c>
       <c r="E81" s="5" t="n">
-        <v>191.45</v>
+        <v>192.6</v>
       </c>
     </row>
     <row r="82">
@@ -7894,10 +7914,10 @@
         <v>27.11</v>
       </c>
       <c r="D82" s="5" t="n">
-        <v>35.16</v>
+        <v>35.37</v>
       </c>
       <c r="E82" s="5" t="n">
-        <v>41.7</v>
+        <v>41.95</v>
       </c>
     </row>
     <row r="83">
@@ -7913,10 +7933,10 @@
         <v>131.25</v>
       </c>
       <c r="D83" s="5" t="n">
-        <v>109.85</v>
+        <v>110.5</v>
       </c>
       <c r="E83" s="5" t="n">
-        <v>201.47</v>
+        <v>202.68</v>
       </c>
     </row>
     <row r="84">
@@ -7932,10 +7952,10 @@
         <v>34.97</v>
       </c>
       <c r="D84" s="5" t="n">
-        <v>46.71</v>
+        <v>46.99</v>
       </c>
       <c r="E84" s="5" t="n">
-        <v>53.57</v>
+        <v>53.89</v>
       </c>
     </row>
     <row r="85">
@@ -7951,10 +7971,10 @@
         <v>36.19</v>
       </c>
       <c r="D85" s="5" t="n">
-        <v>48.01</v>
+        <v>48.29</v>
       </c>
       <c r="E85" s="5" t="n">
-        <v>55.33</v>
+        <v>55.66</v>
       </c>
     </row>
     <row r="86">
@@ -7970,10 +7990,10 @@
         <v>30.36</v>
       </c>
       <c r="D86" s="5" t="n">
-        <v>40.65</v>
+        <v>40.89</v>
       </c>
       <c r="E86" s="5" t="n">
-        <v>46.3</v>
+        <v>46.58</v>
       </c>
     </row>
     <row r="87">
@@ -7989,10 +8009,10 @@
         <v>30.73</v>
       </c>
       <c r="D87" s="5" t="n">
-        <v>41.16</v>
+        <v>41.4</v>
       </c>
       <c r="E87" s="5" t="n">
-        <v>46.76</v>
+        <v>47.04</v>
       </c>
     </row>
     <row r="88">
@@ -8008,10 +8028,10 @@
         <v>24.89</v>
       </c>
       <c r="D88" s="5" t="n">
-        <v>33.58</v>
+        <v>33.78</v>
       </c>
       <c r="E88" s="5" t="n">
-        <v>37.78</v>
+        <v>38.01</v>
       </c>
     </row>
     <row r="89">
@@ -8027,10 +8047,10 @@
         <v>24.65</v>
       </c>
       <c r="D89" s="5" t="n">
-        <v>31.56</v>
+        <v>31.75</v>
       </c>
       <c r="E89" s="5" t="n">
-        <v>37.37</v>
+        <v>37.59</v>
       </c>
     </row>
     <row r="90">
@@ -8046,10 +8066,10 @@
         <v>21.04</v>
       </c>
       <c r="D90" s="5" t="n">
-        <v>27.89</v>
+        <v>28.06</v>
       </c>
       <c r="E90" s="5" t="n">
-        <v>31.85</v>
+        <v>32.05</v>
       </c>
     </row>
     <row r="91">
@@ -8065,10 +8085,10 @@
         <v>18.96</v>
       </c>
       <c r="D91" s="5" t="n">
-        <v>24.98</v>
+        <v>25.13</v>
       </c>
       <c r="E91" s="5" t="n">
-        <v>28.67</v>
+        <v>28.84</v>
       </c>
     </row>
     <row r="92">
@@ -8084,10 +8104,10 @@
         <v>66.16</v>
       </c>
       <c r="D92" s="5" t="n">
-        <v>61.78</v>
+        <v>62.15</v>
       </c>
       <c r="E92" s="5" t="n">
-        <v>99.52</v>
+        <v>100.12</v>
       </c>
     </row>
     <row r="93">
@@ -8103,10 +8123,10 @@
         <v>59.69</v>
       </c>
       <c r="D93" s="5" t="n">
-        <v>60.55</v>
+        <v>60.92</v>
       </c>
       <c r="E93" s="5" t="n">
-        <v>89.33</v>
+        <v>89.87</v>
       </c>
     </row>
     <row r="94">
@@ -8122,10 +8142,10 @@
         <v>28.62</v>
       </c>
       <c r="D94" s="5" t="n">
-        <v>37.17</v>
+        <v>37.39</v>
       </c>
       <c r="E94" s="5" t="n">
-        <v>42.62</v>
+        <v>42.87</v>
       </c>
     </row>
     <row r="95">
@@ -8141,10 +8161,10 @@
         <v>28.26</v>
       </c>
       <c r="D95" s="5" t="n">
-        <v>38</v>
+        <v>38.23</v>
       </c>
       <c r="E95" s="5" t="n">
-        <v>41.95</v>
+        <v>42.2</v>
       </c>
     </row>
     <row r="96">
@@ -8160,10 +8180,10 @@
         <v>40.58</v>
       </c>
       <c r="D96" s="5" t="n">
-        <v>50.84</v>
+        <v>51.14</v>
       </c>
       <c r="E96" s="5" t="n">
-        <v>60.06</v>
+        <v>60.42</v>
       </c>
     </row>
     <row r="97">
@@ -8179,10 +8199,10 @@
         <v>33.89</v>
       </c>
       <c r="D97" s="5" t="n">
-        <v>41.19</v>
+        <v>41.44</v>
       </c>
       <c r="E97" s="5" t="n">
-        <v>50</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="98">
@@ -8198,10 +8218,10 @@
         <v>37.84</v>
       </c>
       <c r="D98" s="5" t="n">
-        <v>43.42</v>
+        <v>43.68</v>
       </c>
       <c r="E98" s="5" t="n">
-        <v>55.72</v>
+        <v>56.05</v>
       </c>
     </row>
     <row r="99">
@@ -8217,10 +8237,10 @@
         <v>35.44</v>
       </c>
       <c r="D99" s="5" t="n">
-        <v>44.01</v>
+        <v>44.28</v>
       </c>
       <c r="E99" s="5" t="n">
-        <v>52.08</v>
+        <v>52.39</v>
       </c>
     </row>
     <row r="100">
@@ -8236,10 +8256,10 @@
         <v>31.61</v>
       </c>
       <c r="D100" s="5" t="n">
-        <v>39.57</v>
+        <v>39.81</v>
       </c>
       <c r="E100" s="5" t="n">
-        <v>46.36</v>
+        <v>46.64</v>
       </c>
     </row>
     <row r="101">
@@ -8255,10 +8275,10 @@
         <v>29</v>
       </c>
       <c r="D101" s="5" t="n">
-        <v>34.63</v>
+        <v>34.84</v>
       </c>
       <c r="E101" s="5" t="n">
-        <v>42.53</v>
+        <v>42.79</v>
       </c>
     </row>
     <row r="102">
@@ -8274,10 +8294,10 @@
         <v>30.77</v>
       </c>
       <c r="D102" s="5" t="n">
-        <v>38.98</v>
+        <v>39.22</v>
       </c>
       <c r="E102" s="5" t="n">
-        <v>45.13</v>
+        <v>45.4</v>
       </c>
     </row>
     <row r="103">
@@ -8293,10 +8313,10 @@
         <v>25.62</v>
       </c>
       <c r="D103" s="5" t="n">
-        <v>32.53</v>
+        <v>32.73</v>
       </c>
       <c r="E103" s="5" t="n">
-        <v>37.58</v>
+        <v>37.8</v>
       </c>
     </row>
     <row r="104">
@@ -8312,10 +8332,10 @@
         <v>29.13</v>
       </c>
       <c r="D104" s="5" t="n">
-        <v>35.24</v>
+        <v>35.45</v>
       </c>
       <c r="E104" s="5" t="n">
-        <v>42.72</v>
+        <v>42.97</v>
       </c>
     </row>
     <row r="105">
@@ -8331,10 +8351,10 @@
         <v>30.01</v>
       </c>
       <c r="D105" s="5" t="n">
-        <v>37.9</v>
+        <v>38.13</v>
       </c>
       <c r="E105" s="5" t="n">
-        <v>44</v>
+        <v>44.26</v>
       </c>
     </row>
     <row r="106">
@@ -8350,10 +8370,10 @@
         <v>27.89</v>
       </c>
       <c r="D106" s="5" t="n">
-        <v>34.74</v>
+        <v>34.95</v>
       </c>
       <c r="E106" s="5" t="n">
-        <v>40.88</v>
+        <v>41.13</v>
       </c>
     </row>
     <row r="107">
@@ -8369,10 +8389,10 @@
         <v>36.3</v>
       </c>
       <c r="D107" s="5" t="n">
-        <v>46.84</v>
+        <v>47.12</v>
       </c>
       <c r="E107" s="5" t="n">
-        <v>53.12</v>
+        <v>53.44</v>
       </c>
     </row>
     <row r="108">
@@ -8388,10 +8408,10 @@
         <v>30.09</v>
       </c>
       <c r="D108" s="5" t="n">
-        <v>38.83</v>
+        <v>39.06</v>
       </c>
       <c r="E108" s="5" t="n">
-        <v>43.96</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="109">
@@ -8407,10 +8427,10 @@
         <v>42.66</v>
       </c>
       <c r="D109" s="5" t="n">
-        <v>53.59</v>
+        <v>53.91</v>
       </c>
       <c r="E109" s="5" t="n">
-        <v>62.21</v>
+        <v>62.58</v>
       </c>
     </row>
     <row r="110">
@@ -8426,10 +8446,10 @@
         <v>90.05</v>
       </c>
       <c r="D110" s="5" t="n">
-        <v>106.64</v>
+        <v>107.28</v>
       </c>
       <c r="E110" s="5" t="n">
-        <v>130.72</v>
+        <v>131.51</v>
       </c>
     </row>
     <row r="111">
@@ -8445,10 +8465,10 @@
         <v>58.79</v>
       </c>
       <c r="D111" s="5" t="n">
-        <v>80.58</v>
+        <v>81.06</v>
       </c>
       <c r="E111" s="5" t="n">
-        <v>84.95999999999999</v>
+        <v>85.47</v>
       </c>
     </row>
     <row r="112">
@@ -8464,10 +8484,10 @@
         <v>60.96</v>
       </c>
       <c r="D112" s="5" t="n">
-        <v>76.94</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="E112" s="5" t="n">
-        <v>87.7</v>
+        <v>88.23</v>
       </c>
     </row>
     <row r="113">
@@ -8483,10 +8503,10 @@
         <v>55</v>
       </c>
       <c r="D113" s="5" t="n">
-        <v>73.7</v>
+        <v>74.14</v>
       </c>
       <c r="E113" s="5" t="n">
-        <v>79.06</v>
+        <v>79.53</v>
       </c>
     </row>
     <row r="114">
@@ -8502,10 +8522,10 @@
         <v>108.73</v>
       </c>
       <c r="D114" s="5" t="n">
-        <v>110.85</v>
+        <v>111.51</v>
       </c>
       <c r="E114" s="5" t="n">
-        <v>156.16</v>
+        <v>157.1</v>
       </c>
     </row>
     <row r="115">
@@ -8521,10 +8541,10 @@
         <v>58.92</v>
       </c>
       <c r="D115" s="5" t="n">
-        <v>74.88</v>
+        <v>75.33</v>
       </c>
       <c r="E115" s="5" t="n">
-        <v>84.55</v>
+        <v>85.06</v>
       </c>
     </row>
     <row r="116">
@@ -8540,10 +8560,10 @@
         <v>65.31</v>
       </c>
       <c r="D116" s="5" t="n">
-        <v>77.79000000000001</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="E116" s="5" t="n">
-        <v>93.62</v>
+        <v>94.18000000000001</v>
       </c>
     </row>
     <row r="117">
@@ -8559,10 +8579,10 @@
         <v>59.78</v>
       </c>
       <c r="D117" s="5" t="n">
-        <v>76.73</v>
+        <v>77.19</v>
       </c>
       <c r="E117" s="5" t="n">
-        <v>85.59</v>
+        <v>86.11</v>
       </c>
     </row>
     <row r="118">
@@ -8578,10 +8598,10 @@
         <v>60.03</v>
       </c>
       <c r="D118" s="5" t="n">
-        <v>74.81</v>
+        <v>75.26000000000001</v>
       </c>
       <c r="E118" s="5" t="n">
-        <v>85.84999999999999</v>
+        <v>86.37</v>
       </c>
     </row>
     <row r="119">
@@ -8597,10 +8617,10 @@
         <v>53.46</v>
       </c>
       <c r="D119" s="5" t="n">
-        <v>71.45</v>
+        <v>71.88</v>
       </c>
       <c r="E119" s="5" t="n">
-        <v>76.36</v>
+        <v>76.81999999999999</v>
       </c>
     </row>
     <row r="120">
@@ -8616,10 +8636,10 @@
         <v>61.01</v>
       </c>
       <c r="D120" s="5" t="n">
-        <v>78.25</v>
+        <v>78.72</v>
       </c>
       <c r="E120" s="5" t="n">
-        <v>87.03</v>
+        <v>87.56</v>
       </c>
     </row>
     <row r="121">
@@ -8635,10 +8655,10 @@
         <v>70.51000000000001</v>
       </c>
       <c r="D121" s="5" t="n">
-        <v>86.77</v>
+        <v>87.29000000000001</v>
       </c>
       <c r="E121" s="5" t="n">
-        <v>100.46</v>
+        <v>101.06</v>
       </c>
     </row>
     <row r="122">
@@ -8654,10 +8674,10 @@
         <v>62.4</v>
       </c>
       <c r="D122" s="5" t="n">
-        <v>82.8</v>
+        <v>83.3</v>
       </c>
       <c r="E122" s="5" t="n">
-        <v>88.55</v>
+        <v>89.08</v>
       </c>
     </row>
     <row r="123">
@@ -8673,10 +8693,10 @@
         <v>57.79</v>
       </c>
       <c r="D123" s="5" t="n">
-        <v>76.48999999999999</v>
+        <v>76.95</v>
       </c>
       <c r="E123" s="5" t="n">
-        <v>81.67</v>
+        <v>82.16</v>
       </c>
     </row>
     <row r="124">
@@ -8692,10 +8712,10 @@
         <v>52.11</v>
       </c>
       <c r="D124" s="5" t="n">
-        <v>69.31999999999999</v>
+        <v>69.73999999999999</v>
       </c>
       <c r="E124" s="5" t="n">
-        <v>73.34999999999999</v>
+        <v>73.79000000000001</v>
       </c>
     </row>
     <row r="125">
@@ -8711,10 +8731,10 @@
         <v>51.91</v>
       </c>
       <c r="D125" s="5" t="n">
-        <v>69.47</v>
+        <v>69.88</v>
       </c>
       <c r="E125" s="5" t="n">
-        <v>72.89</v>
+        <v>73.33</v>
       </c>
     </row>
     <row r="126">
@@ -8730,10 +8750,10 @@
         <v>49.47</v>
       </c>
       <c r="D126" s="5" t="n">
-        <v>65.51000000000001</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="E126" s="5" t="n">
-        <v>69.3</v>
+        <v>69.72</v>
       </c>
     </row>
     <row r="127">
@@ -8749,10 +8769,10 @@
         <v>57.51</v>
       </c>
       <c r="D127" s="5" t="n">
-        <v>70.34</v>
+        <v>70.76000000000001</v>
       </c>
       <c r="E127" s="5" t="n">
-        <v>80.37</v>
+        <v>80.86</v>
       </c>
     </row>
     <row r="128">
@@ -8768,10 +8788,10 @@
         <v>105.62</v>
       </c>
       <c r="D128" s="5" t="n">
-        <v>101.03</v>
+        <v>101.63</v>
       </c>
       <c r="E128" s="5" t="n">
-        <v>147.32</v>
+        <v>148.2</v>
       </c>
     </row>
     <row r="129">
@@ -8787,10 +8807,10 @@
         <v>51.64</v>
       </c>
       <c r="D129" s="5" t="n">
-        <v>68.56</v>
+        <v>68.97</v>
       </c>
       <c r="E129" s="5" t="n">
-        <v>71.89</v>
+        <v>72.31999999999999</v>
       </c>
     </row>
     <row r="130">
@@ -8806,10 +8826,10 @@
         <v>50.99</v>
       </c>
       <c r="D130" s="5" t="n">
-        <v>63.85</v>
+        <v>64.23999999999999</v>
       </c>
       <c r="E130" s="5" t="n">
-        <v>70.84</v>
+        <v>71.27</v>
       </c>
     </row>
     <row r="131">
@@ -8825,10 +8845,10 @@
         <v>46.48</v>
       </c>
       <c r="D131" s="5" t="n">
-        <v>60.74</v>
+        <v>61.1</v>
       </c>
       <c r="E131" s="5" t="n">
-        <v>64.47</v>
+        <v>64.84999999999999</v>
       </c>
     </row>
     <row r="132">
@@ -8844,10 +8864,10 @@
         <v>53.42</v>
       </c>
       <c r="D132" s="5" t="n">
-        <v>66.73999999999999</v>
+        <v>67.14</v>
       </c>
       <c r="E132" s="5" t="n">
-        <v>73.97</v>
+        <v>74.41</v>
       </c>
     </row>
     <row r="133">
@@ -8863,10 +8883,10 @@
         <v>53.9</v>
       </c>
       <c r="D133" s="5" t="n">
-        <v>67.97</v>
+        <v>68.38</v>
       </c>
       <c r="E133" s="5" t="n">
-        <v>74.51000000000001</v>
+        <v>74.95999999999999</v>
       </c>
     </row>
     <row r="134">
@@ -8882,10 +8902,10 @@
         <v>43.69</v>
       </c>
       <c r="D134" s="5" t="n">
-        <v>53.27</v>
+        <v>53.59</v>
       </c>
       <c r="E134" s="5" t="n">
-        <v>60.31</v>
+        <v>60.67</v>
       </c>
     </row>
     <row r="135">
@@ -8901,10 +8921,10 @@
         <v>40.67</v>
       </c>
       <c r="D135" s="5" t="n">
-        <v>47.57</v>
+        <v>47.86</v>
       </c>
       <c r="E135" s="5" t="n">
-        <v>56.06</v>
+        <v>56.4</v>
       </c>
     </row>
     <row r="136">
@@ -8920,10 +8940,10 @@
         <v>42.07</v>
       </c>
       <c r="D136" s="5" t="n">
-        <v>49.91</v>
+        <v>50.21</v>
       </c>
       <c r="E136" s="5" t="n">
-        <v>57.91</v>
+        <v>58.26</v>
       </c>
     </row>
     <row r="137">
@@ -8939,10 +8959,10 @@
         <v>30.63</v>
       </c>
       <c r="D137" s="5" t="n">
-        <v>36.58</v>
+        <v>36.8</v>
       </c>
       <c r="E137" s="5" t="n">
-        <v>42.14</v>
+        <v>42.39</v>
       </c>
     </row>
     <row r="138">
@@ -8958,10 +8978,10 @@
         <v>34.46</v>
       </c>
       <c r="D138" s="5" t="n">
-        <v>39.26</v>
+        <v>39.5</v>
       </c>
       <c r="E138" s="5" t="n">
-        <v>47.38</v>
+        <v>47.66</v>
       </c>
     </row>
     <row r="139">
@@ -8977,10 +8997,10 @@
         <v>31.31</v>
       </c>
       <c r="D139" s="5" t="n">
-        <v>36.46</v>
+        <v>36.68</v>
       </c>
       <c r="E139" s="5" t="n">
-        <v>43.02</v>
+        <v>43.28</v>
       </c>
     </row>
     <row r="140">
@@ -8996,10 +9016,10 @@
         <v>33.61</v>
       </c>
       <c r="D140" s="5" t="n">
-        <v>35.84</v>
+        <v>36.05</v>
       </c>
       <c r="E140" s="5" t="n">
-        <v>46.15</v>
+        <v>46.43</v>
       </c>
     </row>
     <row r="141">
@@ -9015,10 +9035,10 @@
         <v>35.21</v>
       </c>
       <c r="D141" s="5" t="n">
-        <v>38.46</v>
+        <v>38.69</v>
       </c>
       <c r="E141" s="5" t="n">
-        <v>48.32</v>
+        <v>48.61</v>
       </c>
     </row>
     <row r="142">
@@ -9034,10 +9054,10 @@
         <v>31.79</v>
       </c>
       <c r="D142" s="5" t="n">
-        <v>35.39</v>
+        <v>35.61</v>
       </c>
       <c r="E142" s="5" t="n">
-        <v>43.6</v>
+        <v>43.86</v>
       </c>
     </row>
     <row r="143">
@@ -9053,10 +9073,10 @@
         <v>35.26</v>
       </c>
       <c r="D143" s="5" t="n">
-        <v>39.55</v>
+        <v>39.79</v>
       </c>
       <c r="E143" s="5" t="n">
-        <v>48.24</v>
+        <v>48.53</v>
       </c>
     </row>
     <row r="144">
@@ -9072,10 +9092,10 @@
         <v>38.41</v>
       </c>
       <c r="D144" s="5" t="n">
-        <v>40.74</v>
+        <v>40.99</v>
       </c>
       <c r="E144" s="5" t="n">
-        <v>52.42</v>
+        <v>52.74</v>
       </c>
     </row>
     <row r="145">
@@ -9091,10 +9111,10 @@
         <v>41.52</v>
       </c>
       <c r="D145" s="5" t="n">
-        <v>46.85</v>
+        <v>47.13</v>
       </c>
       <c r="E145" s="5" t="n">
-        <v>56.53</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="146">
@@ -9110,10 +9130,10 @@
         <v>42.82</v>
       </c>
       <c r="D146" s="5" t="n">
-        <v>47.26</v>
+        <v>47.54</v>
       </c>
       <c r="E146" s="5" t="n">
-        <v>58.23</v>
+        <v>58.58</v>
       </c>
     </row>
     <row r="147">
@@ -9129,10 +9149,10 @@
         <v>42.1</v>
       </c>
       <c r="D147" s="5" t="n">
-        <v>47.59</v>
+        <v>47.87</v>
       </c>
       <c r="E147" s="5" t="n">
-        <v>57.18</v>
+        <v>57.52</v>
       </c>
     </row>
     <row r="148">
@@ -9148,10 +9168,10 @@
         <v>50.84</v>
       </c>
       <c r="D148" s="5" t="n">
-        <v>60.43</v>
+        <v>60.79</v>
       </c>
       <c r="E148" s="5" t="n">
-        <v>68.95999999999999</v>
+        <v>69.37</v>
       </c>
     </row>
     <row r="149">
@@ -9167,10 +9187,10 @@
         <v>45.47</v>
       </c>
       <c r="D149" s="5" t="n">
-        <v>48.26</v>
+        <v>48.55</v>
       </c>
       <c r="E149" s="5" t="n">
-        <v>61.59</v>
+        <v>61.96</v>
       </c>
     </row>
     <row r="150">
@@ -9186,10 +9206,10 @@
         <v>45.23</v>
       </c>
       <c r="D150" s="5" t="n">
-        <v>47.24</v>
+        <v>47.53</v>
       </c>
       <c r="E150" s="5" t="n">
-        <v>61.19</v>
+        <v>61.56</v>
       </c>
     </row>
     <row r="151">
@@ -9205,10 +9225,10 @@
         <v>62.67</v>
       </c>
       <c r="D151" s="5" t="n">
-        <v>64.87</v>
+        <v>65.26000000000001</v>
       </c>
       <c r="E151" s="5" t="n">
-        <v>84.68000000000001</v>
+        <v>85.18000000000001</v>
       </c>
     </row>
     <row r="152">
@@ -9224,10 +9244,10 @@
         <v>72.90000000000001</v>
       </c>
       <c r="D152" s="5" t="n">
-        <v>63.48</v>
+        <v>63.86</v>
       </c>
       <c r="E152" s="5" t="n">
-        <v>98.56</v>
+        <v>99.15000000000001</v>
       </c>
     </row>
     <row r="153">
@@ -9243,10 +9263,10 @@
         <v>44.52</v>
       </c>
       <c r="D153" s="5" t="n">
-        <v>47.92</v>
+        <v>48.21</v>
       </c>
       <c r="E153" s="5" t="n">
-        <v>60.23</v>
+        <v>60.59</v>
       </c>
     </row>
     <row r="154">
@@ -9262,10 +9282,10 @@
         <v>59.65</v>
       </c>
       <c r="D154" s="5" t="n">
-        <v>62.13</v>
+        <v>62.5</v>
       </c>
       <c r="E154" s="5" t="n">
-        <v>80.76000000000001</v>
+        <v>81.23999999999999</v>
       </c>
     </row>
     <row r="155">
@@ -9281,10 +9301,10 @@
         <v>61.49</v>
       </c>
       <c r="D155" s="5" t="n">
-        <v>62.02</v>
+        <v>62.4</v>
       </c>
       <c r="E155" s="5" t="n">
-        <v>83.13</v>
+        <v>83.62</v>
       </c>
     </row>
     <row r="156">
@@ -9300,10 +9320,10 @@
         <v>76.45999999999999</v>
       </c>
       <c r="D156" s="5" t="n">
-        <v>73.22</v>
+        <v>73.66</v>
       </c>
       <c r="E156" s="5" t="n">
-        <v>103.21</v>
+        <v>103.83</v>
       </c>
     </row>
     <row r="157">
@@ -9319,10 +9339,10 @@
         <v>118.54</v>
       </c>
       <c r="D157" s="5" t="n">
-        <v>125.05</v>
+        <v>125.8</v>
       </c>
       <c r="E157" s="5" t="n">
-        <v>159.78</v>
+        <v>160.74</v>
       </c>
     </row>
     <row r="158">
@@ -9338,10 +9358,10 @@
         <v>86.77</v>
       </c>
       <c r="D158" s="5" t="n">
-        <v>86.93000000000001</v>
+        <v>87.45</v>
       </c>
       <c r="E158" s="5" t="n">
-        <v>116.69</v>
+        <v>117.39</v>
       </c>
     </row>
     <row r="159">
@@ -9357,10 +9377,10 @@
         <v>55.76</v>
       </c>
       <c r="D159" s="5" t="n">
-        <v>58.01</v>
+        <v>58.36</v>
       </c>
       <c r="E159" s="5" t="n">
-        <v>74.81</v>
+        <v>75.26000000000001</v>
       </c>
     </row>
     <row r="160">
@@ -9376,10 +9396,10 @@
         <v>48.5</v>
       </c>
       <c r="D160" s="5" t="n">
-        <v>54.91</v>
+        <v>55.24</v>
       </c>
       <c r="E160" s="5" t="n">
-        <v>64.92</v>
+        <v>65.31</v>
       </c>
     </row>
     <row r="161">
@@ -9395,10 +9415,10 @@
         <v>41.02</v>
       </c>
       <c r="D161" s="5" t="n">
-        <v>44.33</v>
+        <v>44.6</v>
       </c>
       <c r="E161" s="5" t="n">
-        <v>54.81</v>
+        <v>55.14</v>
       </c>
     </row>
     <row r="162">
@@ -9414,10 +9434,10 @@
         <v>46.93</v>
       </c>
       <c r="D162" s="5" t="n">
-        <v>48.11</v>
+        <v>48.4</v>
       </c>
       <c r="E162" s="5" t="n">
-        <v>62.6</v>
+        <v>62.97</v>
       </c>
     </row>
     <row r="163">
@@ -9433,10 +9453,10 @@
         <v>37.59</v>
       </c>
       <c r="D163" s="5" t="n">
-        <v>39.81</v>
+        <v>40.05</v>
       </c>
       <c r="E163" s="5" t="n">
-        <v>50.05</v>
+        <v>50.35</v>
       </c>
     </row>
     <row r="164">
@@ -9452,10 +9472,10 @@
         <v>81.03</v>
       </c>
       <c r="D164" s="5" t="n">
-        <v>82.48</v>
+        <v>82.98</v>
       </c>
       <c r="E164" s="5" t="n">
-        <v>107.73</v>
+        <v>108.37</v>
       </c>
     </row>
     <row r="165">
@@ -9471,10 +9491,10 @@
         <v>114.18</v>
       </c>
       <c r="D165" s="5" t="n">
-        <v>114.23</v>
+        <v>114.91</v>
       </c>
       <c r="E165" s="5" t="n">
-        <v>151.57</v>
+        <v>152.48</v>
       </c>
     </row>
     <row r="166">
@@ -9490,10 +9510,10 @@
         <v>112.64</v>
       </c>
       <c r="D166" s="5" t="n">
-        <v>120.12</v>
+        <v>120.84</v>
       </c>
       <c r="E166" s="5" t="n">
-        <v>149.3</v>
+        <v>150.19</v>
       </c>
     </row>
     <row r="167">
@@ -9509,10 +9529,10 @@
         <v>123.35</v>
       </c>
       <c r="D167" s="5" t="n">
-        <v>143.32</v>
+        <v>144.18</v>
       </c>
       <c r="E167" s="5" t="n">
-        <v>163.38</v>
+        <v>164.36</v>
       </c>
     </row>
     <row r="168">
@@ -9528,10 +9548,10 @@
         <v>123.09</v>
       </c>
       <c r="D168" s="5" t="n">
-        <v>142.89</v>
+        <v>143.75</v>
       </c>
       <c r="E168" s="5" t="n">
-        <v>162.93</v>
+        <v>163.91</v>
       </c>
     </row>
     <row r="169">
@@ -9547,10 +9567,10 @@
         <v>105</v>
       </c>
       <c r="D169" s="5" t="n">
-        <v>130.3</v>
+        <v>131.08</v>
       </c>
       <c r="E169" s="5" t="n">
-        <v>138.9</v>
+        <v>139.73</v>
       </c>
     </row>
     <row r="170">
@@ -9566,10 +9586,10 @@
         <v>131.48</v>
       </c>
       <c r="D170" s="5" t="n">
-        <v>154.96</v>
+        <v>155.89</v>
       </c>
       <c r="E170" s="5" t="n">
-        <v>173.57</v>
+        <v>174.61</v>
       </c>
     </row>
     <row r="171">
@@ -9585,10 +9605,10 @@
         <v>119.74</v>
       </c>
       <c r="D171" s="5" t="n">
-        <v>135.13</v>
+        <v>135.94</v>
       </c>
       <c r="E171" s="5" t="n">
-        <v>157.75</v>
+        <v>158.7</v>
       </c>
     </row>
     <row r="172">
@@ -9604,10 +9624,10 @@
         <v>89.62</v>
       </c>
       <c r="D172" s="5" t="n">
-        <v>104.43</v>
+        <v>105.06</v>
       </c>
       <c r="E172" s="5" t="n">
-        <v>117.83</v>
+        <v>118.54</v>
       </c>
     </row>
     <row r="173">
@@ -9623,10 +9643,10 @@
         <v>82.48</v>
       </c>
       <c r="D173" s="5" t="n">
-        <v>96.17</v>
+        <v>96.75</v>
       </c>
       <c r="E173" s="5" t="n">
-        <v>108.2</v>
+        <v>108.85</v>
       </c>
     </row>
     <row r="174">
@@ -9642,10 +9662,10 @@
         <v>112.43</v>
       </c>
       <c r="D174" s="5" t="n">
-        <v>125.06</v>
+        <v>125.81</v>
       </c>
       <c r="E174" s="5" t="n">
-        <v>147.16</v>
+        <v>148.05</v>
       </c>
     </row>
     <row r="175">
@@ -9661,10 +9681,10 @@
         <v>97.75</v>
       </c>
       <c r="D175" s="5" t="n">
-        <v>110.82</v>
+        <v>111.48</v>
       </c>
       <c r="E175" s="5" t="n">
-        <v>127.66</v>
+        <v>128.43</v>
       </c>
     </row>
     <row r="176">
@@ -9680,10 +9700,10 @@
         <v>183</v>
       </c>
       <c r="D176" s="5" t="n">
-        <v>174.07</v>
+        <v>175.12</v>
       </c>
       <c r="E176" s="5" t="n">
-        <v>238.65</v>
+        <v>240.09</v>
       </c>
     </row>
     <row r="177">
@@ -9699,10 +9719,10 @@
         <v>124.33</v>
       </c>
       <c r="D177" s="5" t="n">
-        <v>126.88</v>
+        <v>127.64</v>
       </c>
       <c r="E177" s="5" t="n">
-        <v>161.91</v>
+        <v>162.88</v>
       </c>
     </row>
     <row r="178">
@@ -9718,10 +9738,10 @@
         <v>82.25</v>
       </c>
       <c r="D178" s="5" t="n">
-        <v>98.84</v>
+        <v>99.43000000000001</v>
       </c>
       <c r="E178" s="5" t="n">
-        <v>106.95</v>
+        <v>107.59</v>
       </c>
     </row>
     <row r="179">
@@ -9737,10 +9757,10 @@
         <v>87.09</v>
       </c>
       <c r="D179" s="5" t="n">
-        <v>96.16</v>
+        <v>96.73999999999999</v>
       </c>
       <c r="E179" s="5" t="n">
-        <v>113.11</v>
+        <v>113.79</v>
       </c>
     </row>
     <row r="180">
@@ -9756,10 +9776,10 @@
         <v>95.98</v>
       </c>
       <c r="D180" s="5" t="n">
-        <v>103.51</v>
+        <v>104.13</v>
       </c>
       <c r="E180" s="5" t="n">
-        <v>124.51</v>
+        <v>125.26</v>
       </c>
     </row>
     <row r="181">
@@ -9775,10 +9795,10 @@
         <v>112.11</v>
       </c>
       <c r="D181" s="5" t="n">
-        <v>121.43</v>
+        <v>122.16</v>
       </c>
       <c r="E181" s="5" t="n">
-        <v>145.26</v>
+        <v>146.13</v>
       </c>
     </row>
     <row r="182">
@@ -9794,10 +9814,10 @@
         <v>88.33</v>
       </c>
       <c r="D182" s="5" t="n">
-        <v>90.7</v>
+        <v>91.23999999999999</v>
       </c>
       <c r="E182" s="5" t="n">
-        <v>114.28</v>
+        <v>114.97</v>
       </c>
     </row>
     <row r="183">
@@ -9813,10 +9833,10 @@
         <v>102.2</v>
       </c>
       <c r="D183" s="5" t="n">
-        <v>102.29</v>
+        <v>102.9</v>
       </c>
       <c r="E183" s="5" t="n">
-        <v>132.04</v>
+        <v>132.83</v>
       </c>
     </row>
     <row r="184">
@@ -9832,10 +9852,10 @@
         <v>108.02</v>
       </c>
       <c r="D184" s="5" t="n">
-        <v>119.79</v>
+        <v>120.51</v>
       </c>
       <c r="E184" s="5" t="n">
-        <v>139.36</v>
+        <v>140.19</v>
       </c>
     </row>
     <row r="185">
@@ -9851,10 +9871,10 @@
         <v>109.7</v>
       </c>
       <c r="D185" s="5" t="n">
-        <v>128.57</v>
+        <v>129.34</v>
       </c>
       <c r="E185" s="5" t="n">
-        <v>141.28</v>
+        <v>142.13</v>
       </c>
     </row>
     <row r="186">
@@ -9870,10 +9890,10 @@
         <v>105.48</v>
       </c>
       <c r="D186" s="5" t="n">
-        <v>125.79</v>
+        <v>126.54</v>
       </c>
       <c r="E186" s="5" t="n">
-        <v>135.61</v>
+        <v>136.42</v>
       </c>
     </row>
     <row r="187">
@@ -9889,10 +9909,10 @@
         <v>113.92</v>
       </c>
       <c r="D187" s="5" t="n">
-        <v>117.81</v>
+        <v>118.51</v>
       </c>
       <c r="E187" s="5" t="n">
-        <v>146.21</v>
+        <v>147.09</v>
       </c>
     </row>
     <row r="188">
@@ -9908,10 +9928,10 @@
         <v>423.33</v>
       </c>
       <c r="D188" s="5" t="n">
-        <v>321.3</v>
+        <v>323.22</v>
       </c>
       <c r="E188" s="5" t="n">
-        <v>543.34</v>
+        <v>546.6</v>
       </c>
     </row>
     <row r="189">
@@ -9927,10 +9947,10 @@
         <v>120.86</v>
       </c>
       <c r="D189" s="5" t="n">
-        <v>142.68</v>
+        <v>143.54</v>
       </c>
       <c r="E189" s="5" t="n">
-        <v>155.13</v>
+        <v>156.06</v>
       </c>
     </row>
     <row r="190">
@@ -9946,10 +9966,10 @@
         <v>177.81</v>
       </c>
       <c r="D190" s="5" t="n">
-        <v>168.29</v>
+        <v>169.3</v>
       </c>
       <c r="E190" s="5" t="n">
-        <v>228.24</v>
+        <v>229.61</v>
       </c>
     </row>
     <row r="191">
@@ -9965,10 +9985,10 @@
         <v>106.79</v>
       </c>
       <c r="D191" s="5" t="n">
-        <v>126.11</v>
+        <v>126.87</v>
       </c>
       <c r="E191" s="5" t="n">
-        <v>136.81</v>
+        <v>137.63</v>
       </c>
     </row>
     <row r="192">
@@ -9984,10 +10004,10 @@
         <v>104.25</v>
       </c>
       <c r="D192" s="5" t="n">
-        <v>117.5</v>
+        <v>118.2</v>
       </c>
       <c r="E192" s="5" t="n">
-        <v>133.29</v>
+        <v>134.09</v>
       </c>
     </row>
     <row r="193">
@@ -10003,10 +10023,10 @@
         <v>122.01</v>
       </c>
       <c r="D193" s="5" t="n">
-        <v>129.91</v>
+        <v>130.69</v>
       </c>
       <c r="E193" s="5" t="n">
-        <v>155.69</v>
+        <v>156.62</v>
       </c>
     </row>
     <row r="194">
@@ -10022,10 +10042,10 @@
         <v>105.02</v>
       </c>
       <c r="D194" s="5" t="n">
-        <v>109.43</v>
+        <v>110.09</v>
       </c>
       <c r="E194" s="5" t="n">
-        <v>133.76</v>
+        <v>134.56</v>
       </c>
     </row>
     <row r="195">
@@ -10041,10 +10061,10 @@
         <v>130.29</v>
       </c>
       <c r="D195" s="5" t="n">
-        <v>133.42</v>
+        <v>134.22</v>
       </c>
       <c r="E195" s="5" t="n">
-        <v>165.63</v>
+        <v>166.62</v>
       </c>
     </row>
     <row r="196">
@@ -10060,10 +10080,10 @@
         <v>121.93</v>
       </c>
       <c r="D196" s="5" t="n">
-        <v>132.93</v>
+        <v>133.72</v>
       </c>
       <c r="E196" s="5" t="n">
-        <v>154.71</v>
+        <v>155.64</v>
       </c>
     </row>
     <row r="197">
@@ -10079,10 +10099,10 @@
         <v>113.03</v>
       </c>
       <c r="D197" s="5" t="n">
-        <v>127.48</v>
+        <v>128.25</v>
       </c>
       <c r="E197" s="5" t="n">
-        <v>143.09</v>
+        <v>143.95</v>
       </c>
     </row>
     <row r="198">
@@ -10098,10 +10118,10 @@
         <v>69.79000000000001</v>
       </c>
       <c r="D198" s="5" t="n">
-        <v>85.87</v>
+        <v>86.38</v>
       </c>
       <c r="E198" s="5" t="n">
-        <v>88.15000000000001</v>
+        <v>88.68000000000001</v>
       </c>
     </row>
     <row r="199">
@@ -10117,10 +10137,10 @@
         <v>77.45999999999999</v>
       </c>
       <c r="D199" s="5" t="n">
-        <v>77.37</v>
+        <v>77.83</v>
       </c>
       <c r="E199" s="5" t="n">
-        <v>97.62</v>
+        <v>98.2</v>
       </c>
     </row>
     <row r="200">
@@ -10136,10 +10156,10 @@
         <v>255.88</v>
       </c>
       <c r="D200" s="5" t="n">
-        <v>179.93</v>
+        <v>181.01</v>
       </c>
       <c r="E200" s="5" t="n">
-        <v>322.07</v>
+        <v>324</v>
       </c>
     </row>
     <row r="201">
@@ -10155,10 +10175,10 @@
         <v>55.83</v>
       </c>
       <c r="D201" s="5" t="n">
-        <v>60.73</v>
+        <v>61.1</v>
       </c>
       <c r="E201" s="5" t="n">
-        <v>70.18000000000001</v>
+        <v>70.61</v>
       </c>
     </row>
     <row r="202">
@@ -10174,10 +10194,10 @@
         <v>50.47</v>
       </c>
       <c r="D202" s="5" t="n">
-        <v>54.37</v>
+        <v>54.69</v>
       </c>
       <c r="E202" s="5" t="n">
-        <v>63.37</v>
+        <v>63.75</v>
       </c>
     </row>
     <row r="203">
@@ -10193,10 +10213,10 @@
         <v>41.9</v>
       </c>
       <c r="D203" s="5" t="n">
-        <v>44.01</v>
+        <v>44.28</v>
       </c>
       <c r="E203" s="5" t="n">
-        <v>52.95</v>
+        <v>53.27</v>
       </c>
     </row>
     <row r="204">
@@ -10212,10 +10232,10 @@
         <v>47.04</v>
       </c>
       <c r="D204" s="5" t="n">
-        <v>48.7</v>
+        <v>48.99</v>
       </c>
       <c r="E204" s="5" t="n">
-        <v>59.83</v>
+        <v>60.19</v>
       </c>
     </row>
     <row r="205">
@@ -10231,10 +10251,10 @@
         <v>62.91</v>
       </c>
       <c r="D205" s="5" t="n">
-        <v>62.3</v>
+        <v>62.67</v>
       </c>
       <c r="E205" s="5" t="n">
-        <v>80.54000000000001</v>
+        <v>81.02</v>
       </c>
     </row>
     <row r="206">
@@ -10250,10 +10270,10 @@
         <v>75.01000000000001</v>
       </c>
       <c r="D206" s="5" t="n">
-        <v>81</v>
+        <v>81.48999999999999</v>
       </c>
       <c r="E206" s="5" t="n">
-        <v>95.54000000000001</v>
+        <v>96.11</v>
       </c>
     </row>
     <row r="207">
@@ -10269,10 +10289,10 @@
         <v>66.40000000000001</v>
       </c>
       <c r="D207" s="5" t="n">
-        <v>68.04000000000001</v>
+        <v>68.45</v>
       </c>
       <c r="E207" s="5" t="n">
-        <v>84.14</v>
+        <v>84.64</v>
       </c>
     </row>
     <row r="208">
@@ -10288,10 +10308,10 @@
         <v>39.08</v>
       </c>
       <c r="D208" s="5" t="n">
-        <v>43.68</v>
+        <v>43.94</v>
       </c>
       <c r="E208" s="5" t="n">
-        <v>49.27</v>
+        <v>49.56</v>
       </c>
     </row>
     <row r="209">
@@ -10307,10 +10327,10 @@
         <v>55.4</v>
       </c>
       <c r="D209" s="5" t="n">
-        <v>56.3</v>
+        <v>56.63</v>
       </c>
       <c r="E209" s="5" t="n">
-        <v>69.63</v>
+        <v>70.05</v>
       </c>
     </row>
     <row r="210">
@@ -10326,10 +10346,10 @@
         <v>49.88</v>
       </c>
       <c r="D210" s="5" t="n">
-        <v>55.23</v>
+        <v>55.56</v>
       </c>
       <c r="E210" s="5" t="n">
-        <v>62.51</v>
+        <v>62.88</v>
       </c>
     </row>
     <row r="211">
@@ -10345,10 +10365,10 @@
         <v>23.5</v>
       </c>
       <c r="D211" s="5" t="n">
-        <v>29.72</v>
+        <v>29.9</v>
       </c>
       <c r="E211" s="5" t="n">
-        <v>29.36</v>
+        <v>29.54</v>
       </c>
     </row>
     <row r="212">
@@ -10364,10 +10384,10 @@
         <v>20.68</v>
       </c>
       <c r="D212" s="5" t="n">
-        <v>28.46</v>
+        <v>28.63</v>
       </c>
       <c r="E212" s="5" t="n">
-        <v>25.79</v>
+        <v>25.94</v>
       </c>
     </row>
     <row r="213">
@@ -10383,10 +10403,10 @@
         <v>24.89</v>
       </c>
       <c r="D213" s="5" t="n">
-        <v>27.19</v>
+        <v>27.36</v>
       </c>
       <c r="E213" s="5" t="n">
-        <v>30.98</v>
+        <v>31.16</v>
       </c>
     </row>
     <row r="214">
@@ -10402,10 +10422,10 @@
         <v>32.84</v>
       </c>
       <c r="D214" s="5" t="n">
-        <v>37.71</v>
+        <v>37.94</v>
       </c>
       <c r="E214" s="5" t="n">
-        <v>40.79</v>
+        <v>41.04</v>
       </c>
     </row>
     <row r="215">
@@ -10421,10 +10441,10 @@
         <v>62.46</v>
       </c>
       <c r="D215" s="5" t="n">
-        <v>61.3</v>
+        <v>61.67</v>
       </c>
       <c r="E215" s="5" t="n">
-        <v>77.40000000000001</v>
+        <v>77.86</v>
       </c>
     </row>
     <row r="216">
@@ -10440,10 +10460,10 @@
         <v>114.98</v>
       </c>
       <c r="D216" s="5" t="n">
-        <v>90.04000000000001</v>
+        <v>90.58</v>
       </c>
       <c r="E216" s="5" t="n">
-        <v>142.14</v>
+        <v>142.99</v>
       </c>
     </row>
     <row r="217">
@@ -10459,10 +10479,10 @@
         <v>107.95</v>
       </c>
       <c r="D217" s="5" t="n">
-        <v>108.42</v>
+        <v>109.07</v>
       </c>
       <c r="E217" s="5" t="n">
-        <v>133.12</v>
+        <v>133.92</v>
       </c>
     </row>
     <row r="218">
@@ -10478,10 +10498,10 @@
         <v>126.87</v>
       </c>
       <c r="D218" s="5" t="n">
-        <v>112.79</v>
+        <v>113.46</v>
       </c>
       <c r="E218" s="5" t="n">
-        <v>156.01</v>
+        <v>156.95</v>
       </c>
     </row>
     <row r="219">
@@ -10497,10 +10517,10 @@
         <v>55.18</v>
       </c>
       <c r="D219" s="5" t="n">
-        <v>57.63</v>
+        <v>57.98</v>
       </c>
       <c r="E219" s="5" t="n">
-        <v>67.66</v>
+        <v>68.06999999999999</v>
       </c>
     </row>
     <row r="220">
@@ -10516,10 +10536,10 @@
         <v>33.73</v>
       </c>
       <c r="D220" s="5" t="n">
-        <v>33.9</v>
+        <v>34.1</v>
       </c>
       <c r="E220" s="5" t="n">
-        <v>41.24</v>
+        <v>41.49</v>
       </c>
     </row>
     <row r="221">
@@ -10535,10 +10555,10 @@
         <v>15.09</v>
       </c>
       <c r="D221" s="5" t="n">
-        <v>22.48</v>
+        <v>22.61</v>
       </c>
       <c r="E221" s="5" t="n">
-        <v>18.37</v>
+        <v>18.48</v>
       </c>
     </row>
     <row r="222">
@@ -10554,10 +10574,10 @@
         <v>40.78</v>
       </c>
       <c r="D222" s="5" t="n">
-        <v>42.46</v>
+        <v>42.72</v>
       </c>
       <c r="E222" s="5" t="n">
-        <v>49.45</v>
+        <v>49.74</v>
       </c>
     </row>
     <row r="223">
@@ -10573,10 +10593,10 @@
         <v>30.8</v>
       </c>
       <c r="D223" s="5" t="n">
-        <v>38.91</v>
+        <v>39.15</v>
       </c>
       <c r="E223" s="5" t="n">
-        <v>37.19</v>
+        <v>37.41</v>
       </c>
     </row>
     <row r="224">
@@ -10592,10 +10612,10 @@
         <v>75.01000000000001</v>
       </c>
       <c r="D224" s="5" t="n">
-        <v>72.91</v>
+        <v>73.34999999999999</v>
       </c>
       <c r="E224" s="5" t="n">
-        <v>89.92</v>
+        <v>90.45999999999999</v>
       </c>
     </row>
     <row r="225">
@@ -10611,10 +10631,10 @@
         <v>48.54</v>
       </c>
       <c r="D225" s="5" t="n">
-        <v>64.48</v>
+        <v>64.86</v>
       </c>
       <c r="E225" s="5" t="n">
-        <v>57.78</v>
+        <v>58.12</v>
       </c>
     </row>
     <row r="226">
@@ -10630,10 +10650,10 @@
         <v>56.47</v>
       </c>
       <c r="D226" s="5" t="n">
-        <v>64.73999999999999</v>
+        <v>65.13</v>
       </c>
       <c r="E226" s="5" t="n">
-        <v>66.73999999999999</v>
+        <v>67.14</v>
       </c>
     </row>
     <row r="227">
@@ -10649,10 +10669,10 @@
         <v>168.15</v>
       </c>
       <c r="D227" s="5" t="n">
-        <v>166.25</v>
+        <v>167.25</v>
       </c>
       <c r="E227" s="5" t="n">
-        <v>197.55</v>
+        <v>198.74</v>
       </c>
     </row>
     <row r="228">
@@ -10668,10 +10688,10 @@
         <v>264.24</v>
       </c>
       <c r="D228" s="5" t="n">
-        <v>272.88</v>
+        <v>274.51</v>
       </c>
       <c r="E228" s="5" t="n">
-        <v>308.62</v>
+        <v>310.47</v>
       </c>
     </row>
     <row r="229">
@@ -10687,10 +10707,10 @@
         <v>375.96</v>
       </c>
       <c r="D229" s="5" t="n">
-        <v>344.25</v>
+        <v>346.32</v>
       </c>
       <c r="E229" s="5" t="n">
-        <v>436.52</v>
+        <v>439.14</v>
       </c>
     </row>
     <row r="230">
@@ -10706,10 +10726,10 @@
         <v>432</v>
       </c>
       <c r="D230" s="5" t="n">
-        <v>392.76</v>
+        <v>395.12</v>
       </c>
       <c r="E230" s="5" t="n">
-        <v>498.54</v>
+        <v>501.53</v>
       </c>
     </row>
     <row r="231">
@@ -10725,10 +10745,10 @@
         <v>137.33</v>
       </c>
       <c r="D231" s="5" t="n">
-        <v>138.8</v>
+        <v>139.64</v>
       </c>
       <c r="E231" s="5" t="n">
-        <v>157.52</v>
+        <v>158.47</v>
       </c>
     </row>
     <row r="232">
@@ -10744,10 +10764,10 @@
         <v>130.9</v>
       </c>
       <c r="D232" s="5" t="n">
-        <v>127.43</v>
+        <v>128.2</v>
       </c>
       <c r="E232" s="5" t="n">
-        <v>149.24</v>
+        <v>150.14</v>
       </c>
     </row>
     <row r="233">
@@ -10763,10 +10783,10 @@
         <v>97.36</v>
       </c>
       <c r="D233" s="5" t="n">
-        <v>112.07</v>
+        <v>112.74</v>
       </c>
       <c r="E233" s="5" t="n">
-        <v>110.32</v>
+        <v>110.98</v>
       </c>
     </row>
     <row r="234">
@@ -10782,10 +10802,10 @@
         <v>58.3</v>
       </c>
       <c r="D234" s="5" t="n">
-        <v>66.03</v>
+        <v>66.43000000000001</v>
       </c>
       <c r="E234" s="5" t="n">
-        <v>65.66</v>
+        <v>66.05</v>
       </c>
     </row>
     <row r="235">
@@ -10801,10 +10821,10 @@
         <v>11.57</v>
       </c>
       <c r="D235" s="5" t="n">
-        <v>35.02</v>
+        <v>35.23</v>
       </c>
       <c r="E235" s="5" t="n">
-        <v>12.95</v>
+        <v>13.03</v>
       </c>
     </row>
     <row r="236">
@@ -10820,10 +10840,10 @@
         <v>32.05</v>
       </c>
       <c r="D236" s="5" t="n">
-        <v>53.59</v>
+        <v>53.91</v>
       </c>
       <c r="E236" s="5" t="n">
-        <v>35.72</v>
+        <v>35.93</v>
       </c>
     </row>
     <row r="237">
@@ -10839,10 +10859,10 @@
         <v>55.29</v>
       </c>
       <c r="D237" s="5" t="n">
-        <v>64.36</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="E237" s="5" t="n">
-        <v>61.34</v>
+        <v>61.71</v>
       </c>
     </row>
     <row r="238">
@@ -10858,10 +10878,10 @@
         <v>54.59</v>
       </c>
       <c r="D238" s="5" t="n">
-        <v>68.5</v>
+        <v>68.91</v>
       </c>
       <c r="E238" s="5" t="n">
-        <v>60.29</v>
+        <v>60.65</v>
       </c>
     </row>
     <row r="239">
@@ -10877,10 +10897,10 @@
         <v>86.78</v>
       </c>
       <c r="D239" s="5" t="n">
-        <v>92.09</v>
+        <v>92.65000000000001</v>
       </c>
       <c r="E239" s="5" t="n">
-        <v>95.56999999999999</v>
+        <v>96.15000000000001</v>
       </c>
     </row>
     <row r="240">
@@ -10896,10 +10916,10 @@
         <v>145.97</v>
       </c>
       <c r="D240" s="5" t="n">
-        <v>139.64</v>
+        <v>140.47</v>
       </c>
       <c r="E240" s="5" t="n">
-        <v>160.3</v>
+        <v>161.26</v>
       </c>
     </row>
     <row r="241">
@@ -10915,10 +10935,10 @@
         <v>85.79000000000001</v>
       </c>
       <c r="D241" s="5" t="n">
-        <v>59.71</v>
+        <v>60.07</v>
       </c>
       <c r="E241" s="5" t="n">
-        <v>93.95</v>
+        <v>94.51000000000001</v>
       </c>
     </row>
     <row r="242">
@@ -10934,10 +10954,10 @@
         <v>76.38</v>
       </c>
       <c r="D242" s="5" t="n">
-        <v>60.23</v>
+        <v>60.59</v>
       </c>
       <c r="E242" s="5" t="n">
-        <v>83.31999999999999</v>
+        <v>83.81999999999999</v>
       </c>
     </row>
     <row r="243">
@@ -10953,10 +10973,10 @@
         <v>80.04000000000001</v>
       </c>
       <c r="D243" s="5" t="n">
-        <v>70.27</v>
+        <v>70.69</v>
       </c>
       <c r="E243" s="5" t="n">
-        <v>86.98</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="244">
@@ -10972,10 +10992,10 @@
         <v>28.16</v>
       </c>
       <c r="D244" s="5" t="n">
-        <v>28.48</v>
+        <v>28.65</v>
       </c>
       <c r="E244" s="5" t="n">
-        <v>30.49</v>
+        <v>30.67</v>
       </c>
     </row>
     <row r="245">
@@ -10991,10 +11011,10 @@
         <v>15.14</v>
       </c>
       <c r="D245" s="5" t="n">
-        <v>18.57</v>
+        <v>18.68</v>
       </c>
       <c r="E245" s="5" t="n">
-        <v>16.36</v>
+        <v>16.45</v>
       </c>
     </row>
     <row r="246">
@@ -11010,10 +11030,10 @@
         <v>31.79</v>
       </c>
       <c r="D246" s="5" t="n">
-        <v>37.67</v>
+        <v>37.89</v>
       </c>
       <c r="E246" s="5" t="n">
-        <v>34.27</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="247">
@@ -11029,10 +11049,10 @@
         <v>25.23</v>
       </c>
       <c r="D247" s="5" t="n">
-        <v>27.21</v>
+        <v>27.37</v>
       </c>
       <c r="E247" s="5" t="n">
-        <v>27.14</v>
+        <v>27.31</v>
       </c>
     </row>
     <row r="248">
@@ -11048,10 +11068,10 @@
         <v>17.65</v>
       </c>
       <c r="D248" s="5" t="n">
-        <v>23.7</v>
+        <v>23.84</v>
       </c>
       <c r="E248" s="5" t="n">
-        <v>18.93</v>
+        <v>19.04</v>
       </c>
     </row>
     <row r="249">
@@ -11067,10 +11087,10 @@
         <v>133.13</v>
       </c>
       <c r="D249" s="5" t="n">
-        <v>88.68000000000001</v>
+        <v>89.20999999999999</v>
       </c>
       <c r="E249" s="5" t="n">
-        <v>142.34</v>
+        <v>143.2</v>
       </c>
     </row>
     <row r="250">
@@ -11086,10 +11106,10 @@
         <v>46.25</v>
       </c>
       <c r="D250" s="5" t="n">
-        <v>55.42</v>
+        <v>55.75</v>
       </c>
       <c r="E250" s="5" t="n">
-        <v>49.3</v>
+        <v>49.59</v>
       </c>
     </row>
     <row r="251">
@@ -11105,10 +11125,10 @@
         <v>80.23</v>
       </c>
       <c r="D251" s="5" t="n">
-        <v>90.08</v>
+        <v>90.62</v>
       </c>
       <c r="E251" s="5" t="n">
-        <v>85.22</v>
+        <v>85.73</v>
       </c>
     </row>
     <row r="252">
@@ -11124,10 +11144,10 @@
         <v>146.58</v>
       </c>
       <c r="D252" s="5" t="n">
-        <v>140.75</v>
+        <v>141.6</v>
       </c>
       <c r="E252" s="5" t="n">
-        <v>155.16</v>
+        <v>156.09</v>
       </c>
     </row>
     <row r="253">
@@ -11143,10 +11163,10 @@
         <v>198.82</v>
       </c>
       <c r="D253" s="5" t="n">
-        <v>173.24</v>
+        <v>174.28</v>
       </c>
       <c r="E253" s="5" t="n">
-        <v>209.73</v>
+        <v>210.99</v>
       </c>
     </row>
     <row r="254">
@@ -11162,10 +11182,10 @@
         <v>191.83</v>
       </c>
       <c r="D254" s="5" t="n">
-        <v>157.21</v>
+        <v>158.15</v>
       </c>
       <c r="E254" s="5" t="n">
-        <v>202.21</v>
+        <v>203.42</v>
       </c>
     </row>
     <row r="255">
@@ -11181,10 +11201,10 @@
         <v>216.14</v>
       </c>
       <c r="D255" s="5" t="n">
-        <v>151.05</v>
+        <v>151.95</v>
       </c>
       <c r="E255" s="5" t="n">
-        <v>227.67</v>
+        <v>229.03</v>
       </c>
     </row>
     <row r="256">
@@ -11200,10 +11220,10 @@
         <v>26.5</v>
       </c>
       <c r="D256" s="5" t="n">
-        <v>18.3</v>
+        <v>18.41</v>
       </c>
       <c r="E256" s="5" t="n">
-        <v>27.89</v>
+        <v>28.06</v>
       </c>
     </row>
     <row r="257">
@@ -11219,10 +11239,10 @@
         <v>10.18</v>
       </c>
       <c r="D257" s="5" t="n">
-        <v>21.42</v>
+        <v>21.54</v>
       </c>
       <c r="E257" s="5" t="n">
-        <v>10.71</v>
+        <v>10.77</v>
       </c>
     </row>
     <row r="258">
@@ -11238,10 +11258,10 @@
         <v>52.94</v>
       </c>
       <c r="D258" s="5" t="n">
-        <v>67.36</v>
+        <v>67.76000000000001</v>
       </c>
       <c r="E258" s="5" t="n">
-        <v>55.65</v>
+        <v>55.98</v>
       </c>
     </row>
     <row r="259">
@@ -11257,10 +11277,10 @@
         <v>39.93</v>
       </c>
       <c r="D259" s="5" t="n">
-        <v>54.89</v>
+        <v>55.22</v>
       </c>
       <c r="E259" s="5" t="n">
-        <v>41.95</v>
+        <v>42.2</v>
       </c>
     </row>
     <row r="260">
@@ -11276,10 +11296,10 @@
         <v>23.72</v>
       </c>
       <c r="D260" s="5" t="n">
-        <v>50.64</v>
+        <v>50.94</v>
       </c>
       <c r="E260" s="5" t="n">
-        <v>24.84</v>
+        <v>24.99</v>
       </c>
     </row>
     <row r="261">
@@ -11295,10 +11315,10 @@
         <v>76.73</v>
       </c>
       <c r="D261" s="5" t="n">
-        <v>71.56999999999999</v>
+        <v>72</v>
       </c>
       <c r="E261" s="5" t="n">
-        <v>80.11</v>
+        <v>80.59999999999999</v>
       </c>
     </row>
     <row r="262">
@@ -11314,10 +11334,10 @@
         <v>62.93</v>
       </c>
       <c r="D262" s="5" t="n">
-        <v>64.28</v>
+        <v>64.66</v>
       </c>
       <c r="E262" s="5" t="n">
-        <v>65.51000000000001</v>
+        <v>65.90000000000001</v>
       </c>
     </row>
     <row r="263">
@@ -11333,10 +11353,10 @@
         <v>70.56</v>
       </c>
       <c r="D263" s="5" t="n">
-        <v>77.63</v>
+        <v>78.09</v>
       </c>
       <c r="E263" s="5" t="n">
-        <v>73.27</v>
+        <v>73.70999999999999</v>
       </c>
     </row>
     <row r="264">
@@ -11352,10 +11372,10 @@
         <v>93.92</v>
       </c>
       <c r="D264" s="5" t="n">
-        <v>80.84</v>
+        <v>81.33</v>
       </c>
       <c r="E264" s="5" t="n">
-        <v>97.28</v>
+        <v>97.86</v>
       </c>
     </row>
     <row r="265">
@@ -11371,10 +11391,10 @@
         <v>463.18</v>
       </c>
       <c r="D265" s="5" t="n">
-        <v>273.39</v>
+        <v>275.03</v>
       </c>
       <c r="E265" s="5" t="n">
-        <v>478.57</v>
+        <v>481.44</v>
       </c>
     </row>
     <row r="266">
@@ -11390,10 +11410,10 @@
         <v>107.96</v>
       </c>
       <c r="D266" s="5" t="n">
-        <v>84.48999999999999</v>
+        <v>84.98999999999999</v>
       </c>
       <c r="E266" s="5" t="n">
-        <v>111.06</v>
+        <v>111.72</v>
       </c>
     </row>
     <row r="267">
@@ -11409,10 +11429,10 @@
         <v>107.79</v>
       </c>
       <c r="D267" s="5" t="n">
-        <v>95.45</v>
+        <v>96.02</v>
       </c>
       <c r="E267" s="5" t="n">
-        <v>110.4</v>
+        <v>111.06</v>
       </c>
     </row>
     <row r="268">
@@ -11428,10 +11448,10 @@
         <v>61.8</v>
       </c>
       <c r="D268" s="5" t="n">
-        <v>56.36</v>
+        <v>56.7</v>
       </c>
       <c r="E268" s="5" t="n">
-        <v>63.02</v>
+        <v>63.4</v>
       </c>
     </row>
     <row r="269">
@@ -11447,10 +11467,10 @@
         <v>45.13</v>
       </c>
       <c r="D269" s="5" t="n">
-        <v>52.28</v>
+        <v>52.6</v>
       </c>
       <c r="E269" s="5" t="n">
-        <v>45.93</v>
+        <v>46.21</v>
       </c>
     </row>
     <row r="270">
@@ -11466,10 +11486,10 @@
         <v>13.79</v>
       </c>
       <c r="D270" s="5" t="n">
-        <v>32.42</v>
+        <v>32.62</v>
       </c>
       <c r="E270" s="5" t="n">
-        <v>14.01</v>
+        <v>14.09</v>
       </c>
     </row>
     <row r="271">
@@ -11485,10 +11505,10 @@
         <v>16.99</v>
       </c>
       <c r="D271" s="5" t="n">
-        <v>27.89</v>
+        <v>28.06</v>
       </c>
       <c r="E271" s="5" t="n">
-        <v>17.22</v>
+        <v>17.33</v>
       </c>
     </row>
     <row r="272">
@@ -11504,10 +11524,10 @@
         <v>43.74</v>
       </c>
       <c r="D272" s="5" t="n">
-        <v>38.9</v>
+        <v>39.14</v>
       </c>
       <c r="E272" s="5" t="n">
-        <v>44.14</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="273">
@@ -11523,10 +11543,10 @@
         <v>40.2</v>
       </c>
       <c r="D273" s="5" t="n">
-        <v>45.26</v>
+        <v>45.54</v>
       </c>
       <c r="E273" s="5" t="n">
-        <v>40.38</v>
+        <v>40.62</v>
       </c>
     </row>
     <row r="274">
@@ -11542,10 +11562,10 @@
         <v>44.39</v>
       </c>
       <c r="D274" s="5" t="n">
-        <v>41.17</v>
+        <v>41.42</v>
       </c>
       <c r="E274" s="5" t="n">
-        <v>44.39</v>
+        <v>44.66</v>
       </c>
     </row>
     <row r="275">
@@ -11561,10 +11581,10 @@
         <v>39.73</v>
       </c>
       <c r="D275" s="5" t="n">
-        <v>32.76</v>
+        <v>32.89</v>
       </c>
       <c r="E275" s="5" t="n">
-        <v>39.73</v>
+        <v>39.89</v>
       </c>
     </row>
     <row r="276">
@@ -11580,10 +11600,10 @@
         <v>44.24</v>
       </c>
       <c r="D276" s="5" t="n">
-        <v>42.63</v>
+        <v>42.71</v>
       </c>
       <c r="E276" s="5" t="n">
-        <v>44.24</v>
+        <v>44.33</v>
       </c>
     </row>
     <row r="277">
@@ -11624,8 +11644,27 @@
         <v>110.53</v>
       </c>
     </row>
+    <row r="279">
+      <c r="A279" s="4" t="inlineStr">
+        <is>
+          <t>Aug 2026</t>
+        </is>
+      </c>
+      <c r="B279" s="5" t="n">
+        <v>62.06</v>
+      </c>
+      <c r="C279" s="5" t="n">
+        <v>80.65000000000001</v>
+      </c>
+      <c r="D279" s="5" t="n">
+        <v>62.06</v>
+      </c>
+      <c r="E279" s="5" t="n">
+        <v>80.65000000000001</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B278">
+  <conditionalFormatting sqref="B2:B279">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -11637,7 +11676,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C278">
+  <conditionalFormatting sqref="C2:C279">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -11649,7 +11688,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D278">
+  <conditionalFormatting sqref="D2:D279">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -11661,7 +11700,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E278">
+  <conditionalFormatting sqref="E2:E279">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
